--- a/projects/mini-rally/04_Developement_tracking/Mini_Rally_Product_Plan.xlsx
+++ b/projects/mini-rally/04_Developement_tracking/Mini_Rally_Product_Plan.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Ra109800aecf940a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Roadmap" sheetId="2" r:id="R24891df4abb545a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BA Tasks" sheetId="3" r:id="R48e3900e9ae14292"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEV Tasks" sheetId="4" r:id="R3312ad1c136040ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="5" r:id="R54c293758b8e43a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rc4d4e13c9aa94da6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Roadmap" sheetId="2" r:id="R8c9eb6e2538346b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BA Tasks" sheetId="3" r:id="R2a26c085553640bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEV Tasks" sheetId="4" r:id="R0447679099534b5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="5" r:id="R125ffe1788d448b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -769,10 +769,8 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
-      <x:c r="A2" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Single planning workbook | Baseline: 2026-07-26 | Scope: BA, FE DEV, DevInt and UAT through Phase 5</x:t>
-        </x:is>
+      <x:c r="A2" s="6" t="str">
+        <x:v>Single planning workbook | Baseline: 2026-07-28 | Scope: BA, FE DEV, DevInt and UAT through closed Phase 5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
@@ -816,10 +814,8 @@
           <x:t xml:space="preserve">BA baseline</x:t>
         </x:is>
       </x:c>
-      <x:c r="H5" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Phase 0-5 governance aligned</x:t>
-        </x:is>
+      <x:c r="H5" s="15" t="str">
+        <x:v>Phase 0-5 BA baseline aligned; Phase 5 DEV handoff ready</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -829,7 +825,7 @@
         </x:is>
       </x:c>
       <x:c r="B6" s="15" t="n">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D6" s="15" t="inlineStr">
         <x:is>
@@ -845,10 +841,8 @@
           <x:t xml:space="preserve">DEV current</x:t>
         </x:is>
       </x:c>
-      <x:c r="H6" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Phase 0-4 DevInt; Phase 5 production not started</x:t>
-        </x:is>
+      <x:c r="H6" s="15" t="str">
+        <x:v>Phase 0-4 DevInt active; Phase 5 production not started</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -858,7 +852,7 @@
         </x:is>
       </x:c>
       <x:c r="B7" s="15" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="15" t="inlineStr">
         <x:is>
@@ -875,7 +869,7 @@
         </x:is>
       </x:c>
       <x:c r="H7" s="15" t="str">
-        <x:v>P5.2 Capacity Planning active; docs aligned and mockup implementation next</x:v>
+        <x:v>Start Phase 5 production analysis from dedicated DEV handoff</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -888,9 +882,10 @@
     <x:row r="10">
       <x:c r="A10" s="66" t="str">
         <x:v>1. BA owns business rules, SRS/mockup alignment and acceptance.
-2. Every Phase 5 feature follows: propose -&gt; BA confirm -&gt; docs align -&gt; implement -&gt; verify -&gt; BA accept -&gt; close.
-3. BA/Mockup readiness and Production readiness are always separate.
-4. Phase 5 closes only after P5.1-P5.3 close, tests/traceability pass and BA accepts; only then create the Phase 5 DEV handoff.</x:v>
+2. Closed Phase 5 scope is Portfolio Items plus Capacity Planning.
+3. Release Planning and Release Tracking are excluded; Reports are Future Backlog only.
+4. BA/Mockup readiness, DEV handoff readiness and Production readiness remain separate.
+5. Future changes require propose -&gt; BA confirm -&gt; docs -&gt; implement -&gt; verify -&gt; accept.</x:v>
       </x:c>
       <x:c r="B10" s="67" t="n"/>
       <x:c r="C10" s="67" t="n"/>
@@ -928,39 +923,37 @@
     </x:row>
     <x:row r="16" ht="32" customHeight="1">
       <x:c r="A16" s="11" t="str">
-        <x:v>Phase 5 Order</x:v>
-      </x:c>
-      <x:c r="B16" s="11" t="n">
+        <x:v>Phase 5 Closed</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
         <x:v>P5.0 Rebaseline</x:v>
       </x:c>
-      <x:c r="D16" s="11" t="n">
+      <x:c r="D16" s="11" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
-        <x:v>P5.1 Closure</x:v>
-      </x:c>
-      <x:c r="F16" s="11" t="n">
+        <x:v>P5.1 Portfolio Items</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>P5.2 Capacity -&gt; P5.3 Tracking</x:v>
-      </x:c>
-      <x:c r="H16" s="11" t="n">
+        <x:v>P5.2 Capacity Planning</x:v>
+      </x:c>
+      <x:c r="H16" s="11" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="I16" s="11" t="str">
-        <x:v>P5.4 Closeout</x:v>
+        <x:v>P5.3 removed / P5.4 DEV Handoff</x:v>
       </x:c>
       <x:c r="J16" s="11" t="n"/>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
-      <x:c r="A18" s="52" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sources of truth: RECONCILED_SOURCE_OF_TRUTH.md, Phase 5/PHASE5_DEVELOPMENT_TRACKING.md, phase SRS/checklists, 06_Dev testing align and 07_Test Business/specs. The Phase 5 DEV handoff is created only after phase close.</x:t>
-        </x:is>
+      <x:c r="A18" s="52" t="str">
+        <x:v>Sources of truth: RECONCILED_SOURCE_OF_TRUTH.md, Phase 5/PHASE5_DEV_HANDOFF.md, Phase 5 SRS/catalogs, PHASE5_DEVELOPMENT_TRACKING.md and 07_Test Business/specs. Phase 5 is BA/mockup closed; production implementation is not started.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1003,7 +996,7 @@
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Product baseline 2026-07-26 | P5-GOV v2 confirmed; DEV dates remain an editable proposal</x:v>
+        <x:v>Product baseline 2026-07-28 | P5-GOV v4 closed; DEV dates remain an editable proposal</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
@@ -1298,26 +1291,28 @@
         </x:is>
       </x:c>
       <x:c r="C10" s="15" t="str">
-        <x:v>Portfolio Items, Capacity Planning and Release Tracking; Release Planning deferred</x:v>
+        <x:v>Portfolio Items and Capacity Planning; Release Planning/Tracking excluded</x:v>
       </x:c>
       <x:c r="D10" s="22" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E10" s="34" t="str">
-        <x:v>Needs BA</x:v>
+        <x:v>Ready</x:v>
       </x:c>
       <x:c r="F10" s="15" t="str">
-        <x:v>P5.2 Capacity Planning</x:v>
+        <x:v>DEV Handoff</x:v>
       </x:c>
       <x:c r="G10" s="74" t="n">
         <x:v>46229</x:v>
       </x:c>
-      <x:c r="H10" s="74"/>
+      <x:c r="H10" s="74" t="n">
+        <x:v>46231</x:v>
+      </x:c>
       <x:c r="I10" s="15" t="str">
-        <x:v>P5.1-P5.3 BA accepted; Phase 5 tests and traceability complete; Phase 5 DEV handoff created</x:v>
+        <x:v>P5.1/P5.2 BA accepted; scope/tests/workbook reconciled; Phase 5 DEV handoff created</x:v>
       </x:c>
       <x:c r="J10" s="15" t="str">
-        <x:v>Implement P5.2 Capacity Planning after docs alignment</x:v>
+        <x:v>Start production analysis from Phase 5 DEV handoff</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="58" customHeight="1">
@@ -1332,7 +1327,7 @@
         </x:is>
       </x:c>
       <x:c r="C11" s="15" t="str">
-        <x:v>Team/Iteration boards, generic Reports, Theme/Initiative, Release Planning, burnup history and multi-Release scenarios</x:v>
+        <x:v>Team/Iteration boards, Reports, Release Planning, Release Tracking, Theme/deeper hierarchy, burnup history and multi-Release scenarios</x:v>
       </x:c>
       <x:c r="D11" s="25" t="str">
         <x:v>Future Backlog</x:v>
@@ -2990,10 +2985,8 @@
       </x:c>
     </x:row>
     <x:row r="28" ht="94.5" customHeight="1">
-      <x:c r="A28" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BA-0501</x:t>
-        </x:is>
+      <x:c r="A28" s="15" t="str">
+        <x:v>BA-0501</x:v>
       </x:c>
       <x:c r="B28" s="15" t="inlineStr">
         <x:is>
@@ -3036,143 +3029,105 @@
       <x:c r="J28" s="74" t="n">
         <x:v>46229</x:v>
       </x:c>
-      <x:c r="K28" s="74" t="n"/>
+      <x:c r="K28" s="74" t="n">
+        <x:v>46231</x:v>
+      </x:c>
       <x:c r="L28" s="76" t="str">
-        <x:v>P5.1 Amendment v3 implementation verified and BA accepted; continue Phase 5</x:v>
+        <x:v>Feature and Epic flows, formulas, archive rules and accepted UI are documented and BA accepted</x:v>
       </x:c>
       <x:c r="M28" s="76" t="str">
-        <x:v>BA accepted 2026-07-26</x:v>
+        <x:v>DEV handoff</x:v>
       </x:c>
       <x:c r="N28" s="76" t="str">
-        <x:v>P5.1 plus BA-confirmed Amendment v3 accepted 2026-07-26: shared Feature-linked Work Item flow, Backlog shows Unscheduled only, Task Estimate/To Do/Actual independent with complete setting To Do to 0. Build and runtime smoke completed; close P5.1 and continue Phase 5. Production API/persistence remains dev scope.</x:v>
+        <x:v>P5.1 Feature baseline and Epic amendment closed 2026-07-28; production persistence/API/RBAC remains DEV scope</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="54" customHeight="1">
-      <x:c r="A29" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BA-0502</x:t>
-        </x:is>
+      <x:c r="A29" s="15" t="str">
+        <x:v>BA-F501</x:v>
       </x:c>
       <x:c r="B29" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Phase 5</x:t>
         </x:is>
       </x:c>
-      <x:c r="C29" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Release Planning</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D29" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Define and accept Feature-to-Release planning board</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E29" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Phase 5/02_Release_Planning/SRS.md</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F29" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BA-0501</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G29" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">P0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H29" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Planned</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I29" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BA/PO</x:t>
-        </x:is>
+      <x:c r="C29" s="15" t="str">
+        <x:v>Release Planning</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="str">
+        <x:v>Keep Release Planning outside the closed Phase 5 MVP</x:v>
+      </x:c>
+      <x:c r="E29" s="15" t="str">
+        <x:v>Future_Backlog</x:v>
+      </x:c>
+      <x:c r="F29" s="15" t="str">
+        <x:v>BA decision 2026-07-26</x:v>
+      </x:c>
+      <x:c r="G29" s="15" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="H29" s="22" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="I29" s="15" t="str">
+        <x:v>BA/PO</x:v>
       </x:c>
       <x:c r="J29" s="74" t="n"/>
       <x:c r="K29" s="74" t="n"/>
-      <x:c r="L29" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Assign, move and unassign Features without duplicating Release management</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M29" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Feature proposal</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N29" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Starts only after P5.1 closes</x:t>
-        </x:is>
+      <x:c r="L29" s="15" t="str">
+        <x:v>No Release Planning behavior is required for Phase 5 close</x:v>
+      </x:c>
+      <x:c r="M29" s="15" t="str">
+        <x:v>Future backlog review</x:v>
+      </x:c>
+      <x:c r="N29" s="15" t="str">
+        <x:v>Capacity Planning publish is the accepted Phase 5 planning action</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="54" customHeight="1">
-      <x:c r="A30" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BA-0503</x:t>
-        </x:is>
+      <x:c r="A30" s="15" t="str">
+        <x:v>BA-F502</x:v>
       </x:c>
       <x:c r="B30" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Phase 5</x:t>
         </x:is>
       </x:c>
-      <x:c r="C30" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Release Tracking</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D30" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Define and accept Release KPI and Feature progress tracking</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E30" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Phase 5/03_Release_Tracking/SRS.md</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F30" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BA-0502</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G30" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">P0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H30" s="22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Planned</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I30" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BA/PO</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J30" s="74" t="n"/>
-      <x:c r="K30" s="74" t="n"/>
-      <x:c r="L30" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Plan Estimate rollup, zero-estimate handling and no auto Release state pass UAT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M30" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Feature proposal</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N30" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Burnup waits for trustworthy history</x:t>
-        </x:is>
+      <x:c r="C30" s="15" t="str">
+        <x:v>Release Tracking</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="str">
+        <x:v>Remove dedicated Release Tracking from Phase 5</x:v>
+      </x:c>
+      <x:c r="E30" s="15" t="str">
+        <x:v>Phase 5/PHASE5_DEV_HANDOFF.md</x:v>
+      </x:c>
+      <x:c r="F30" s="15" t="str">
+        <x:v>BA decision 2026-07-28</x:v>
+      </x:c>
+      <x:c r="G30" s="15" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="H30" s="22" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="I30" s="15" t="str">
+        <x:v>BA/PO</x:v>
+      </x:c>
+      <x:c r="J30" s="74" t="n">
+        <x:v>46231</x:v>
+      </x:c>
+      <x:c r="K30" s="74" t="n">
+        <x:v>46231</x:v>
+      </x:c>
+      <x:c r="L30" s="15" t="str">
+        <x:v>No Release Tracking implementation is claimed; future observation may be proposed under Reports</x:v>
+      </x:c>
+      <x:c r="M30" s="15" t="str">
+        <x:v>Future Reports proposal</x:v>
+      </x:c>
+      <x:c r="N30" s="15" t="str">
+        <x:v>Supersedes the prior P5.3 selected-Release screen proposal</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="54" customHeight="1">
@@ -3198,7 +3153,7 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H31" s="28" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I31" s="15" t="str">
         <x:v>BA/PO</x:v>
@@ -3206,60 +3161,66 @@
       <x:c r="J31" s="74" t="n">
         <x:v>46229</x:v>
       </x:c>
-      <x:c r="K31" s="74"/>
+      <x:c r="K31" s="74" t="n">
+        <x:v>46231</x:v>
+      </x:c>
       <x:c r="L31" s="15" t="str">
-        <x:v>Plan list, create modal, Teams by Total, allocations, publish and RBAC pass UAT</x:v>
+        <x:v>Single-Release Team capacity planning, allocations, metrics, warnings and publish lifecycle are BA accepted</x:v>
       </x:c>
       <x:c r="M31" s="15" t="str">
-        <x:v>Docs alignment -&gt; CAP-1 mockup</x:v>
+        <x:v>DEV handoff</x:v>
       </x:c>
       <x:c r="N31" s="15" t="str">
-        <x:v>BA confirmed 2026-07-26: Rally child Projects map to Mini Rally Teams; one Draft/Published plan per Project+Release</x:v>
+        <x:v>P5.2 closed 2026-07-28; production persistence/API/server authorization remains DEV scope</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="54" customHeight="1">
       <x:c r="A32" s="15" t="str">
-        <x:v>BA-0503</x:v>
+        <x:v>BA-F503</x:v>
       </x:c>
       <x:c r="B32" s="15" t="str">
         <x:v>Phase 5</x:v>
       </x:c>
       <x:c r="C32" s="15" t="str">
-        <x:v>Release Tracking</x:v>
+        <x:v>Reports Observation</x:v>
       </x:c>
       <x:c r="D32" s="15" t="str">
-        <x:v>Define and accept Release KPI and Feature progress tracking</x:v>
+        <x:v>Preserve Reports as the preferred future cross-release observation direction</x:v>
       </x:c>
       <x:c r="E32" s="15" t="str">
-        <x:v>Phase 5/03_Release_Tracking/SRS.md</x:v>
+        <x:v>Future_Backlog</x:v>
       </x:c>
       <x:c r="F32" s="15" t="str">
-        <x:v>BA-0502</x:v>
+        <x:v>Phase 5 close decision</x:v>
       </x:c>
       <x:c r="G32" s="15" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="H32" s="25" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Future Backlog</x:v>
       </x:c>
       <x:c r="I32" s="15" t="str">
         <x:v>BA/PO</x:v>
       </x:c>
-      <x:c r="J32" s="74"/>
-      <x:c r="K32" s="74"/>
+      <x:c r="J32" s="74" t="n">
+        <x:v>46231</x:v>
+      </x:c>
+      <x:c r="K32" s="74" t="n">
+        <x:v>46231</x:v>
+      </x:c>
       <x:c r="L32" s="15" t="str">
-        <x:v>Plan Estimate rollup, zero-estimate handling and no auto Release state pass UAT</x:v>
+        <x:v>Phase 5 close does not define or claim a Report feature</x:v>
       </x:c>
       <x:c r="M32" s="15" t="str">
-        <x:v>Feature proposal</x:v>
+        <x:v>Future feature proposal</x:v>
       </x:c>
       <x:c r="N32" s="15" t="str">
-        <x:v>Starts after P5.2 Capacity Planning closes</x:v>
+        <x:v>Requires separate proposal, SRS, confirmation and delivery gates</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="54" customHeight="1">
       <x:c r="A33" s="57" t="str">
-        <x:v>BA-0504</x:v>
+        <x:v>BA-0503</x:v>
       </x:c>
       <x:c r="B33" s="57" t="str">
         <x:v>Phase 5</x:v>
@@ -3271,74 +3232,74 @@
         <x:v>Close Phase 5 and publish the dedicated DEV handoff</x:v>
       </x:c>
       <x:c r="E33" s="57" t="str">
-        <x:v>Phase 5 test pack + traceability + Phase 5 DEV handoff</x:v>
+        <x:v>Phase 5/PHASE5_DEV_HANDOFF.md</x:v>
       </x:c>
       <x:c r="F33" s="57" t="str">
-        <x:v>BA-0501..0503</x:v>
+        <x:v>BA-0501 + BA-0502 + scope decision</x:v>
       </x:c>
       <x:c r="G33" s="57" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H33" s="59" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="I33" s="57" t="str">
         <x:v>BA/UAT</x:v>
       </x:c>
-      <x:c r="J33" s="75"/>
-      <x:c r="K33" s="75"/>
+      <x:c r="J33" s="75" t="n">
+        <x:v>46231</x:v>
+      </x:c>
+      <x:c r="K33" s="75" t="n">
+        <x:v>46231</x:v>
+      </x:c>
       <x:c r="L33" s="57" t="str">
-        <x:v>P5.1-P5.3 closed; build/runtime/test evidence complete; BA accepts phase</x:v>
+        <x:v>P5.1/P5.2 closed; Release Tracking excluded; documents/workbook/test disposition aligned</x:v>
       </x:c>
       <x:c r="M33" s="57" t="str">
-        <x:v>DEV handoff</x:v>
+        <x:v>Developer document review</x:v>
       </x:c>
       <x:c r="N33" s="57" t="str">
-        <x:v>Handoff is created only after Phase 5 close</x:v>
+        <x:v>Phase 5 is BA/mockup closed and DEV handoff ready; production implementation is not started</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="54" customHeight="1">
       <x:c r="A34" s="57" t="str">
-        <x:v>BA-0505</x:v>
+        <x:v>BA-F504</x:v>
       </x:c>
       <x:c r="B34" s="57" t="str">
         <x:v>Future</x:v>
       </x:c>
       <x:c r="C34" s="57" t="str">
-        <x:v>Release Planning</x:v>
+        <x:v>Preliminary Estimate Config</x:v>
       </x:c>
       <x:c r="D34" s="57" t="str">
-        <x:v>Keep Release Planning deferred until BA re-promotes it</x:v>
+        <x:v>Define user-managed Preliminary Estimate point/count mapping</x:v>
       </x:c>
       <x:c r="E34" s="57" t="str">
-        <x:v>Future_Backlog/02_Release_Planning.md</x:v>
+        <x:v>Future_Backlog</x:v>
       </x:c>
       <x:c r="F34" s="57" t="str">
-        <x:v>BA decision 2026-07-26</x:v>
+        <x:v>Project Management design proposal</x:v>
       </x:c>
       <x:c r="G34" s="57" t="str">
         <x:v>P2</x:v>
       </x:c>
       <x:c r="H34" s="61" t="str">
-        <x:v>Done</x:v>
+        <x:v>Future Backlog</x:v>
       </x:c>
       <x:c r="I34" s="57" t="str">
         <x:v>BA/PO</x:v>
       </x:c>
-      <x:c r="J34" s="75" t="n">
-        <x:v>46229</x:v>
-      </x:c>
-      <x:c r="K34" s="75" t="n">
-        <x:v>46229</x:v>
-      </x:c>
+      <x:c r="J34" s="75"/>
+      <x:c r="K34" s="75"/>
       <x:c r="L34" s="57" t="str">
-        <x:v>Active Phase 5 order no longer depends on Release Planning</x:v>
+        <x:v>Production does not silently treat the mock mapping as a permanent hard-coded rule</x:v>
       </x:c>
       <x:c r="M34" s="57" t="str">
         <x:v>Future backlog review</x:v>
       </x:c>
       <x:c r="N34" s="57" t="str">
-        <x:v>Capacity Planning publish is the active Phase 5 assignment mechanism</x:v>
+        <x:v>Confirmed future location: Settings &gt; Workspace &gt; Project Management</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5211,45 +5172,33 @@
       <x:c r="N31" s="15" t="str"/>
     </x:row>
     <x:row r="32" ht="54" customHeight="1">
-      <x:c r="A32" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DEV-0501</x:t>
-        </x:is>
+      <x:c r="A32" s="15" t="str">
+        <x:v>DEV-0501</x:v>
       </x:c>
       <x:c r="B32" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Phase 5</x:t>
         </x:is>
       </x:c>
-      <x:c r="C32" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Portfolio Items</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D32" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implement production Portfolio Items from the closed Phase 5 handoff</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E32" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Future Phase 5 DEV handoff</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F32" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BA-0501 + Phase 5 close</x:t>
-        </x:is>
+      <x:c r="C32" s="15" t="str">
+        <x:v>Portfolio Items</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="str">
+        <x:v>Implement production Portfolio Items from the closed Phase 5 handoff</x:v>
+      </x:c>
+      <x:c r="E32" s="15" t="str">
+        <x:v>Phase 5/PHASE5_DEV_HANDOFF.md</x:v>
+      </x:c>
+      <x:c r="F32" s="15" t="str">
+        <x:v>BA-0501 + Phase 5 close</x:v>
       </x:c>
       <x:c r="G32" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">P0</x:t>
         </x:is>
       </x:c>
-      <x:c r="H32" s="34" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Needs BA</x:t>
-        </x:is>
+      <x:c r="H32" s="34" t="str">
+        <x:v>Ready</x:v>
       </x:c>
       <x:c r="I32" s="15" t="inlineStr">
         <x:is>
@@ -5258,170 +5207,120 @@
       </x:c>
       <x:c r="J32" s="74" t="n"/>
       <x:c r="K32" s="74" t="n"/>
-      <x:c r="L32" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Project-scoped RBAC, Feature data, Archive and rollups pass DevInt</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M32" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DevInt</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N32" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mockup implementation is not production authorization</x:t>
-        </x:is>
+      <x:c r="L32" s="15" t="str">
+        <x:v>Epic/Feature persistence, project scope, archive and leaf rollups pass DevInt</x:v>
+      </x:c>
+      <x:c r="M32" s="15" t="str">
+        <x:v>DevInt</x:v>
+      </x:c>
+      <x:c r="N32" s="15" t="str">
+        <x:v>Mockup acceptance is not production evidence</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="54" customHeight="1">
-      <x:c r="A33" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DEV-0502</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B33" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Phase 5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C33" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Release Planning</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D33" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implement Feature-to-Release planning</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E33" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Future Phase 5 DEV handoff</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F33" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DEV-0501 + BA-0502</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G33" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">P0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H33" s="34" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Needs BA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I33" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FE DEV</x:t>
-        </x:is>
+      <x:c r="A33" s="15" t="str">
+        <x:v>DEV-F501</x:v>
+      </x:c>
+      <x:c r="B33" s="15" t="str">
+        <x:v>Future</x:v>
+      </x:c>
+      <x:c r="C33" s="15" t="str">
+        <x:v>Release Planning</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="str">
+        <x:v>Do not implement until BA re-promotes Release Planning</x:v>
+      </x:c>
+      <x:c r="E33" s="15" t="str">
+        <x:v>Future_Backlog</x:v>
+      </x:c>
+      <x:c r="F33" s="15" t="str">
+        <x:v>PO approval</x:v>
+      </x:c>
+      <x:c r="G33" s="15" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="H33" s="34" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="I33" s="15" t="str">
+        <x:v>DEV</x:v>
       </x:c>
       <x:c r="J33" s="74" t="n"/>
       <x:c r="K33" s="74" t="n"/>
-      <x:c r="L33" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Assign/move/unassign is project-scoped and does not duplicate Release CRUD</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M33" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DevInt</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N33" s="15" t="n"/>
+      <x:c r="L33" s="15" t="str">
+        <x:v>No hidden or partial Release Planning implementation enters active navigation</x:v>
+      </x:c>
+      <x:c r="M33" s="15" t="str">
+        <x:v>Future backlog review</x:v>
+      </x:c>
+      <x:c r="N33" s="15" t="str">
+        <x:v>Excluded from closed Phase 5</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="54" customHeight="1">
-      <x:c r="A34" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DEV-0503</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B34" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Phase 5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C34" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Release Tracking</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D34" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implement Release KPI and Feature progress tracking</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E34" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Future Phase 5 DEV handoff</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F34" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DEV-0502 + BA-0503</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G34" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">P0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H34" s="34" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Needs BA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I34" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FE DEV</x:t>
-        </x:is>
+      <x:c r="A34" s="15" t="str">
+        <x:v>DEV-F502</x:v>
+      </x:c>
+      <x:c r="B34" s="15" t="str">
+        <x:v>Future</x:v>
+      </x:c>
+      <x:c r="C34" s="15" t="str">
+        <x:v>Release Tracking</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="str">
+        <x:v>Do not implement a dedicated Release Tracking screen from historical Phase 5 stubs</x:v>
+      </x:c>
+      <x:c r="E34" s="15" t="str">
+        <x:v>Future_Backlog</x:v>
+      </x:c>
+      <x:c r="F34" s="15" t="str">
+        <x:v>PO approval</x:v>
+      </x:c>
+      <x:c r="G34" s="15" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="H34" s="34" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="I34" s="15" t="str">
+        <x:v>DEV</x:v>
       </x:c>
       <x:c r="J34" s="74" t="n"/>
       <x:c r="K34" s="74" t="n"/>
-      <x:c r="L34" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Confirmed rollup, zero-state and manual Release lifecycle pass DevInt</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M34" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DevInt</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N34" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">No fabricated burnup history</x:t>
-        </x:is>
+      <x:c r="L34" s="15" t="str">
+        <x:v>Future observation is proposed under Reports only after BA confirmation</x:v>
+      </x:c>
+      <x:c r="M34" s="15" t="str">
+        <x:v>Future backlog review</x:v>
+      </x:c>
+      <x:c r="N34" s="15" t="str">
+        <x:v>Removed from Phase 5 by BA 2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="54" customHeight="1">
       <x:c r="A35" s="15" t="str">
-        <x:v>DEV-0501</x:v>
+        <x:v>DEV-0502</x:v>
       </x:c>
       <x:c r="B35" s="15" t="str">
         <x:v>Phase 5</x:v>
       </x:c>
       <x:c r="C35" s="15" t="str">
-        <x:v>Portfolio Items</x:v>
+        <x:v>Portfolio Integration</x:v>
       </x:c>
       <x:c r="D35" s="15" t="str">
-        <x:v>Implement production Portfolio Items from the closed Phase 5 handoff</x:v>
+        <x:v>Integrate Epic/Feature identity and leaf rollups with Work Item, Backlog, Iteration and Task flows</x:v>
       </x:c>
       <x:c r="E35" s="15" t="str">
-        <x:v>Future Phase 5 DEV handoff</x:v>
+        <x:v>Phase 5/PHASE5_DEV_HANDOFF.md</x:v>
       </x:c>
       <x:c r="F35" s="15" t="str">
-        <x:v>BA-0501 + Phase 5 close</x:v>
+        <x:v>DEV-0501</x:v>
       </x:c>
       <x:c r="G35" s="15" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H35" s="28" t="str">
-        <x:v>Needs BA</x:v>
+        <x:v>Ready</x:v>
       </x:c>
       <x:c r="I35" s="15" t="str">
         <x:v>FE DEV</x:v>
@@ -5429,18 +5328,18 @@
       <x:c r="J35" s="74"/>
       <x:c r="K35" s="74"/>
       <x:c r="L35" s="15" t="str">
-        <x:v>Project-scoped RBAC, Feature data, Archive and rollups pass DevInt</x:v>
+        <x:v>One shared record model drives every surface and cross-project links are rejected</x:v>
       </x:c>
       <x:c r="M35" s="15" t="str">
         <x:v>DevInt</x:v>
       </x:c>
       <x:c r="N35" s="15" t="str">
-        <x:v>Mockup implementation is not production authorization</x:v>
+        <x:v>Includes Feature field, Unscheduled Backlog behavior and shared Task hour rules</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="54" customHeight="1">
       <x:c r="A36" s="15" t="str">
-        <x:v>DEV-0502</x:v>
+        <x:v>DEV-0503</x:v>
       </x:c>
       <x:c r="B36" s="15" t="str">
         <x:v>Phase 5</x:v>
@@ -5449,19 +5348,19 @@
         <x:v>Capacity Planning</x:v>
       </x:c>
       <x:c r="D36" s="15" t="str">
-        <x:v>Implement single-Release Team capacity planning</x:v>
+        <x:v>Implement production single-Release Team capacity planning</x:v>
       </x:c>
       <x:c r="E36" s="15" t="str">
-        <x:v>Future Phase 5 DEV handoff</x:v>
+        <x:v>Phase 5/PHASE5_DEV_HANDOFF.md</x:v>
       </x:c>
       <x:c r="F36" s="15" t="str">
-        <x:v>DEV-0501 + BA-0502</x:v>
+        <x:v>DEV-0501 + Timebox Release registry</x:v>
       </x:c>
       <x:c r="G36" s="15" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H36" s="28" t="str">
-        <x:v>Needs BA</x:v>
+        <x:v>Ready</x:v>
       </x:c>
       <x:c r="I36" s="15" t="str">
         <x:v>FE DEV</x:v>
@@ -5469,58 +5368,58 @@
       <x:c r="J36" s="74"/>
       <x:c r="K36" s="74"/>
       <x:c r="L36" s="15" t="str">
-        <x:v>Plan list/detail, Team capacity, allocations, publish and RBAC pass DevInt</x:v>
+        <x:v>Plan lifecycle, Team capacity, split allocations, metrics, warnings and publish pass DevInt</x:v>
       </x:c>
       <x:c r="M36" s="15" t="str">
         <x:v>DevInt</x:v>
       </x:c>
       <x:c r="N36" s="15" t="str">
-        <x:v>Publish updates Feature Release/Team only; no child Story/Defect cascade</x:v>
+        <x:v>Publish may update Feature Release/planned dates only; never Project/Team or child Story/Defect</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="54" customHeight="1">
       <x:c r="A37" s="15" t="str">
-        <x:v>DEV-0503</x:v>
+        <x:v>DEV-0504</x:v>
       </x:c>
       <x:c r="B37" s="15" t="str">
         <x:v>Phase 5</x:v>
       </x:c>
       <x:c r="C37" s="15" t="str">
-        <x:v>Release Tracking</x:v>
+        <x:v>Authorization</x:v>
       </x:c>
       <x:c r="D37" s="15" t="str">
-        <x:v>Implement Release KPI and Feature progress tracking</x:v>
+        <x:v>Enforce Portfolio and Capacity Project/Team scope plus temporary planner Full/View server-side</x:v>
       </x:c>
       <x:c r="E37" s="15" t="str">
-        <x:v>Future Phase 5 DEV handoff</x:v>
+        <x:v>Phase 5/PHASE5_DEV_HANDOFF.md</x:v>
       </x:c>
       <x:c r="F37" s="15" t="str">
-        <x:v>DEV-0502 + BA-0503</x:v>
+        <x:v>DEV-0501 + DEV-0503 + Phase 4 RBAC</x:v>
       </x:c>
       <x:c r="G37" s="15" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H37" s="25" t="str">
-        <x:v>Needs BA</x:v>
+        <x:v>Ready</x:v>
       </x:c>
       <x:c r="I37" s="15" t="str">
-        <x:v>FE DEV</x:v>
+        <x:v>FE/BE DEV</x:v>
       </x:c>
       <x:c r="J37" s="74"/>
       <x:c r="K37" s="74"/>
       <x:c r="L37" s="15" t="str">
-        <x:v>Confirmed rollup, zero-state and manual Release lifecycle pass DevInt</x:v>
+        <x:v>Workspace Admin, managed/unmanaged Project Admin and Project Member negative paths pass</x:v>
       </x:c>
       <x:c r="M37" s="15" t="str">
-        <x:v>DevInt</x:v>
+        <x:v>Security/DevInt</x:v>
       </x:c>
       <x:c r="N37" s="15" t="str">
-        <x:v>No fabricated burnup history</x:v>
+        <x:v>Control visibility is not authorization evidence</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="54" customHeight="1">
       <x:c r="A38" s="57" t="str">
-        <x:v>DEV-0504</x:v>
+        <x:v>DEV-0505</x:v>
       </x:c>
       <x:c r="B38" s="57" t="str">
         <x:v>Phase 5</x:v>
@@ -5529,19 +5428,19 @@
         <x:v>Regression</x:v>
       </x:c>
       <x:c r="D38" s="57" t="str">
-        <x:v>Add Phase 5 FE/component/E2E and authorization coverage</x:v>
+        <x:v>Add Phase 5 service/component/E2E and authorization coverage</x:v>
       </x:c>
       <x:c r="E38" s="57" t="str">
-        <x:v>Phase 5 test scenarios + future DEV handoff</x:v>
+        <x:v>Phase 5 test scenarios + PHASE5_DEV_HANDOFF.md</x:v>
       </x:c>
       <x:c r="F38" s="57" t="str">
-        <x:v>DEV-0501..0503</x:v>
+        <x:v>DEV-0501..0504</x:v>
       </x:c>
       <x:c r="G38" s="57" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H38" s="59" t="str">
-        <x:v>Needs BA</x:v>
+        <x:v>Ready</x:v>
       </x:c>
       <x:c r="I38" s="57" t="str">
         <x:v>DEV/QA</x:v>
@@ -5549,12 +5448,14 @@
       <x:c r="J38" s="75"/>
       <x:c r="K38" s="75"/>
       <x:c r="L38" s="57" t="str">
-        <x:v>Portfolio critical path and role/project negative cases pass</x:v>
+        <x:v>Portfolio/Capacity critical, negative, publish and cross-module regression paths pass</x:v>
       </x:c>
       <x:c r="M38" s="57" t="str">
         <x:v>UAT sign-off</x:v>
       </x:c>
-      <x:c r="N38" s="57"/>
+      <x:c r="N38" s="57" t="str">
+        <x:v>Historical Not Run/Partial mockup cases are required production acceptance coverage</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="54" customHeight="1">
       <x:c r="A39" s="57" t="str">
@@ -5567,7 +5468,7 @@
         <x:v>Deferred UI</x:v>
       </x:c>
       <x:c r="D39" s="57" t="str">
-        <x:v>Do not build Team/Iteration boards, generic Reports, Theme/Initiative, Release Planning, burnup history or multi-Release scenarios until prioritized</x:v>
+        <x:v>Do not build Team/Iteration boards, Reports, Release Planning, Release Tracking, Theme/deeper hierarchy, burnup history or multi-Release scenarios until prioritized</x:v>
       </x:c>
       <x:c r="E39" s="57" t="str">
         <x:v>Future_Backlog</x:v>
@@ -6195,25 +6096,23 @@
           <x:t xml:space="preserve">D-015</x:t>
         </x:is>
       </x:c>
-      <x:c r="B19" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Release Navigation</x:t>
-        </x:is>
+      <x:c r="B19" s="15" t="str">
+        <x:v>Release Tracking</x:v>
       </x:c>
       <x:c r="C19" s="15" t="str">
-        <x:v>Promoted to Phase 5 P5.3 after Capacity Planning; use Plan Estimate progress, separate zero-estimate items, no automatic Release state and no burnup until trustworthy history exists</x:v>
+        <x:v>Dedicated Release Tracking is removed from closed Phase 5; future cross-release observation should be proposed under Reports</x:v>
       </x:c>
       <x:c r="D19" s="19" t="str">
         <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="E19" s="15" t="str">
-        <x:v>Phase 5</x:v>
+        <x:v>Future</x:v>
       </x:c>
       <x:c r="F19" s="15" t="str">
         <x:v>BA/PO</x:v>
       </x:c>
       <x:c r="G19" s="15" t="str">
-        <x:v>P5-GOV v2</x:v>
+        <x:v>P5-GOV v4 / BA decision 2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
@@ -6222,10 +6121,8 @@
           <x:t xml:space="preserve">D-016</x:t>
         </x:is>
       </x:c>
-      <x:c r="B20" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Release Tracking</x:t>
-        </x:is>
+      <x:c r="B20" s="15" t="str">
+        <x:v>Plan Dates</x:v>
       </x:c>
       <x:c r="C20" s="15" t="str">
         <x:v>Dates after 2026-07-26 in this workbook are proposed execution dates and may be re-baselined by BA/DEV leads</x:v>
@@ -6249,13 +6146,11 @@
           <x:t xml:space="preserve">D-017</x:t>
         </x:is>
       </x:c>
-      <x:c r="B21" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Plan Dates</x:t>
-        </x:is>
+      <x:c r="B21" s="15" t="str">
+        <x:v>Phase 5 Scope</x:v>
       </x:c>
       <x:c r="C21" s="15" t="str">
-        <x:v>Phase 5 active MVP is Portfolio Items, Capacity Planning and Release Tracking; Release Planning is Future Backlog</x:v>
+        <x:v>Closed Phase 5 MVP is Portfolio Items plus Capacity Planning; Release Planning/Tracking are excluded and Reports remain Future Backlog</x:v>
       </x:c>
       <x:c r="D21" s="19" t="str">
         <x:v>Confirmed</x:v>
@@ -6267,7 +6162,7 @@
         <x:v>BA/PO</x:v>
       </x:c>
       <x:c r="G21" s="15" t="str">
-        <x:v>P5-GOV v2</x:v>
+        <x:v>P5-GOV v4</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
@@ -6276,13 +6171,11 @@
           <x:t xml:space="preserve">D-018</x:t>
         </x:is>
       </x:c>
-      <x:c r="B22" s="57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Phase 5 Scope</x:t>
-        </x:is>
+      <x:c r="B22" s="57" t="str">
+        <x:v>Phase 5 Order</x:v>
       </x:c>
       <x:c r="C22" s="57" t="str">
-        <x:v>Execute P5.1 Portfolio Items -&gt; P5.2 Capacity Planning -&gt; P5.3 Release Tracking -&gt; P5.4 Phase closeout and DEV handoff</x:v>
+        <x:v>P5.1 Portfolio Items -&gt; P5.2 Capacity Planning -&gt; P5.3 scope removal -&gt; P5.4 phase closeout and DEV handoff</x:v>
       </x:c>
       <x:c r="D22" s="64" t="str">
         <x:v>Confirmed</x:v>
@@ -6294,7 +6187,7 @@
         <x:v>BA/DEV</x:v>
       </x:c>
       <x:c r="G22" s="57" t="str">
-        <x:v>P5-GOV v2</x:v>
+        <x:v>P5-GOV v4</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
@@ -6303,25 +6196,23 @@
           <x:t xml:space="preserve">D-019</x:t>
         </x:is>
       </x:c>
-      <x:c r="B23" s="57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Phase 5 Order</x:t>
-        </x:is>
+      <x:c r="B23" s="57" t="str">
+        <x:v>Phase 5 Readiness</x:v>
       </x:c>
       <x:c r="C23" s="57" t="str">
-        <x:v>P5.1 is BA accepted and closed for BA/mockup scope; production implementation waits for Phase 5 DEV handoff</x:v>
+        <x:v>P5.1 and P5.2 are BA accepted; production implementation may start from the dedicated Phase 5 DEV handoff</x:v>
       </x:c>
       <x:c r="D23" s="64" t="str">
         <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="E23" s="57" t="str">
-        <x:v>P5.1</x:v>
+        <x:v>Phase 5</x:v>
       </x:c>
       <x:c r="F23" s="57" t="str">
-        <x:v>BA</x:v>
+        <x:v>BA/DEV</x:v>
       </x:c>
       <x:c r="G23" s="57" t="str">
-        <x:v>P5.1 closure 2026-07-26</x:v>
+        <x:v>Phase 5 close 2026-07-28</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
@@ -6342,13 +6233,13 @@
         <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="E24" s="57" t="str">
-        <x:v>P5.1-P5.3</x:v>
+        <x:v>P5.1-P5.2</x:v>
       </x:c>
       <x:c r="F24" s="57" t="str">
         <x:v>BA/DEV</x:v>
       </x:c>
       <x:c r="G24" s="57" t="str">
-        <x:v>P5-GOV v2</x:v>
+        <x:v>P5-GOV v4</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
@@ -6384,10 +6275,8 @@
           <x:t xml:space="preserve">D-022</x:t>
         </x:is>
       </x:c>
-      <x:c r="B26" s="57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Feature Archive</x:t>
-        </x:is>
+      <x:c r="B26" s="57" t="str">
+        <x:v>Release Planning</x:v>
       </x:c>
       <x:c r="C26" s="57" t="str">
         <x:v>Release Planning is deferred; Capacity Planning publish is the active Feature Release/Team assignment mechanism for Phase 5</x:v>
@@ -6411,25 +6300,23 @@
           <x:t xml:space="preserve">D-023</x:t>
         </x:is>
       </x:c>
-      <x:c r="B27" s="57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Release Planning</x:t>
-        </x:is>
+      <x:c r="B27" s="57" t="str">
+        <x:v>Release Tracking</x:v>
       </x:c>
       <x:c r="C27" s="57" t="str">
-        <x:v>Use KPI + Feature list, Plan Estimate progress, separate zero-estimate items and no automatic Release transition</x:v>
+        <x:v>Historical selected-Release KPI/burnup proposals are superseded and do not authorize implementation</x:v>
       </x:c>
       <x:c r="D27" s="64" t="str">
-        <x:v>Confirmed</x:v>
+        <x:v>Superseded</x:v>
       </x:c>
       <x:c r="E27" s="57" t="str">
-        <x:v>P5.3</x:v>
+        <x:v>Future</x:v>
       </x:c>
       <x:c r="F27" s="57" t="str">
         <x:v>BA/DEV</x:v>
       </x:c>
       <x:c r="G27" s="57" t="str">
-        <x:v>P5-GOV v2</x:v>
+        <x:v>P5-GOV v4</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="54" customHeight="1">
@@ -6438,10 +6325,8 @@
           <x:t xml:space="preserve">D-024</x:t>
         </x:is>
       </x:c>
-      <x:c r="B28" s="57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Release Tracking</x:t>
-        </x:is>
+      <x:c r="B28" s="57" t="str">
+        <x:v>Capacity Planning</x:v>
       </x:c>
       <x:c r="C28" s="57" t="str">
         <x:v>Capacity Planning uses Team rows, manual capacity, Draft/Published lifecycle, Project+Release uniqueness, single-Team Feature allocation and Publish to master Feature</x:v>
@@ -6465,10 +6350,8 @@
           <x:t xml:space="preserve">D-025</x:t>
         </x:is>
       </x:c>
-      <x:c r="B29" s="57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Capacity Planning</x:t>
-        </x:is>
+      <x:c r="B29" s="57" t="str">
+        <x:v>Phase Gate</x:v>
       </x:c>
       <x:c r="C29" s="57" t="str">
         <x:v>Each feature requires proposal, BA confirmation, docs, implementation, verification and BA acceptance; create DEV handoff only after Phase 5 closes</x:v>
@@ -6483,7 +6366,7 @@
         <x:v>BA/DEV/QA</x:v>
       </x:c>
       <x:c r="G29" s="57" t="str">
-        <x:v>P5-GOV v2</x:v>
+        <x:v>P5-GOV v4</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="54" customHeight="1">
@@ -6492,35 +6375,23 @@
           <x:t xml:space="preserve">D-026</x:t>
         </x:is>
       </x:c>
-      <x:c r="B30" s="57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Phase Gate</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C30" s="57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Each feature requires proposal, BA confirmation, docs, implementation, verification and BA acceptance; create DEV handoff only after Phase 5 closes</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D30" s="64" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Confirmed</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E30" s="57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Phase 5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F30" s="57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BA/DEV/QA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G30" s="57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">P5-GOV v1</x:t>
-        </x:is>
+      <x:c r="B30" s="57" t="str">
+        <x:v>Phase Gate</x:v>
+      </x:c>
+      <x:c r="C30" s="57" t="str">
+        <x:v>Phase 5 is BA/mockup closed and has a dedicated DEV handoff; future rule changes still require proposal, confirmation, docs, implementation and acceptance</x:v>
+      </x:c>
+      <x:c r="D30" s="64" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="E30" s="57" t="str">
+        <x:v>Phase 5</x:v>
+      </x:c>
+      <x:c r="F30" s="57" t="str">
+        <x:v>BA/DEV/QA</x:v>
+      </x:c>
+      <x:c r="G30" s="57" t="str">
+        <x:v>PHASE5_DEV_HANDOFF.md</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="40.5" customHeight="1">

--- a/projects/mini-rally/04_Developement_tracking/Mini_Rally_Product_Plan.xlsx
+++ b/projects/mini-rally/04_Developement_tracking/Mini_Rally_Product_Plan.xlsx
@@ -2,11 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rc4d4e13c9aa94da6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Roadmap" sheetId="2" r:id="R8c9eb6e2538346b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BA Tasks" sheetId="3" r:id="R2a26c085553640bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEV Tasks" sheetId="4" r:id="R0447679099534b5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="5" r:id="R125ffe1788d448b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R11b00c37c4674640"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Roadmap" sheetId="2" r:id="R77c55a1bf1824334"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BA Tasks" sheetId="3" r:id="Ra2c2e57ec78649c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEV Tasks" sheetId="4" r:id="Ra7926415bcad4b25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Log" sheetId="5" r:id="R61db600075194c95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Future Backlog" sheetId="6" r:id="R314dd3ab2ae44254"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 6 Reports" sheetId="7" r:id="Re66d5c03b76045f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Tracking" sheetId="8" r:id="R118a70b0a9014e4a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="19">
+  <x:fonts count="35">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -130,8 +134,102 @@
       <x:color rgb="FF2F6B2F"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF7F6000"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF9C6500"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF667085"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF375623"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF243447"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="20"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos Display"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF33546F"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF33546F"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF2E7D32"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF375623"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF375623"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="16">
+  <x:fills count="45">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -208,8 +306,153 @@
         <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F6F9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF9C6500"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFDF5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFDF5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="11">
+  <x:borders count="19">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -291,11 +534,99 @@
         <x:color rgb="FFD0D7E2"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6B800"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE6B800"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6B800"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFE6B800"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6B800"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6B800"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE6B800"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6B800"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFA9D18E"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFA9D18E"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFA9D18E"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFA9D18E"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFA9D18E"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFA9D18E"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFA9D18E"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFA9D18E"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFAEB8C4"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFAEB8C4"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFAEB8C4"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFAEB8C4"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB8C2CC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB8C2CC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB8C2CC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB8C2CC"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="77">
+  <x:cellXfs count="240">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -479,10 +810,568 @@
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="19" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="19" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="19" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="20" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="20" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="20" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="20" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="20" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="20" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="20" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="20" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="20" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="25" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="19" fillId="25" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="19" fillId="25" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="19" fillId="25" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="26" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="29" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="29" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="32" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="33" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="33" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="33" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="34" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="38" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="39" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="31" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="41" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="33" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="33" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="43" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="43" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="43" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="43" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="15">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF60497A"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE4DFEC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1F4E78"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFA23B00"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1F4E78"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF667085"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF2F2F2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1F4E78"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1F4E78"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFDDEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF667085"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF2F2F2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
   <x:colors>
     <x:indexedColors>
       <x:rgbColor rgb="00000000"/>
@@ -552,6 +1441,25 @@
     </x:indexedColors>
   </x:colors>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FutureBacklogTable" displayName="FutureBacklogTable" ref="A8:J44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A8:J44"/>
+  <x:tableColumns count="10">
+    <x:tableColumn id="1" name="Backlog ID"/>
+    <x:tableColumn id="2" name="Origin"/>
+    <x:tableColumn id="3" name="Area"/>
+    <x:tableColumn id="4" name="Future Item / Decision"/>
+    <x:tableColumn id="5" name="Classification"/>
+    <x:tableColumn id="6" name="Current Status"/>
+    <x:tableColumn id="7" name="Business Direction / Decision Needed"/>
+    <x:tableColumn id="8" name="Dependency / Trigger"/>
+    <x:tableColumn id="9" name="Next BA Action"/>
+    <x:tableColumn id="10" name="Primary Source"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -770,7 +1678,7 @@
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Single planning workbook | Baseline: 2026-07-28 | Scope: BA, FE DEV, DevInt and UAT through closed Phase 5</x:v>
+        <x:v>Single planning workbook | Baseline: 2026-07-31 | Phase 5 closed | Phase 6 Reports and Portfolio &gt; Release Tracking BA/mockup approved; DEV implementation excluded</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
@@ -790,7 +1698,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="48" customHeight="1">
       <x:c r="A5" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Total</x:t>
@@ -798,7 +1706,7 @@
       </x:c>
       <x:c r="B5" s="15" t="n">
         <x:f>COUNTA('BA Tasks'!$A$5:$A$200)</x:f>
-        <x:v>30</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D5" s="15" t="inlineStr">
         <x:is>
@@ -814,18 +1722,20 @@
           <x:t xml:space="preserve">BA baseline</x:t>
         </x:is>
       </x:c>
-      <x:c r="H5" s="15" t="str">
-        <x:v>Phase 0-5 BA baseline aligned; Phase 5 DEV handoff ready</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+      <x:c r="H5" s="118" t="str">
+        <x:v>Phase 0-5 BA/mockup baseline closed; Phase 6 Reports and Release Tracking approved for DEV handoff</x:v>
+      </x:c>
+      <x:c r="I5" s="119"/>
+    </x:row>
+    <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Done</x:t>
         </x:is>
       </x:c>
       <x:c r="B6" s="15" t="n">
-        <x:v>23</x:v>
+        <x:f>COUNTIF('BA Tasks'!$H$5:$H$200,"Done")</x:f>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D6" s="15" t="inlineStr">
         <x:is>
@@ -841,17 +1751,19 @@
           <x:t xml:space="preserve">DEV current</x:t>
         </x:is>
       </x:c>
-      <x:c r="H6" s="15" t="str">
-        <x:v>Phase 0-4 DevInt active; Phase 5 production not started</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+      <x:c r="H6" s="118" t="str">
+        <x:v>Production implementation, persistence, history, authorization and automated tests remain DEV-owned</x:v>
+      </x:c>
+      <x:c r="I6" s="119"/>
+    </x:row>
+    <x:row r="7" ht="48" customHeight="1">
       <x:c r="A7" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Open</x:t>
         </x:is>
       </x:c>
       <x:c r="B7" s="15" t="n">
+        <x:f>B5-B6</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="15" t="inlineStr">
@@ -868,9 +1780,10 @@
           <x:t xml:space="preserve">Next gate</x:t>
         </x:is>
       </x:c>
-      <x:c r="H7" s="15" t="str">
-        <x:v>Start Phase 5 production analysis from dedicated DEV handoff</x:v>
-      </x:c>
+      <x:c r="H7" s="118" t="str">
+        <x:v>DEV may implement from the Phase 6 report contract and Release Tracking SRS</x:v>
+      </x:c>
+      <x:c r="I7" s="119"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="38" t="inlineStr">
@@ -882,10 +1795,10 @@
     <x:row r="10">
       <x:c r="A10" s="66" t="str">
         <x:v>1. BA owns business rules, SRS/mockup alignment and acceptance.
-2. Closed Phase 5 scope is Portfolio Items plus Capacity Planning.
-3. Release Planning and Release Tracking are excluded; Reports are Future Backlog only.
-4. BA/Mockup readiness, DEV handoff readiness and Production readiness remain separate.
-5. Future changes require propose -&gt; BA confirm -&gt; docs -&gt; implement -&gt; verify -&gt; accept.</x:v>
+2. Closed Phase 5 remains Portfolio Items plus Capacity Planning.
+3. Reports has exactly Iteration Burndown, Velocity and Team Capacity.
+4. Release Tracking is a separate Portfolio surface and the final Portfolio menu item.
+5. Dependencies is Future Backlog FB-P6-001; DEV owns production implementation and verification.</x:v>
       </x:c>
       <x:c r="B10" s="67" t="n"/>
       <x:c r="C10" s="67" t="n"/>
@@ -923,37 +1836,37 @@
     </x:row>
     <x:row r="16" ht="32" customHeight="1">
       <x:c r="A16" s="11" t="str">
-        <x:v>Phase 5 Closed</x:v>
+        <x:v>Phase 6 Closed</x:v>
       </x:c>
       <x:c r="B16" s="11" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>P5.0 Rebaseline</x:v>
+        <x:v>Report Contracts</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
-        <x:v>P5.1 Portfolio Items</x:v>
+        <x:v>Release Tracking SRS</x:v>
       </x:c>
       <x:c r="F16" s="11" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>P5.2 Capacity Planning</x:v>
+        <x:v>Mockup Approved</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="I16" s="11" t="str">
-        <x:v>P5.3 removed / P5.4 DEV Handoff</x:v>
+        <x:v>DEV Handoff</x:v>
       </x:c>
       <x:c r="J16" s="11" t="n"/>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
       <x:c r="A18" s="52" t="str">
-        <x:v>Sources of truth: RECONCILED_SOURCE_OF_TRUTH.md, Phase 5/PHASE5_DEV_HANDOFF.md, Phase 5 SRS/catalogs, PHASE5_DEVELOPMENT_TRACKING.md and 07_Test Business/specs. Phase 5 is BA/mockup closed; production implementation is not started.</x:v>
+        <x:v>Sources of truth: RECONCILED_SOURCE_OF_TRUTH.md; Phase 6/PHASE6_REPORTS_BUSINESS_AND_DATA_CONTRACT.md; Phase 6/01_Release_Tracking/SRS.md. BA/mockup readiness does not claim production readiness.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -966,6 +1879,9 @@
     <x:mergeCell ref="D4:E4"/>
     <x:mergeCell ref="A10:J14"/>
     <x:mergeCell ref="A2:J2"/>
+    <x:mergeCell ref="H5:I5"/>
+    <x:mergeCell ref="H6:I6"/>
+    <x:mergeCell ref="H7:I7"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -996,7 +1912,7 @@
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Product baseline 2026-07-28 | P5-GOV v4 closed; DEV dates remain an editable proposal</x:v>
+        <x:v>Product baseline 2026-07-31 | Phase 5 BA/mockup closed | Phase 6 Reports and Release Tracking BA/mockup approved</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
@@ -1315,46 +2231,91 @@
         <x:v>Start production analysis from Phase 5 DEV handoff</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="58" customHeight="1">
-      <x:c r="A11" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Future</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Deferred scope</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="15" t="str">
-        <x:v>Team/Iteration boards, Reports, Release Planning, Release Tracking, Theme/deeper hierarchy, burnup history and multi-Release scenarios</x:v>
-      </x:c>
-      <x:c r="D11" s="25" t="str">
+    <x:row r="11" ht="64" customHeight="1">
+      <x:c r="A11" s="76" t="str">
+        <x:v>Phase 6</x:v>
+      </x:c>
+      <x:c r="B11" s="76" t="str">
+        <x:v>Reporting &amp; release insight</x:v>
+      </x:c>
+      <x:c r="C11" s="76" t="str">
+        <x:v>Reports: Iteration Burndown, Velocity and Team Capacity; separate Portfolio &gt; Release Tracking</x:v>
+      </x:c>
+      <x:c r="D11" s="183" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E11" s="125" t="str">
+        <x:v>DEV Owned</x:v>
+      </x:c>
+      <x:c r="F11" s="76" t="str">
+        <x:v>DEV Handoff</x:v>
+      </x:c>
+      <x:c r="G11" s="126"/>
+      <x:c r="H11" s="126"/>
+      <x:c r="I11" s="76" t="str">
+        <x:v>Report contracts and Release Tracking SRS/mockup are aligned with no open BA decision</x:v>
+      </x:c>
+      <x:c r="J11" s="76" t="str">
+        <x:v>DEV implementation and production QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="64" customHeight="1">
+      <x:c r="A12" s="117" t="str">
+        <x:v>Future</x:v>
+      </x:c>
+      <x:c r="B12" s="117" t="str">
+        <x:v>Deferred scope</x:v>
+      </x:c>
+      <x:c r="C12" s="117" t="str">
+        <x:v>Team/Iteration boards, Release Planning, Theme/deeper hierarchy, Release dependency analysis and multi-Release planning scenarios</x:v>
+      </x:c>
+      <x:c r="D12" s="117" t="str">
         <x:v>Future Backlog</x:v>
       </x:c>
-      <x:c r="E11" s="25" t="str">
+      <x:c r="E12" s="117" t="str">
         <x:v>Future Backlog</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="str">
+      <x:c r="F12" s="117" t="str">
         <x:v>Backlog</x:v>
       </x:c>
-      <x:c r="G11" s="74"/>
-      <x:c r="H11" s="74"/>
-      <x:c r="I11" s="15" t="str">
+      <x:c r="G12" s="117"/>
+      <x:c r="H12" s="117"/>
+      <x:c r="I12" s="117" t="str">
         <x:v>Only promoted after BA/PO confirmation</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="str">
+      <x:c r="J12" s="117" t="str">
         <x:v>Quarterly product review</x:v>
       </x:c>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="130" t="str">
+        <x:v>Phase 6 is BA/mockup approved and DEV-handoff ready. Production data history, APIs, authorization, performance, tests and deployment remain DEV responsibilities.</x:v>
+      </x:c>
+      <x:c r="B14" s="130"/>
+      <x:c r="C14" s="130"/>
+      <x:c r="D14" s="130"/>
+      <x:c r="E14" s="130"/>
+      <x:c r="F14" s="130"/>
+      <x:c r="G14" s="130"/>
+      <x:c r="H14" s="130"/>
+      <x:c r="I14" s="130"/>
+      <x:c r="J14" s="130"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>
     <x:mergeCell ref="A2:J2"/>
+    <x:mergeCell ref="A14:J14"/>
   </x:mergeCells>
-  <x:dataValidations count="1">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="D5:E11">
       <x:formula1>"Done,In Progress,Ready,Planned,Future Backlog,Needs BA"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D5:D12">
+      <x:formula1>"Done,Ready,Draft Proposal,Decision Pending,Future Backlog"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E5:E12">
+      <x:formula1>"In Progress,Ready,DEV Owned,Future Backlog"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3109,7 +4070,7 @@
         <x:v>P2</x:v>
       </x:c>
       <x:c r="H30" s="22" t="str">
-        <x:v>Future Backlog</x:v>
+        <x:v>Promoted</x:v>
       </x:c>
       <x:c r="I30" s="15" t="str">
         <x:v>BA/PO</x:v>
@@ -3124,10 +4085,10 @@
         <x:v>No Release Tracking implementation is claimed; future observation may be proposed under Reports</x:v>
       </x:c>
       <x:c r="M30" s="15" t="str">
-        <x:v>Future Reports proposal</x:v>
+        <x:v>Phase 6 DEV handoff</x:v>
       </x:c>
       <x:c r="N30" s="15" t="str">
-        <x:v>Supersedes the prior P5.3 selected-Release screen proposal</x:v>
+        <x:v>Historical Phase 5 deferral; promoted and governed by current Phase 6 contracts</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="54" customHeight="1">
@@ -3197,7 +4158,7 @@
         <x:v>P2</x:v>
       </x:c>
       <x:c r="H32" s="25" t="str">
-        <x:v>Future Backlog</x:v>
+        <x:v>Promoted</x:v>
       </x:c>
       <x:c r="I32" s="15" t="str">
         <x:v>BA/PO</x:v>
@@ -3212,10 +4173,10 @@
         <x:v>Phase 5 close does not define or claim a Report feature</x:v>
       </x:c>
       <x:c r="M32" s="15" t="str">
-        <x:v>Future feature proposal</x:v>
+        <x:v>Phase 6 DEV handoff</x:v>
       </x:c>
       <x:c r="N32" s="15" t="str">
-        <x:v>Requires separate proposal, SRS, confirmation and delivery gates</x:v>
+        <x:v>Historical Phase 5 deferral; promoted and governed by current Phase 6 contracts</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="54" customHeight="1">
@@ -3300,6 +4261,326 @@
       </x:c>
       <x:c r="N34" s="57" t="str">
         <x:v>Confirmed future location: Settings &gt; Workspace &gt; Project Management</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="62" customHeight="1">
+      <x:c r="A35" s="112" t="str">
+        <x:v>BA-0600</x:v>
+      </x:c>
+      <x:c r="B35" s="76" t="str">
+        <x:v>Phase 6</x:v>
+      </x:c>
+      <x:c r="C35" s="76" t="str">
+        <x:v>Governance</x:v>
+      </x:c>
+      <x:c r="D35" s="76" t="str">
+        <x:v>Close Phase 6 Reports and Release Tracking business rules and publish the shared data contract</x:v>
+      </x:c>
+      <x:c r="E35" s="76" t="str">
+        <x:v>Phase 6 contracts + Decision Log</x:v>
+      </x:c>
+      <x:c r="F35" s="76" t="str">
+        <x:v>Confirmed report and Release Tracking decisions</x:v>
+      </x:c>
+      <x:c r="G35" s="76" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="H35" s="183" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="I35" s="76" t="str">
+        <x:v>Lead BA</x:v>
+      </x:c>
+      <x:c r="J35" s="76"/>
+      <x:c r="K35" s="76"/>
+      <x:c r="L35" s="76" t="str">
+        <x:v>All report and Release Tracking formulas, scope, units, historical behavior and drill-down rules are explicit</x:v>
+      </x:c>
+      <x:c r="M35" s="76" t="str">
+        <x:v>DEV handoff</x:v>
+      </x:c>
+      <x:c r="N35" s="76" t="str">
+        <x:v>No open BA decision; production implementation remains DEV-owned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="62" customHeight="1">
+      <x:c r="A36" s="112" t="str">
+        <x:v>BA-0601</x:v>
+      </x:c>
+      <x:c r="B36" s="76" t="str">
+        <x:v>Phase 6</x:v>
+      </x:c>
+      <x:c r="C36" s="76" t="str">
+        <x:v>Iteration Burndown</x:v>
+      </x:c>
+      <x:c r="D36" s="76" t="str">
+        <x:v>Define Iteration Burndown using end-of-day Task ToDo, cumulative Accepted Points and a fixed Task Estimate baseline</x:v>
+      </x:c>
+      <x:c r="E36" s="76" t="str">
+        <x:v>Phase 6/02_Iteration_Burndown/SRS.md + mockup</x:v>
+      </x:c>
+      <x:c r="F36" s="76" t="str">
+        <x:v>BA-0600; Iteration and Task rules</x:v>
+      </x:c>
+      <x:c r="G36" s="76" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="H36" s="185" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="I36" s="76" t="str">
+        <x:v>BA/UX</x:v>
+      </x:c>
+      <x:c r="J36" s="76"/>
+      <x:c r="K36" s="76"/>
+      <x:c r="L36" s="76" t="str">
+        <x:v>Daily snapshot, dual units, Ideal formula and unavailable-history state are explicit</x:v>
+      </x:c>
+      <x:c r="M36" s="76" t="str">
+        <x:v>DEV handoff</x:v>
+      </x:c>
+      <x:c r="N36" s="76" t="str">
+        <x:v>Production requires immutable daily snapshots and a start baseline</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="62" customHeight="1">
+      <x:c r="A37" s="112" t="str">
+        <x:v>BA-0602</x:v>
+      </x:c>
+      <x:c r="B37" s="76" t="str">
+        <x:v>Phase 6</x:v>
+      </x:c>
+      <x:c r="C37" s="76" t="str">
+        <x:v>Velocity</x:v>
+      </x:c>
+      <x:c r="D37" s="76" t="str">
+        <x:v>Define Velocity with Accepted During, Accepted After, Not Accepted, trend and Last/Best/Worst averages</x:v>
+      </x:c>
+      <x:c r="E37" s="76" t="str">
+        <x:v>Phase 6/03_Velocity_Chart/SRS.md + mockup</x:v>
+      </x:c>
+      <x:c r="F37" s="76" t="str">
+        <x:v>BA-0600; acceptedDate</x:v>
+      </x:c>
+      <x:c r="G37" s="76" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="H37" s="185" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="I37" s="76" t="str">
+        <x:v>BA/UX</x:v>
+      </x:c>
+      <x:c r="J37" s="76"/>
+      <x:c r="K37" s="76"/>
+      <x:c r="L37" s="76" t="str">
+        <x:v>Last 5/10, eligible Iterations and During-only calculations are explicit</x:v>
+      </x:c>
+      <x:c r="M37" s="76" t="str">
+        <x:v>DEV handoff</x:v>
+      </x:c>
+      <x:c r="N37" s="76" t="str">
+        <x:v>Velocity is recalculated from current assignment and acceptedDate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="62" customHeight="1">
+      <x:c r="A38" s="112" t="str">
+        <x:v>BA-0603</x:v>
+      </x:c>
+      <x:c r="B38" s="76" t="str">
+        <x:v>Phase 6</x:v>
+      </x:c>
+      <x:c r="C38" s="76" t="str">
+        <x:v>Release Tracking</x:v>
+      </x:c>
+      <x:c r="D38" s="76" t="str">
+        <x:v>Define Portfolio &gt; Release Tracking classification, list status, mismatch issues and Release Burnup</x:v>
+      </x:c>
+      <x:c r="E38" s="76" t="str">
+        <x:v>Phase 6/01_Release_Tracking/SRS.md + mockup</x:v>
+      </x:c>
+      <x:c r="F38" s="76" t="str">
+        <x:v>BA-0600; Portfolio and Release rules</x:v>
+      </x:c>
+      <x:c r="G38" s="76" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="H38" s="183" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="I38" s="76" t="str">
+        <x:v>BA/UX</x:v>
+      </x:c>
+      <x:c r="J38" s="76"/>
+      <x:c r="K38" s="76"/>
+      <x:c r="L38" s="76" t="str">
+        <x:v>Direct/Derived/Unparented, Points/Count, issue overlay and history dependency are explicit</x:v>
+      </x:c>
+      <x:c r="M38" s="76" t="str">
+        <x:v>DEV handoff</x:v>
+      </x:c>
+      <x:c r="N38" s="76" t="str">
+        <x:v>Dependencies remains Future Backlog FB-P6-001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="62" customHeight="1">
+      <x:c r="A39" s="112" t="str">
+        <x:v>BA-0604</x:v>
+      </x:c>
+      <x:c r="B39" s="76" t="str">
+        <x:v>Phase 6</x:v>
+      </x:c>
+      <x:c r="C39" s="76" t="str">
+        <x:v>Team Capacity</x:v>
+      </x:c>
+      <x:c r="D39" s="76" t="str">
+        <x:v>Define Team Capacity as a Team Status projection for Capacity, Estimate, ToDo and Actual hours</x:v>
+      </x:c>
+      <x:c r="E39" s="76" t="str">
+        <x:v>Phase 6/04_Team_Capacity/SRS.md + mockup</x:v>
+      </x:c>
+      <x:c r="F39" s="76" t="str">
+        <x:v>BA-0600; Team Status</x:v>
+      </x:c>
+      <x:c r="G39" s="76" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="H39" s="185" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="I39" s="76" t="str">
+        <x:v>BA/UX</x:v>
+      </x:c>
+      <x:c r="J39" s="76"/>
+      <x:c r="K39" s="76"/>
+      <x:c r="L39" s="76" t="str">
+        <x:v>Iteration picker, All Teams expansion and selected-Team rows are explicit</x:v>
+      </x:c>
+      <x:c r="M39" s="76" t="str">
+        <x:v>DEV handoff</x:v>
+      </x:c>
+      <x:c r="N39" s="76" t="str">
+        <x:v>No separate capacity store</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="62" customHeight="1">
+      <x:c r="A40" s="112" t="str">
+        <x:v>BA-0605</x:v>
+      </x:c>
+      <x:c r="B40" s="76" t="str">
+        <x:v>Phase 6</x:v>
+      </x:c>
+      <x:c r="C40" s="76" t="str">
+        <x:v>Navigation &amp; Shell</x:v>
+      </x:c>
+      <x:c r="D40" s="76" t="str">
+        <x:v>Align navigation and filters for three Reports types and separate Portfolio &gt; Release Tracking</x:v>
+      </x:c>
+      <x:c r="E40" s="76" t="str">
+        <x:v>Phase 6 UI contracts + mockup</x:v>
+      </x:c>
+      <x:c r="F40" s="76" t="str">
+        <x:v>BA-0601..0604</x:v>
+      </x:c>
+      <x:c r="G40" s="76" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="H40" s="219" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="I40" s="76" t="str">
+        <x:v>BA/UX</x:v>
+      </x:c>
+      <x:c r="J40" s="76"/>
+      <x:c r="K40" s="76"/>
+      <x:c r="L40" s="76" t="str">
+        <x:v>Release Tracking is the final Portfolio item and global scope drives every view</x:v>
+      </x:c>
+      <x:c r="M40" s="76" t="str">
+        <x:v>DEV handoff</x:v>
+      </x:c>
+      <x:c r="N40" s="76" t="str">
+        <x:v>No duplicate Project/Team filter</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="62" customHeight="1">
+      <x:c r="A41" s="112" t="str">
+        <x:v>BA-0606</x:v>
+      </x:c>
+      <x:c r="B41" s="76" t="str">
+        <x:v>Phase 6</x:v>
+      </x:c>
+      <x:c r="C41" s="76" t="str">
+        <x:v>Mockup &amp; UAT</x:v>
+      </x:c>
+      <x:c r="D41" s="76" t="str">
+        <x:v>Complete approved mockups and reconcile formulas, empty states, scope and warnings</x:v>
+      </x:c>
+      <x:c r="E41" s="76" t="str">
+        <x:v>Phase 6 mockup + SRS pack</x:v>
+      </x:c>
+      <x:c r="F41" s="76" t="str">
+        <x:v>BA-0605</x:v>
+      </x:c>
+      <x:c r="G41" s="76" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="H41" s="219" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="I41" s="76" t="str">
+        <x:v>BA/UX/UAT</x:v>
+      </x:c>
+      <x:c r="J41" s="76"/>
+      <x:c r="K41" s="76"/>
+      <x:c r="L41" s="76" t="str">
+        <x:v>Three Reports and Release Tracking match the approved business contract</x:v>
+      </x:c>
+      <x:c r="M41" s="76" t="str">
+        <x:v>DEV handoff</x:v>
+      </x:c>
+      <x:c r="N41" s="76" t="str">
+        <x:v>Playwright was waived by BA for mockup approval</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="62" customHeight="1">
+      <x:c r="A42" s="112" t="str">
+        <x:v>BA-0607</x:v>
+      </x:c>
+      <x:c r="B42" s="76" t="str">
+        <x:v>Phase 6</x:v>
+      </x:c>
+      <x:c r="C42" s="76" t="str">
+        <x:v>Closeout</x:v>
+      </x:c>
+      <x:c r="D42" s="76" t="str">
+        <x:v>Close Phase 6 BA/mockup package and transfer production delivery to DEV</x:v>
+      </x:c>
+      <x:c r="E42" s="76" t="str">
+        <x:v>Phase 6 contracts + Product Plan</x:v>
+      </x:c>
+      <x:c r="F42" s="76" t="str">
+        <x:v>BA-0606</x:v>
+      </x:c>
+      <x:c r="G42" s="76" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="H42" s="111" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="I42" s="76" t="str">
+        <x:v>Lead BA/UAT</x:v>
+      </x:c>
+      <x:c r="J42" s="76"/>
+      <x:c r="K42" s="76"/>
+      <x:c r="L42" s="76" t="str">
+        <x:v>No unresolved BA rule remains; readiness boundary is explicit</x:v>
+      </x:c>
+      <x:c r="M42" s="76" t="str">
+        <x:v>DEV handoff</x:v>
+      </x:c>
+      <x:c r="N42" s="76" t="str">
+        <x:v>BA/mockup approved; not production-ready</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3307,7 +4588,12 @@
     <x:mergeCell ref="A2:N2"/>
     <x:mergeCell ref="A1:N1"/>
   </x:mergeCells>
-  <x:dataValidations count="4">
+  <x:conditionalFormatting sqref="H35:H42">
+    <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Decision Pending"/>
+    <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Draft Proposal"/>
+    <x:cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="Planned"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="6">
     <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="G5:G32">
       <x:formula1>"P0,P1,P2,P3"</x:formula1>
     </x:dataValidation>
@@ -3319,6 +4605,12 @@
     </x:dataValidation>
     <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="H33:H34">
       <x:formula1>"Done,In Progress,Ready,Planned,Needs BA,Future Backlog"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G5:G42">
+      <x:formula1>"P0,P1,P2"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="H5:H42">
+      <x:formula1>"Done,In Progress,Ready,Future Backlog,Draft Proposal,Decision Pending,Planned"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5268,33 +6560,33 @@
         <x:v>Release Tracking</x:v>
       </x:c>
       <x:c r="D34" s="15" t="str">
-        <x:v>Do not implement a dedicated Release Tracking screen from historical Phase 5 stubs</x:v>
+        <x:v>Historical Phase 5 deferral; use the current Phase 6 Release Tracking SRS for any implementation</x:v>
       </x:c>
       <x:c r="E34" s="15" t="str">
-        <x:v>Future_Backlog</x:v>
+        <x:v>Phase 6/01_Release_Tracking/SRS.md</x:v>
       </x:c>
       <x:c r="F34" s="15" t="str">
-        <x:v>PO approval</x:v>
+        <x:v>Phase 6 DEV prioritization</x:v>
       </x:c>
       <x:c r="G34" s="15" t="str">
-        <x:v>P3</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="H34" s="34" t="str">
-        <x:v>Future Backlog</x:v>
+        <x:v>Superseded</x:v>
       </x:c>
       <x:c r="I34" s="15" t="str">
         <x:v>DEV</x:v>
       </x:c>
-      <x:c r="J34" s="74" t="n"/>
-      <x:c r="K34" s="74" t="n"/>
+      <x:c r="J34" s="74"/>
+      <x:c r="K34" s="74"/>
       <x:c r="L34" s="15" t="str">
-        <x:v>Future observation is proposed under Reports only after BA confirmation</x:v>
+        <x:v>No implementation should follow the obsolete Phase 5 exclusion wording</x:v>
       </x:c>
       <x:c r="M34" s="15" t="str">
-        <x:v>Future backlog review</x:v>
+        <x:v>Phase 6 DEV handoff</x:v>
       </x:c>
       <x:c r="N34" s="15" t="str">
-        <x:v>Removed from Phase 5 by BA 2026-07-28</x:v>
+        <x:v>Production scope is now defined; scheduling remains DEV-owned</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="54" customHeight="1">
@@ -5468,10 +6760,10 @@
         <x:v>Deferred UI</x:v>
       </x:c>
       <x:c r="D39" s="57" t="str">
-        <x:v>Do not build Team/Iteration boards, Reports, Release Planning, Release Tracking, Theme/deeper hierarchy, burnup history or multi-Release scenarios until prioritized</x:v>
+        <x:v>Keep only still-deferred UI out of active navigation: Team/Iteration boards, Release Planning, Theme/deeper hierarchy and other Future Backlog items</x:v>
       </x:c>
       <x:c r="E39" s="57" t="str">
-        <x:v>Future_Backlog</x:v>
+        <x:v>Future Backlog</x:v>
       </x:c>
       <x:c r="F39" s="57" t="str">
         <x:v>PO approval</x:v>
@@ -5488,12 +6780,14 @@
       <x:c r="J39" s="75"/>
       <x:c r="K39" s="75"/>
       <x:c r="L39" s="57" t="str">
-        <x:v>No hidden or partial implementation enters active navigation</x:v>
+        <x:v>No hidden or partial deferred feature enters active navigation</x:v>
       </x:c>
       <x:c r="M39" s="57" t="str">
         <x:v>Quarterly review</x:v>
       </x:c>
-      <x:c r="N39" s="57"/>
+      <x:c r="N39" s="57" t="str">
+        <x:v>Reports and Release Tracking were promoted to Phase 6 and are no longer covered by this deferral</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5539,10 +6833,8 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
-      <x:c r="A2" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Confirmed cross-phase rules and Phase 5 governance decisions that BA, DEV and QA must follow</x:t>
-        </x:is>
+      <x:c r="A2" s="6" t="str">
+        <x:v>Confirmed cross-phase rules plus Phase 6 Reports proposals and decisions that BA, UX and UAT must follow</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
@@ -6100,19 +7392,19 @@
         <x:v>Release Tracking</x:v>
       </x:c>
       <x:c r="C19" s="15" t="str">
-        <x:v>Dedicated Release Tracking is removed from closed Phase 5; future cross-release observation should be proposed under Reports</x:v>
+        <x:v>Dedicated Release Tracking was excluded from closed Phase 5 and later promoted as a separate Phase 6 Portfolio surface</x:v>
       </x:c>
       <x:c r="D19" s="19" t="str">
-        <x:v>Confirmed</x:v>
+        <x:v>Superseded</x:v>
       </x:c>
       <x:c r="E19" s="15" t="str">
-        <x:v>Future</x:v>
+        <x:v>Historical Phase 5 decision</x:v>
       </x:c>
       <x:c r="F19" s="15" t="str">
         <x:v>BA/PO</x:v>
       </x:c>
       <x:c r="G19" s="15" t="str">
-        <x:v>P5-GOV v4 / BA decision 2026-07-28</x:v>
+        <x:v>P5-GOV v4; superseded by Phase 6/01_Release_Tracking/SRS.md</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
@@ -6304,19 +7596,19 @@
         <x:v>Release Tracking</x:v>
       </x:c>
       <x:c r="C27" s="57" t="str">
-        <x:v>Historical selected-Release KPI/burnup proposals are superseded and do not authorize implementation</x:v>
+        <x:v>The older Release Tracking proposal was superseded during Phase 5, then redefined and approved under the Phase 6 SRS</x:v>
       </x:c>
       <x:c r="D27" s="64" t="str">
         <x:v>Superseded</x:v>
       </x:c>
       <x:c r="E27" s="57" t="str">
-        <x:v>Future</x:v>
+        <x:v>Historical</x:v>
       </x:c>
       <x:c r="F27" s="57" t="str">
         <x:v>BA/DEV</x:v>
       </x:c>
       <x:c r="G27" s="57" t="str">
-        <x:v>P5-GOV v4</x:v>
+        <x:v>P5-GOV v4; Phase 6/01_Release_Tracking/SRS.md</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="54" customHeight="1">
@@ -6503,6 +7795,190 @@
         <x:is>
           <x:t xml:space="preserve">P5.1 Amendment v3</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="48" customHeight="1">
+      <x:c r="A34" s="112" t="str">
+        <x:v>D-030</x:v>
+      </x:c>
+      <x:c r="B34" s="76" t="str">
+        <x:v>Phase 6 Scope</x:v>
+      </x:c>
+      <x:c r="C34" s="76" t="str">
+        <x:v>Reports contains exactly Iteration Burndown, Velocity and Team Capacity; Release Tracking is a separate Portfolio surface</x:v>
+      </x:c>
+      <x:c r="D34" s="221" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="E34" s="76" t="str">
+        <x:v>Phase 6</x:v>
+      </x:c>
+      <x:c r="F34" s="76" t="str">
+        <x:v>BA/PO</x:v>
+      </x:c>
+      <x:c r="G34" s="76" t="str">
+        <x:v>Phase 6 contracts; user approval 2026-07-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="48" customHeight="1">
+      <x:c r="A35" s="112" t="str">
+        <x:v>D-031</x:v>
+      </x:c>
+      <x:c r="B35" s="76" t="str">
+        <x:v>Iteration Burndown</x:v>
+      </x:c>
+      <x:c r="C35" s="76" t="str">
+        <x:v>Remaining ToDo uses end-of-day Task ToDo hours; Accepted Points are cumulative Accepted/Release Story/Defect points; Ideal uses Task Estimate captured at Iteration start</x:v>
+      </x:c>
+      <x:c r="D35" s="221" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="E35" s="76" t="str">
+        <x:v>P6 Reports</x:v>
+      </x:c>
+      <x:c r="F35" s="76" t="str">
+        <x:v>BA/PO</x:v>
+      </x:c>
+      <x:c r="G35" s="76" t="str">
+        <x:v>Phase 6/02_Iteration_Burndown/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="48" customHeight="1">
+      <x:c r="A36" s="112" t="str">
+        <x:v>D-032</x:v>
+      </x:c>
+      <x:c r="B36" s="76" t="str">
+        <x:v>Velocity</x:v>
+      </x:c>
+      <x:c r="C36" s="76" t="str">
+        <x:v>Each completed Iteration stacks Accepted During, Accepted After and Not Accepted; Trend/Last3/Best3/Worst3 use Accepted During only; window is 5 or 10</x:v>
+      </x:c>
+      <x:c r="D36" s="221" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="E36" s="76" t="str">
+        <x:v>P6 Reports</x:v>
+      </x:c>
+      <x:c r="F36" s="76" t="str">
+        <x:v>BA/PO</x:v>
+      </x:c>
+      <x:c r="G36" s="76" t="str">
+        <x:v>Phase 6/03_Velocity_Chart/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="48" customHeight="1">
+      <x:c r="A37" s="112" t="str">
+        <x:v>D-033</x:v>
+      </x:c>
+      <x:c r="B37" s="76" t="str">
+        <x:v>Team Capacity</x:v>
+      </x:c>
+      <x:c r="C37" s="76" t="str">
+        <x:v>Capacity, Estimate, ToDo and Actual are Team Status member-hours for one selected Iteration; All Teams expands Team to Member</x:v>
+      </x:c>
+      <x:c r="D37" s="221" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="E37" s="76" t="str">
+        <x:v>P6 Reports</x:v>
+      </x:c>
+      <x:c r="F37" s="76" t="str">
+        <x:v>BA/PO</x:v>
+      </x:c>
+      <x:c r="G37" s="76" t="str">
+        <x:v>Phase 6/04_Team_Capacity/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="48" customHeight="1">
+      <x:c r="A38" s="112" t="str">
+        <x:v>D-034</x:v>
+      </x:c>
+      <x:c r="B38" s="76" t="str">
+        <x:v>Release Tracking</x:v>
+      </x:c>
+      <x:c r="C38" s="76" t="str">
+        <x:v>Direct, Derived and Unparented use owning Release/parent fields plus current Project/Team scope; groups do not overlap</x:v>
+      </x:c>
+      <x:c r="D38" s="221" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="E38" s="76" t="str">
+        <x:v>P6 Release Tracking</x:v>
+      </x:c>
+      <x:c r="F38" s="76" t="str">
+        <x:v>BA/PO</x:v>
+      </x:c>
+      <x:c r="G38" s="76" t="str">
+        <x:v>Phase 6/01_Release_Tracking/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="48" customHeight="1">
+      <x:c r="A39" s="112" t="str">
+        <x:v>D-035</x:v>
+      </x:c>
+      <x:c r="B39" s="76" t="str">
+        <x:v>Release Tracking</x:v>
+      </x:c>
+      <x:c r="C39" s="76" t="str">
+        <x:v>Chart Unit is the sole Points/Count selector for list and Burnup; Direct status includes all children, Derived status includes matching Release/scope children</x:v>
+      </x:c>
+      <x:c r="D39" s="221" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="E39" s="76" t="str">
+        <x:v>P6 Release Tracking</x:v>
+      </x:c>
+      <x:c r="F39" s="76" t="str">
+        <x:v>BA/PO</x:v>
+      </x:c>
+      <x:c r="G39" s="76" t="str">
+        <x:v>Phase 6/01_Release_Tracking/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="48" customHeight="1">
+      <x:c r="A40" t="str">
+        <x:v>D-036</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Release Tracking</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>Unparented Story/Defect appears only for its own selected Release and current scope; numeric rank is sequential inside each active bucket</x:v>
+      </x:c>
+      <x:c r="D40" s="227" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>P6 Release Tracking</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>BA/PO</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>RT-Q-01 resolved; user confirmation 2026-07-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="48" customHeight="1">
+      <x:c r="A41" t="str">
+        <x:v>D-037</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>Release Tracking Issues</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Release mismatch is independent from percent done; issue popup groups mismatched children, compares against selected Release dates and warns when all assigned children mismatch</x:v>
+      </x:c>
+      <x:c r="D41" s="227" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>P6 Release Tracking</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>BA/PO</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>Phase 6/01_Release_Tracking/SRS.md</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6510,11 +7986,3469 @@
     <x:mergeCell ref="A2:G2"/>
     <x:mergeCell ref="A1:G1"/>
   </x:mergeCells>
-  <x:dataValidations count="1">
+  <x:conditionalFormatting sqref="D34:D39">
+    <x:cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="Confirmed"/>
+    <x:cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="Draft Proposal"/>
+    <x:cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="Decision Pending"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="2">
     <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="D22:D30">
       <x:formula1>"Confirmed,Deferred,Proposed"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D5:D39">
+      <x:formula1>"Confirmed,Superseded,Draft Proposal,Decision Pending"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="60" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="42" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="46" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="46" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="79" t="str">
+        <x:v>MINI RALLY — FUTURE BACKLOG</x:v>
+      </x:c>
+      <x:c r="B1" s="79"/>
+      <x:c r="C1" s="79"/>
+      <x:c r="D1" s="79"/>
+      <x:c r="E1" s="79"/>
+      <x:c r="F1" s="79"/>
+      <x:c r="G1" s="79"/>
+      <x:c r="H1" s="79"/>
+      <x:c r="I1" s="79"/>
+      <x:c r="J1" s="79"/>
+    </x:row>
+    <x:row r="2" ht="25" customHeight="1">
+      <x:c r="A2" s="82" t="str">
+        <x:v>BA/mockup scope only | Consolidated 2026-07-29 | Future features, deferred enhancements and unresolved product decisions; production DEV/API work is intentionally excluded</x:v>
+      </x:c>
+      <x:c r="B2" s="82"/>
+      <x:c r="C2" s="82"/>
+      <x:c r="D2" s="82"/>
+      <x:c r="E2" s="82"/>
+      <x:c r="F2" s="82"/>
+      <x:c r="G2" s="82"/>
+      <x:c r="H2" s="82"/>
+      <x:c r="I2" s="82"/>
+      <x:c r="J2" s="82"/>
+    </x:row>
+    <x:row r="4" ht="27" customHeight="1">
+      <x:c r="A4" s="87" t="str">
+        <x:v>Total Items</x:v>
+      </x:c>
+      <x:c r="B4" s="93" t="n">
+        <x:f>COUNTA(A9:A45)</x:f>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C4" s="87" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="D4" s="93" t="n">
+        <x:f>COUNTIF(F9:F45,"Future Backlog")</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E4" s="87" t="str">
+        <x:v>Decision Pending</x:v>
+      </x:c>
+      <x:c r="F4" s="93" t="n">
+        <x:f>COUNTIF(F9:F45,"Decision Pending")</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G4" s="87" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
+      <x:c r="H4" s="93" t="n">
+        <x:f>COUNTIF(F9:F45,"Deferred")</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I4" s="87" t="str">
+        <x:v>Conditional</x:v>
+      </x:c>
+      <x:c r="J4" s="93" t="n">
+        <x:f>COUNTIF(F9:F45,"Conditional")</x:f>
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="27" customHeight="1">
+      <x:c r="A5" s="135" t="str">
+        <x:v>Promoted / removed</x:v>
+      </x:c>
+      <x:c r="B5" s="141" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="31" customHeight="1">
+      <x:c r="A6" s="102" t="str">
+        <x:v>Promotion gate: add a backlog item to an active phase only after BA/PO confirms a new proposal, aligns the SRS/mockup and sets a separate acceptance gate. Existing accepted behavior remains authoritative until then.</x:v>
+      </x:c>
+      <x:c r="B6" s="103"/>
+      <x:c r="C6" s="103"/>
+      <x:c r="D6" s="103"/>
+      <x:c r="E6" s="103"/>
+      <x:c r="F6" s="103"/>
+      <x:c r="G6" s="103"/>
+      <x:c r="H6" s="103"/>
+      <x:c r="I6" s="103"/>
+      <x:c r="J6" s="104"/>
+    </x:row>
+    <x:row r="8" ht="31" customHeight="1">
+      <x:c r="A8" s="106" t="str">
+        <x:v>Backlog ID</x:v>
+      </x:c>
+      <x:c r="B8" s="106" t="str">
+        <x:v>Origin</x:v>
+      </x:c>
+      <x:c r="C8" s="106" t="str">
+        <x:v>Area</x:v>
+      </x:c>
+      <x:c r="D8" s="106" t="str">
+        <x:v>Future Item / Decision</x:v>
+      </x:c>
+      <x:c r="E8" s="106" t="str">
+        <x:v>Classification</x:v>
+      </x:c>
+      <x:c r="F8" s="106" t="str">
+        <x:v>Current Status</x:v>
+      </x:c>
+      <x:c r="G8" s="106" t="str">
+        <x:v>Business Direction / Decision Needed</x:v>
+      </x:c>
+      <x:c r="H8" s="106" t="str">
+        <x:v>Dependency / Trigger</x:v>
+      </x:c>
+      <x:c r="I8" s="106" t="str">
+        <x:v>Next BA Action</x:v>
+      </x:c>
+      <x:c r="J8" s="106" t="str">
+        <x:v>Primary Source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="58" customHeight="1">
+      <x:c r="A9" s="112" t="str">
+        <x:v>FB-P1-001</x:v>
+      </x:c>
+      <x:c r="B9" s="76" t="str">
+        <x:v>Phase 1</x:v>
+      </x:c>
+      <x:c r="C9" s="76" t="str">
+        <x:v>Time Tracking</x:v>
+      </x:c>
+      <x:c r="D9" s="76" t="str">
+        <x:v>Advanced time sheet and aggregation of Actual from time entries</x:v>
+      </x:c>
+      <x:c r="E9" s="76" t="str">
+        <x:v>Deferred Enhancement</x:v>
+      </x:c>
+      <x:c r="F9" s="111" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
+      <x:c r="G9" s="76" t="str">
+        <x:v>Current baseline keeps Actual as a manually entered field. A future slice may replace or reconcile it with detailed time entries.</x:v>
+      </x:c>
+      <x:c r="H9" s="76" t="str">
+        <x:v>Reopen only when a time-entry/timesheet problem statement is confirmed.</x:v>
+      </x:c>
+      <x:c r="I9" s="76" t="str">
+        <x:v>Define time-entry lifecycle, approval, corrections and how Actual is calculated.</x:v>
+      </x:c>
+      <x:c r="J9" s="76" t="str">
+        <x:v>Phase 1/PHASE1_DEVELOPMENT_TRACKING.md; Phase 1/05_Time_Tracking/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="112" t="str">
+        <x:v>FB-P1-002</x:v>
+      </x:c>
+      <x:c r="B10" s="76" t="str">
+        <x:v>Phase 1</x:v>
+      </x:c>
+      <x:c r="C10" s="76" t="str">
+        <x:v>Attachments</x:v>
+      </x:c>
+      <x:c r="D10" s="76" t="str">
+        <x:v>Attachment preview and versioning</x:v>
+      </x:c>
+      <x:c r="E10" s="76" t="str">
+        <x:v>Deferred Enhancement</x:v>
+      </x:c>
+      <x:c r="F10" s="111" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
+      <x:c r="G10" s="76" t="str">
+        <x:v>Current attachment scope is basic upload/list/download/delete. Preview and file version history were deliberately excluded.</x:v>
+      </x:c>
+      <x:c r="H10" s="76" t="str">
+        <x:v>Requires a separate content-management proposal.</x:v>
+      </x:c>
+      <x:c r="I10" s="76" t="str">
+        <x:v>Confirm supported preview types, version replacement rules, retention and permissions.</x:v>
+      </x:c>
+      <x:c r="J10" s="76" t="str">
+        <x:v>Phase 1/PHASE1_DEVELOPMENT_TRACKING.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="112" t="str">
+        <x:v>FB-P2-001</x:v>
+      </x:c>
+      <x:c r="B11" s="76" t="str">
+        <x:v>Phase 2</x:v>
+      </x:c>
+      <x:c r="C11" s="76" t="str">
+        <x:v>Iteration Status</x:v>
+      </x:c>
+      <x:c r="D11" s="76" t="str">
+        <x:v>Iteration Status Board view</x:v>
+      </x:c>
+      <x:c r="E11" s="76" t="str">
+        <x:v>Future Feature</x:v>
+      </x:c>
+      <x:c r="F11" s="111" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G11" s="76" t="str">
+        <x:v>Current accepted surface is List only. A future Board must reuse the same Work Item identities and shared statuses.</x:v>
+      </x:c>
+      <x:c r="H11" s="76" t="str">
+        <x:v>Needs decisions on columns, card fields, filters, rank, permissions, audit and accessibility.</x:v>
+      </x:c>
+      <x:c r="I11" s="76" t="str">
+        <x:v>Create a Board proposal and reconcile it with Backlog, Work Item Detail and Iteration Status List.</x:v>
+      </x:c>
+      <x:c r="J11" s="76" t="str">
+        <x:v>Future_Backlog/03_Iteration_Status_Board.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="58" customHeight="1">
+      <x:c r="A12" s="112" t="str">
+        <x:v>FB-P2-002</x:v>
+      </x:c>
+      <x:c r="B12" s="76" t="str">
+        <x:v>Phase 2</x:v>
+      </x:c>
+      <x:c r="C12" s="76" t="str">
+        <x:v>Iterations</x:v>
+      </x:c>
+      <x:c r="D12" s="76" t="str">
+        <x:v>Iteration date-overlap policy</x:v>
+      </x:c>
+      <x:c r="E12" s="76" t="str">
+        <x:v>Open Decision</x:v>
+      </x:c>
+      <x:c r="F12" s="111" t="str">
+        <x:v>Decision Pending</x:v>
+      </x:c>
+      <x:c r="G12" s="76" t="str">
+        <x:v>The accepted fallback is warn-only; it is not decided whether overlapping same-Team Iterations should ever be blocked.</x:v>
+      </x:c>
+      <x:c r="H12" s="76" t="str">
+        <x:v>Requires BA/PO decision before stricter validation is introduced.</x:v>
+      </x:c>
+      <x:c r="I12" s="76" t="str">
+        <x:v>Decide warn-only versus blocking, scope of overlap and exception behavior.</x:v>
+      </x:c>
+      <x:c r="J12" s="76" t="str">
+        <x:v>Phase 2/PHASE2_DEVELOPMENT_TRACKING.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="58" customHeight="1">
+      <x:c r="A13" s="112" t="str">
+        <x:v>FB-P2-003</x:v>
+      </x:c>
+      <x:c r="B13" s="76" t="str">
+        <x:v>Phase 2</x:v>
+      </x:c>
+      <x:c r="C13" s="76" t="str">
+        <x:v>Lists and Filters</x:v>
+      </x:c>
+      <x:c r="D13" s="76" t="str">
+        <x:v>Saved Views for Backlog, Iteration Status and Team Status</x:v>
+      </x:c>
+      <x:c r="E13" s="76" t="str">
+        <x:v>Deferred Enhancement</x:v>
+      </x:c>
+      <x:c r="F13" s="111" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
+      <x:c r="G13" s="76" t="str">
+        <x:v>Saved Views may be added after list/filter contracts are stable. No cross-screen saved-view behavior is currently defined.</x:v>
+      </x:c>
+      <x:c r="H13" s="76" t="str">
+        <x:v>Stable filter, sort and column-state contracts.</x:v>
+      </x:c>
+      <x:c r="I13" s="76" t="str">
+        <x:v>Define ownership, sharing, default view, rename/delete and permission rules.</x:v>
+      </x:c>
+      <x:c r="J13" s="76" t="str">
+        <x:v>Phase 2/PHASE2_DEVELOPMENT_TRACKING.md; Phase 3/PHASE3_DEVELOPMENT_TRACKING.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="58" customHeight="1">
+      <x:c r="A14" s="112" t="str">
+        <x:v>FB-P2-004</x:v>
+      </x:c>
+      <x:c r="B14" s="76" t="str">
+        <x:v>Phase 2</x:v>
+      </x:c>
+      <x:c r="C14" s="76" t="str">
+        <x:v>Iteration Lifecycle</x:v>
+      </x:c>
+      <x:c r="D14" s="76" t="str">
+        <x:v>Dedicated Close Iteration and carry-over workflow</x:v>
+      </x:c>
+      <x:c r="E14" s="76" t="str">
+        <x:v>Conditional Option</x:v>
+      </x:c>
+      <x:c r="F14" s="111" t="str">
+        <x:v>Conditional</x:v>
+      </x:c>
+      <x:c r="G14" s="76" t="str">
+        <x:v>Current baseline deliberately uses manual Iteration status and manual movement of unfinished Story/Defect items; no carry-over wizard is required.</x:v>
+      </x:c>
+      <x:c r="H14" s="76" t="str">
+        <x:v>Reopen only if manual movement becomes insufficient.</x:v>
+      </x:c>
+      <x:c r="I14" s="76" t="str">
+        <x:v>Confirm whether closing locks scope, which items move, and whether records are moved or copied.</x:v>
+      </x:c>
+      <x:c r="J14" s="76" t="str">
+        <x:v>Phase 2/PHASE2_DEVELOPMENT_TRACKING.md; Phase 2/03_Iteration_Status/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="58" customHeight="1">
+      <x:c r="A15" s="112" t="str">
+        <x:v>FB-P3-001</x:v>
+      </x:c>
+      <x:c r="B15" s="76" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="C15" s="76" t="str">
+        <x:v>Team Execution</x:v>
+      </x:c>
+      <x:c r="D15" s="76" t="str">
+        <x:v>Team Board</x:v>
+      </x:c>
+      <x:c r="E15" s="76" t="str">
+        <x:v>Future Feature</x:v>
+      </x:c>
+      <x:c r="F15" s="111" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G15" s="76" t="str">
+        <x:v>Optional Track &gt; Team Board using Iteration assignments and the shared Schedule State catalog. It must not create a second work-item store.</x:v>
+      </x:c>
+      <x:c r="H15" s="76" t="str">
+        <x:v>Depends on Iterations, Iteration Status and Team Status baselines.</x:v>
+      </x:c>
+      <x:c r="I15" s="76" t="str">
+        <x:v>Create a fresh BA proposal before adding navigation or mockup scope.</x:v>
+      </x:c>
+      <x:c r="J15" s="76" t="str">
+        <x:v>Future_Backlog/01_Team_Board.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="58" customHeight="1">
+      <x:c r="A16" s="112" t="str">
+        <x:v>FB-P3-002</x:v>
+      </x:c>
+      <x:c r="B16" s="76" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="C16" s="76" t="str">
+        <x:v>Team Board</x:v>
+      </x:c>
+      <x:c r="D16" s="76" t="str">
+        <x:v>Board card entity scope</x:v>
+      </x:c>
+      <x:c r="E16" s="76" t="str">
+        <x:v>Open Decision</x:v>
+      </x:c>
+      <x:c r="F16" s="111" t="str">
+        <x:v>Decision Pending</x:v>
+      </x:c>
+      <x:c r="G16" s="76" t="str">
+        <x:v>Not decided whether Team Board creates/shows only Story and Defect or also Task and Feature.</x:v>
+      </x:c>
+      <x:c r="H16" s="76" t="str">
+        <x:v>Depends on Team Board being re-prioritized.</x:v>
+      </x:c>
+      <x:c r="I16" s="76" t="str">
+        <x:v>Choose supported item types and define create/detail routing for each.</x:v>
+      </x:c>
+      <x:c r="J16" s="76" t="str">
+        <x:v>Future_Backlog/01_Team_Board.md (FB-TB-Q01)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="58" customHeight="1">
+      <x:c r="A17" s="112" t="str">
+        <x:v>FB-P3-003</x:v>
+      </x:c>
+      <x:c r="B17" s="76" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="C17" s="76" t="str">
+        <x:v>Board Behavior</x:v>
+      </x:c>
+      <x:c r="D17" s="76" t="str">
+        <x:v>Drag/drop state update behavior</x:v>
+      </x:c>
+      <x:c r="E17" s="76" t="str">
+        <x:v>Open Decision</x:v>
+      </x:c>
+      <x:c r="F17" s="111" t="str">
+        <x:v>Decision Pending</x:v>
+      </x:c>
+      <x:c r="G17" s="76" t="str">
+        <x:v>Not decided whether drag/drop immediately changes Schedule State and the mirrored Flow State.</x:v>
+      </x:c>
+      <x:c r="H17" s="76" t="str">
+        <x:v>Requires a confirmed board workflow and audit rules.</x:v>
+      </x:c>
+      <x:c r="I17" s="76" t="str">
+        <x:v>Define atomic status effects, failure rollback and cross-screen synchronization.</x:v>
+      </x:c>
+      <x:c r="J17" s="76" t="str">
+        <x:v>Future_Backlog/01_Team_Board.md (FB-TB-Q02); Future_Backlog/03_Iteration_Status_Board.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="58" customHeight="1">
+      <x:c r="A18" s="112" t="str">
+        <x:v>FB-P3-004</x:v>
+      </x:c>
+      <x:c r="B18" s="76" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="C18" s="76" t="str">
+        <x:v>Board Behavior</x:v>
+      </x:c>
+      <x:c r="D18" s="76" t="str">
+        <x:v>Allowed board transitions and validation</x:v>
+      </x:c>
+      <x:c r="E18" s="76" t="str">
+        <x:v>Open Decision</x:v>
+      </x:c>
+      <x:c r="F18" s="111" t="str">
+        <x:v>Decision Pending</x:v>
+      </x:c>
+      <x:c r="G18" s="76" t="str">
+        <x:v>The legal transition graph between workflow columns has not been defined.</x:v>
+      </x:c>
+      <x:c r="H18" s="76" t="str">
+        <x:v>Depends on Board columns and shared status mapping.</x:v>
+      </x:c>
+      <x:c r="I18" s="76" t="str">
+        <x:v>Confirm allowed forward/backward transitions, overrides and audit requirements.</x:v>
+      </x:c>
+      <x:c r="J18" s="76" t="str">
+        <x:v>Future_Backlog/01_Team_Board.md (FB-TB-Q03)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="58" customHeight="1">
+      <x:c r="A19" s="112" t="str">
+        <x:v>FB-P3-005</x:v>
+      </x:c>
+      <x:c r="B19" s="76" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="C19" s="76" t="str">
+        <x:v>Board Configuration</x:v>
+      </x:c>
+      <x:c r="D19" s="76" t="str">
+        <x:v>WIP limits</x:v>
+      </x:c>
+      <x:c r="E19" s="76" t="str">
+        <x:v>Open Decision</x:v>
+      </x:c>
+      <x:c r="F19" s="111" t="str">
+        <x:v>Decision Pending</x:v>
+      </x:c>
+      <x:c r="G19" s="76" t="str">
+        <x:v>WIP limits are outside the MVP. Requirement, scope and configuration location remain undecided.</x:v>
+      </x:c>
+      <x:c r="H19" s="76" t="str">
+        <x:v>Only relevant if a Board is promoted.</x:v>
+      </x:c>
+      <x:c r="I19" s="76" t="str">
+        <x:v>Decide whether limits are advisory or blocking and whether configured by Workspace, Project or Team.</x:v>
+      </x:c>
+      <x:c r="J19" s="76" t="str">
+        <x:v>Future_Backlog/01_Team_Board.md (FB-TB-Q04); Phase 3/PHASE3_DEVELOPMENT_TRACKING.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="58" customHeight="1">
+      <x:c r="A20" s="112" t="str">
+        <x:v>FB-P3-006</x:v>
+      </x:c>
+      <x:c r="B20" s="76" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="C20" s="76" t="str">
+        <x:v>Team Status</x:v>
+      </x:c>
+      <x:c r="D20" s="76" t="str">
+        <x:v>Team Status bulk actions and detailed permission model</x:v>
+      </x:c>
+      <x:c r="E20" s="76" t="str">
+        <x:v>Deferred Enhancement</x:v>
+      </x:c>
+      <x:c r="F20" s="111" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
+      <x:c r="G20" s="76" t="str">
+        <x:v>Bulk actions and a dedicated permission refinement were not included in the accepted Team Status slice.</x:v>
+      </x:c>
+      <x:c r="H20" s="76" t="str">
+        <x:v>Requires a separate BA confirmation after usage needs are known.</x:v>
+      </x:c>
+      <x:c r="I20" s="76" t="str">
+        <x:v>Identify real bulk-use cases, affected fields, selection rules and permission/audit impact.</x:v>
+      </x:c>
+      <x:c r="J20" s="76" t="str">
+        <x:v>Phase 3/PHASE3_DEVELOPMENT_TRACKING.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="58" customHeight="1">
+      <x:c r="A21" s="112" t="str">
+        <x:v>FB-P3-007</x:v>
+      </x:c>
+      <x:c r="B21" s="76" t="str">
+        <x:v>Phase 3</x:v>
+      </x:c>
+      <x:c r="C21" s="76" t="str">
+        <x:v>Quality / Defect</x:v>
+      </x:c>
+      <x:c r="D21" s="76" t="str">
+        <x:v>Reopen Defect from Closed or Closed Declined</x:v>
+      </x:c>
+      <x:c r="E21" s="76" t="str">
+        <x:v>Open Decision</x:v>
+      </x:c>
+      <x:c r="F21" s="111" t="str">
+        <x:v>Decision Pending</x:v>
+      </x:c>
+      <x:c r="G21" s="76" t="str">
+        <x:v>Reopen is deferred until BA confirms who may reopen and whether reason/audit fields are required.</x:v>
+      </x:c>
+      <x:c r="H21" s="76" t="str">
+        <x:v>Depends on permission and audit policy.</x:v>
+      </x:c>
+      <x:c r="I21" s="76" t="str">
+        <x:v>Decide authorized roles, target State, required reason and history presentation.</x:v>
+      </x:c>
+      <x:c r="J21" s="76" t="str">
+        <x:v>Phase 3/PHASE3_DEVELOPMENT_TRACKING.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="58" customHeight="1">
+      <x:c r="A22" s="112" t="str">
+        <x:v>FB-P4-001</x:v>
+      </x:c>
+      <x:c r="B22" s="76" t="str">
+        <x:v>Phase 4</x:v>
+      </x:c>
+      <x:c r="C22" s="76" t="str">
+        <x:v>Settings</x:v>
+      </x:c>
+      <x:c r="D22" s="76" t="str">
+        <x:v>Project-specific Workflow Status configuration</x:v>
+      </x:c>
+      <x:c r="E22" s="76" t="str">
+        <x:v>Deferred Configuration</x:v>
+      </x:c>
+      <x:c r="F22" s="111" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G22" s="76" t="str">
+        <x:v>All Projects currently use the approved default Agile statuses. A custom workflow designer/configuration is not yet defined.</x:v>
+      </x:c>
+      <x:c r="H22" s="76" t="str">
+        <x:v>Requires a new Project Settings design slice.</x:v>
+      </x:c>
+      <x:c r="I22" s="76" t="str">
+        <x:v>Define editable statuses, ordering, transition effects, migration and cross-screen behavior.</x:v>
+      </x:c>
+      <x:c r="J22" s="76" t="str">
+        <x:v>Phase 4/03_Settings_Audit/SRS.md; Phase 4/PHASE4_MOCKUP_CHECKLIST.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="58" customHeight="1">
+      <x:c r="A23" s="112" t="str">
+        <x:v>FB-P4-002</x:v>
+      </x:c>
+      <x:c r="B23" s="76" t="str">
+        <x:v>Phase 4</x:v>
+      </x:c>
+      <x:c r="C23" s="76" t="str">
+        <x:v>Settings</x:v>
+      </x:c>
+      <x:c r="D23" s="76" t="str">
+        <x:v>Labels management and work-item tagging</x:v>
+      </x:c>
+      <x:c r="E23" s="76" t="str">
+        <x:v>Deferred Configuration</x:v>
+      </x:c>
+      <x:c r="F23" s="111" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G23" s="76" t="str">
+        <x:v>Label creation, assignment, filtering and reporting were deferred because no end-to-end label workflow was confirmed.</x:v>
+      </x:c>
+      <x:c r="H23" s="76" t="str">
+        <x:v>Requires a complete label usage proposal.</x:v>
+      </x:c>
+      <x:c r="I23" s="76" t="str">
+        <x:v>Define label scope, uniqueness, colors, assignment, filters, permissions and reporting.</x:v>
+      </x:c>
+      <x:c r="J23" s="76" t="str">
+        <x:v>Phase 4/03_Settings_Audit/SRS.md; Phase 4/PHASE4_MOCKUP_CHECKLIST.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="58" customHeight="1">
+      <x:c r="A24" s="112" t="str">
+        <x:v>FB-P4-003</x:v>
+      </x:c>
+      <x:c r="B24" s="76" t="str">
+        <x:v>Phase 4</x:v>
+      </x:c>
+      <x:c r="C24" s="76" t="str">
+        <x:v>RBAC</x:v>
+      </x:c>
+      <x:c r="D24" s="76" t="str">
+        <x:v>External collaborator / Guest role</x:v>
+      </x:c>
+      <x:c r="E24" s="76" t="str">
+        <x:v>Conditional Option</x:v>
+      </x:c>
+      <x:c r="F24" s="111" t="str">
+        <x:v>Conditional</x:v>
+      </x:c>
+      <x:c r="G24" s="76" t="str">
+        <x:v>Guest was removed from the three-role MVP. External collaboration requires a separate scope decision.</x:v>
+      </x:c>
+      <x:c r="H24" s="76" t="str">
+        <x:v>Reopen only when an external-sharing use case is approved.</x:v>
+      </x:c>
+      <x:c r="I24" s="76" t="str">
+        <x:v>Define tenant visibility, invitation, expiration, allowed actions and audit behavior.</x:v>
+      </x:c>
+      <x:c r="J24" s="76" t="str">
+        <x:v>Phase 4/02_Roles_Permissions/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="58" customHeight="1">
+      <x:c r="A25" s="112" t="str">
+        <x:v>FB-P4-004</x:v>
+      </x:c>
+      <x:c r="B25" s="76" t="str">
+        <x:v>Phase 4</x:v>
+      </x:c>
+      <x:c r="C25" s="76" t="str">
+        <x:v>Audit</x:v>
+      </x:c>
+      <x:c r="D25" s="76" t="str">
+        <x:v>Project Admin project-level audit visibility</x:v>
+      </x:c>
+      <x:c r="E25" s="76" t="str">
+        <x:v>Deferred Enhancement</x:v>
+      </x:c>
+      <x:c r="F25" s="111" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
+      <x:c r="G25" s="76" t="str">
+        <x:v>Workspace-wide Audit is a Workspace Admin baseline; Project Admin project-level audit visibility was deferred.</x:v>
+      </x:c>
+      <x:c r="H25" s="76" t="str">
+        <x:v>Requires project-scoped audit requirements and privacy review.</x:v>
+      </x:c>
+      <x:c r="I25" s="76" t="str">
+        <x:v>Define visible event types, scope filters, retention and export permissions.</x:v>
+      </x:c>
+      <x:c r="J25" s="76" t="str">
+        <x:v>Phase 4/02_Roles_Permissions/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="58" customHeight="1">
+      <x:c r="A26" s="112" t="str">
+        <x:v>FB-P4-005</x:v>
+      </x:c>
+      <x:c r="B26" s="76" t="str">
+        <x:v>Phase 4</x:v>
+      </x:c>
+      <x:c r="C26" s="76" t="str">
+        <x:v>Home</x:v>
+      </x:c>
+      <x:c r="D26" s="76" t="str">
+        <x:v>Recent Activity scope</x:v>
+      </x:c>
+      <x:c r="E26" s="76" t="str">
+        <x:v>Open Decision</x:v>
+      </x:c>
+      <x:c r="F26" s="111" t="str">
+        <x:v>Decision Pending</x:v>
+      </x:c>
+      <x:c r="G26" s="76" t="str">
+        <x:v>It is still unclear whether Home Recent Activity is workspace-wide or user-scoped and whether it paginates.</x:v>
+      </x:c>
+      <x:c r="H26" s="76" t="str">
+        <x:v>Needs BA confirmation before the Home contract is extended.</x:v>
+      </x:c>
+      <x:c r="I26" s="76" t="str">
+        <x:v>Decide visibility scope, event inclusion, ordering, pagination and empty state.</x:v>
+      </x:c>
+      <x:c r="J26" s="76" t="str">
+        <x:v>08_Convert to figma/P7_Future_QA_and_Handoff/RELEASE_NOTES.md (Q-09)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="58" customHeight="1">
+      <x:c r="A27" s="112" t="str">
+        <x:v>FB-P4-006</x:v>
+      </x:c>
+      <x:c r="B27" s="76" t="str">
+        <x:v>Phase 4</x:v>
+      </x:c>
+      <x:c r="C27" s="76" t="str">
+        <x:v>Project Management</x:v>
+      </x:c>
+      <x:c r="D27" s="76" t="str">
+        <x:v>Project hard-delete policy</x:v>
+      </x:c>
+      <x:c r="E27" s="76" t="str">
+        <x:v>Open Decision</x:v>
+      </x:c>
+      <x:c r="F27" s="111" t="str">
+        <x:v>Decision Pending</x:v>
+      </x:c>
+      <x:c r="G27" s="76" t="str">
+        <x:v>Archive/Restore is the accepted baseline; permanent hard delete remains an unresolved optional policy.</x:v>
+      </x:c>
+      <x:c r="H27" s="76" t="str">
+        <x:v>Only reconsider if regulatory/data-retention needs require deletion.</x:v>
+      </x:c>
+      <x:c r="I27" s="76" t="str">
+        <x:v>Confirm whether hard delete exists, who can use it, dependency guards and recovery expectations.</x:v>
+      </x:c>
+      <x:c r="J27" s="76" t="str">
+        <x:v>08_Convert to figma/P7_Future_QA_and_Handoff/RELEASE_NOTES.md (Q-10); Phase 4/03_Settings_Audit/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="58" customHeight="1">
+      <x:c r="A28" s="112" t="str">
+        <x:v>FB-P4-007</x:v>
+      </x:c>
+      <x:c r="B28" s="76" t="str">
+        <x:v>Phase 4</x:v>
+      </x:c>
+      <x:c r="C28" s="76" t="str">
+        <x:v>Destructive Actions</x:v>
+      </x:c>
+      <x:c r="D28" s="76" t="str">
+        <x:v>Blocked-delete dependency UX</x:v>
+      </x:c>
+      <x:c r="E28" s="76" t="str">
+        <x:v>Open Decision</x:v>
+      </x:c>
+      <x:c r="F28" s="111" t="str">
+        <x:v>Decision Pending</x:v>
+      </x:c>
+      <x:c r="G28" s="76" t="str">
+        <x:v>A blocked delete must explain dependencies and preserve the record; the consolidated modal/detail presentation remains unspecified.</x:v>
+      </x:c>
+      <x:c r="H28" s="76" t="str">
+        <x:v>Depends on entity-specific dependency messages.</x:v>
+      </x:c>
+      <x:c r="I28" s="76" t="str">
+        <x:v>Define modal structure, dependency list/detail, next actions and accessibility behavior.</x:v>
+      </x:c>
+      <x:c r="J28" s="76" t="str">
+        <x:v>08_Convert to figma/P7_Future_QA_and_Handoff/RELEASE_NOTES.md (Q-02/Q-16); Phase 4/02_Roles_Permissions/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="58" customHeight="1">
+      <x:c r="A29" s="112" t="str">
+        <x:v>FB-P5-003</x:v>
+      </x:c>
+      <x:c r="B29" s="76" t="str">
+        <x:v>Phase 5</x:v>
+      </x:c>
+      <x:c r="C29" s="76" t="str">
+        <x:v>Portfolio Planning</x:v>
+      </x:c>
+      <x:c r="D29" s="76" t="str">
+        <x:v>Release Planning</x:v>
+      </x:c>
+      <x:c r="E29" s="76" t="str">
+        <x:v>Future Feature</x:v>
+      </x:c>
+      <x:c r="F29" s="143" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G29" s="76" t="str">
+        <x:v>Release Planning was removed from the closed Phase 5 MVP. Future scope may cover unassigned Feature backlog and assign/move/unassign across Releases without creating a second Release registry.</x:v>
+      </x:c>
+      <x:c r="H29" s="76" t="str">
+        <x:v>Requires a separate BA problem statement.</x:v>
+      </x:c>
+      <x:c r="I29" s="76" t="str">
+        <x:v>Validate that Capacity Planning does not already solve the target planning problem, then create a new SRS/mockup gate.</x:v>
+      </x:c>
+      <x:c r="J29" s="76" t="str">
+        <x:v>Future_Backlog/02_Release_Planning.md; Phase 5/PHASE5_DEV_HANDOFF.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="58" customHeight="1">
+      <x:c r="A30" s="112" t="str">
+        <x:v>FB-P5-005</x:v>
+      </x:c>
+      <x:c r="B30" s="76" t="str">
+        <x:v>Phase 5</x:v>
+      </x:c>
+      <x:c r="C30" s="76" t="str">
+        <x:v>Portfolio</x:v>
+      </x:c>
+      <x:c r="D30" s="76" t="str">
+        <x:v>Portfolio Overview</x:v>
+      </x:c>
+      <x:c r="E30" s="76" t="str">
+        <x:v>Future Feature</x:v>
+      </x:c>
+      <x:c r="F30" s="111" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G30" s="76" t="str">
+        <x:v>A broader portfolio overview remains deferred and is not part of the accepted Portfolio Items list/detail scope.</x:v>
+      </x:c>
+      <x:c r="H30" s="76" t="str">
+        <x:v>Requires a distinct leadership decision/use-case proposal.</x:v>
+      </x:c>
+      <x:c r="I30" s="76" t="str">
+        <x:v>Define portfolio-level questions, roll-ups, filters and relationship to Reports.</x:v>
+      </x:c>
+      <x:c r="J30" s="76" t="str">
+        <x:v>reconciliation/DEV_HANDOFF.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="58" customHeight="1">
+      <x:c r="A31" s="112" t="str">
+        <x:v>FB-P5-006</x:v>
+      </x:c>
+      <x:c r="B31" s="76" t="str">
+        <x:v>Phase 5</x:v>
+      </x:c>
+      <x:c r="C31" s="76" t="str">
+        <x:v>Portfolio Hierarchy</x:v>
+      </x:c>
+      <x:c r="D31" s="76" t="str">
+        <x:v>Theme and deeper custom Portfolio Item hierarchy</x:v>
+      </x:c>
+      <x:c r="E31" s="76" t="str">
+        <x:v>Future Capability</x:v>
+      </x:c>
+      <x:c r="F31" s="111" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G31" s="76" t="str">
+        <x:v>The accepted hierarchy stops at Epic -&gt; Feature. Theme and additional configurable levels remain outside scope.</x:v>
+      </x:c>
+      <x:c r="H31" s="76" t="str">
+        <x:v>Requires hierarchy governance and migration rules.</x:v>
+      </x:c>
+      <x:c r="I31" s="76" t="str">
+        <x:v>Define level naming, cardinality, templates, roll-ups, permissions and archive behavior.</x:v>
+      </x:c>
+      <x:c r="J31" s="76" t="str">
+        <x:v>Phase 5/PHASE5_DEV_HANDOFF.md; RECONCILED_SOURCE_OF_TRUTH.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="58" customHeight="1">
+      <x:c r="A32" s="112" t="str">
+        <x:v>FB-P5-007</x:v>
+      </x:c>
+      <x:c r="B32" s="76" t="str">
+        <x:v>Phase 5</x:v>
+      </x:c>
+      <x:c r="C32" s="76" t="str">
+        <x:v>Project Management</x:v>
+      </x:c>
+      <x:c r="D32" s="76" t="str">
+        <x:v>User-configurable Preliminary Estimate mapping</x:v>
+      </x:c>
+      <x:c r="E32" s="76" t="str">
+        <x:v>Deferred Configuration</x:v>
+      </x:c>
+      <x:c r="F32" s="213" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
+      <x:c r="G32" s="76" t="str">
+        <x:v>The current No Entry/XS/S/M/L/XL points/count mapping is temporary mock data. Confirmed future location is Settings &gt; Workspace &gt; Project Management.</x:v>
+      </x:c>
+      <x:c r="H32" s="76" t="str">
+        <x:v>Requires a dedicated configuration design slice.</x:v>
+      </x:c>
+      <x:c r="I32" s="76" t="str">
+        <x:v>Define editable scale values, defaults, validation, change impact and historical behavior.</x:v>
+      </x:c>
+      <x:c r="J32" s="76" t="str">
+        <x:v>Phase 5/PHASE5_DEV_HANDOFF.md; Phase 5/02_Capacity_Planning/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="58" customHeight="1">
+      <x:c r="A33" s="112" t="str">
+        <x:v>FB-P5-008</x:v>
+      </x:c>
+      <x:c r="B33" s="76" t="str">
+        <x:v>Phase 5</x:v>
+      </x:c>
+      <x:c r="C33" s="76" t="str">
+        <x:v>Portfolio / Capacity RBAC</x:v>
+      </x:c>
+      <x:c r="D33" s="76" t="str">
+        <x:v>Detailed action-level Portfolio and Capacity permissions</x:v>
+      </x:c>
+      <x:c r="E33" s="76" t="str">
+        <x:v>Deferred Configuration</x:v>
+      </x:c>
+      <x:c r="F33" s="111" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
+      <x:c r="G33" s="76" t="str">
+        <x:v>Current Capacity Planner permission is a temporary Full/View baseline; detailed action-level permissions are explicitly deferred.</x:v>
+      </x:c>
+      <x:c r="H33" s="76" t="str">
+        <x:v>Requires a separate RBAC refinement proposal.</x:v>
+      </x:c>
+      <x:c r="I33" s="76" t="str">
+        <x:v>Decide permission keys for create/edit/allocate/publish/revert/archive and role defaults.</x:v>
+      </x:c>
+      <x:c r="J33" s="76" t="str">
+        <x:v>Phase 5/PHASE5_DEV_HANDOFF.md; Phase 5/02_Capacity_Planning/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="58" customHeight="1">
+      <x:c r="A34" s="112" t="str">
+        <x:v>FB-P5-009</x:v>
+      </x:c>
+      <x:c r="B34" s="76" t="str">
+        <x:v>Phase 5</x:v>
+      </x:c>
+      <x:c r="C34" s="76" t="str">
+        <x:v>Capacity Planning</x:v>
+      </x:c>
+      <x:c r="D34" s="76" t="str">
+        <x:v>Multi-Release Capacity Plan</x:v>
+      </x:c>
+      <x:c r="E34" s="76" t="str">
+        <x:v>Future Capability</x:v>
+      </x:c>
+      <x:c r="F34" s="111" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G34" s="76" t="str">
+        <x:v>Current Capacity Plan supports exactly one existing Release.</x:v>
+      </x:c>
+      <x:c r="H34" s="76" t="str">
+        <x:v>Requires confirmed demand for planning across Releases.</x:v>
+      </x:c>
+      <x:c r="I34" s="76" t="str">
+        <x:v>Define release selection, allocation overlap, metrics and publish semantics.</x:v>
+      </x:c>
+      <x:c r="J34" s="76" t="str">
+        <x:v>Phase 5/PHASE5_DEV_HANDOFF.md; Phase 5/02_Capacity_Planning/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="58" customHeight="1">
+      <x:c r="A35" s="112" t="str">
+        <x:v>FB-P5-010</x:v>
+      </x:c>
+      <x:c r="B35" s="76" t="str">
+        <x:v>Phase 5</x:v>
+      </x:c>
+      <x:c r="C35" s="76" t="str">
+        <x:v>Capacity Planning</x:v>
+      </x:c>
+      <x:c r="D35" s="76" t="str">
+        <x:v>Plan of Plans</x:v>
+      </x:c>
+      <x:c r="E35" s="76" t="str">
+        <x:v>Future Capability</x:v>
+      </x:c>
+      <x:c r="F35" s="111" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G35" s="76" t="str">
+        <x:v>Portfolio-level aggregation across multiple Capacity Plans is not defined.</x:v>
+      </x:c>
+      <x:c r="H35" s="76" t="str">
+        <x:v>Depends on multi-plan governance and stable Plan metrics.</x:v>
+      </x:c>
+      <x:c r="I35" s="76" t="str">
+        <x:v>Define aggregation hierarchy, double-count prevention, access and drill-down.</x:v>
+      </x:c>
+      <x:c r="J35" s="76" t="str">
+        <x:v>Phase 5/PHASE5_DEV_HANDOFF.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="58" customHeight="1">
+      <x:c r="A36" s="112" t="str">
+        <x:v>FB-P5-011</x:v>
+      </x:c>
+      <x:c r="B36" s="76" t="str">
+        <x:v>Phase 5</x:v>
+      </x:c>
+      <x:c r="C36" s="76" t="str">
+        <x:v>Capacity Planning</x:v>
+      </x:c>
+      <x:c r="D36" s="76" t="str">
+        <x:v>Multiple what-if plans for the same Project and Release</x:v>
+      </x:c>
+      <x:c r="E36" s="76" t="str">
+        <x:v>Future Capability</x:v>
+      </x:c>
+      <x:c r="F36" s="111" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G36" s="76" t="str">
+        <x:v>Current rule allows only one Plan per Project + Release.</x:v>
+      </x:c>
+      <x:c r="H36" s="76" t="str">
+        <x:v>Requires scenario lifecycle and comparison rules.</x:v>
+      </x:c>
+      <x:c r="I36" s="76" t="str">
+        <x:v>Define scenario naming, active baseline, copy/compare, publish authority and cleanup.</x:v>
+      </x:c>
+      <x:c r="J36" s="76" t="str">
+        <x:v>Phase 5/PHASE5_DEV_HANDOFF.md; Phase 5/02_Capacity_Planning/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="58" customHeight="1">
+      <x:c r="A37" s="112" t="str">
+        <x:v>FB-P5-012</x:v>
+      </x:c>
+      <x:c r="B37" s="76" t="str">
+        <x:v>Phase 5</x:v>
+      </x:c>
+      <x:c r="C37" s="76" t="str">
+        <x:v>Capacity Planning</x:v>
+      </x:c>
+      <x:c r="D37" s="76" t="str">
+        <x:v>Automatic capacity rebalance</x:v>
+      </x:c>
+      <x:c r="E37" s="76" t="str">
+        <x:v>Future Capability</x:v>
+      </x:c>
+      <x:c r="F37" s="111" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G37" s="76" t="str">
+        <x:v>Current allocations and Team Capacity are manual; the system does not redistribute demand automatically.</x:v>
+      </x:c>
+      <x:c r="H37" s="76" t="str">
+        <x:v>Requires optimization objectives and override rules.</x:v>
+      </x:c>
+      <x:c r="I37" s="76" t="str">
+        <x:v>Define constraints, recommendation versus automatic action, explainability and undo.</x:v>
+      </x:c>
+      <x:c r="J37" s="76" t="str">
+        <x:v>Phase 5/PHASE5_DEV_HANDOFF.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="58" customHeight="1">
+      <x:c r="A38" s="112" t="str">
+        <x:v>FB-P5-013</x:v>
+      </x:c>
+      <x:c r="B38" s="76" t="str">
+        <x:v>Phase 5</x:v>
+      </x:c>
+      <x:c r="C38" s="76" t="str">
+        <x:v>Capacity Planning</x:v>
+      </x:c>
+      <x:c r="D38" s="76" t="str">
+        <x:v>Velocity-driven automatic capacity</x:v>
+      </x:c>
+      <x:c r="E38" s="76" t="str">
+        <x:v>Future Capability</x:v>
+      </x:c>
+      <x:c r="F38" s="111" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G38" s="76" t="str">
+        <x:v>Capacity Forecast is a Draft-only helper and never auto-updates capacity after apply.</x:v>
+      </x:c>
+      <x:c r="H38" s="76" t="str">
+        <x:v>Depends on trusted historical velocity and snapshot data.</x:v>
+      </x:c>
+      <x:c r="I38" s="76" t="str">
+        <x:v>Define velocity window, exclusions, confidence, manual override and refresh behavior.</x:v>
+      </x:c>
+      <x:c r="J38" s="76" t="str">
+        <x:v>Phase 5/PHASE5_DEV_HANDOFF.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="58" customHeight="1">
+      <x:c r="A39" s="112" t="str">
+        <x:v>FB-P5-014</x:v>
+      </x:c>
+      <x:c r="B39" s="76" t="str">
+        <x:v>Phase 5</x:v>
+      </x:c>
+      <x:c r="C39" s="76" t="str">
+        <x:v>Dependencies</x:v>
+      </x:c>
+      <x:c r="D39" s="76" t="str">
+        <x:v>Portfolio/Capacity dependency data and behavior</x:v>
+      </x:c>
+      <x:c r="E39" s="76" t="str">
+        <x:v>Future Capability</x:v>
+      </x:c>
+      <x:c r="F39" s="111" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G39" s="76" t="str">
+        <x:v>Dependencies columns currently show a placeholder only; no dependency contract or behavior is modelled.</x:v>
+      </x:c>
+      <x:c r="H39" s="76" t="str">
+        <x:v>Requires cross-item dependency rules.</x:v>
+      </x:c>
+      <x:c r="I39" s="76" t="str">
+        <x:v>Define dependency types, direction, validation, warnings, navigation and roll-up impact.</x:v>
+      </x:c>
+      <x:c r="J39" s="76" t="str">
+        <x:v>Phase 5/02_Capacity_Planning/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="58" customHeight="1">
+      <x:c r="A40" s="112" t="str">
+        <x:v>FB-P5-015</x:v>
+      </x:c>
+      <x:c r="B40" s="76" t="str">
+        <x:v>Phase 5</x:v>
+      </x:c>
+      <x:c r="C40" s="76" t="str">
+        <x:v>Capacity Analytics</x:v>
+      </x:c>
+      <x:c r="D40" s="76" t="str">
+        <x:v>Full Breakdown chart</x:v>
+      </x:c>
+      <x:c r="E40" s="76" t="str">
+        <x:v>Deferred Enhancement</x:v>
+      </x:c>
+      <x:c r="F40" s="111" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
+      <x:c r="G40" s="76" t="str">
+        <x:v>Only the compact read-only Breakdown overlay is included; a full Rally-style chart is outside scope.</x:v>
+      </x:c>
+      <x:c r="H40" s="76" t="str">
+        <x:v>Depends on confirmed analytical decisions and chart metrics.</x:v>
+      </x:c>
+      <x:c r="I40" s="76" t="str">
+        <x:v>Define chart questions, time dimension, grouping, interactions and empty states.</x:v>
+      </x:c>
+      <x:c r="J40" s="76" t="str">
+        <x:v>Phase 5/02_Capacity_Planning/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="58" customHeight="1">
+      <x:c r="A41" s="112" t="str">
+        <x:v>FB-P5-016</x:v>
+      </x:c>
+      <x:c r="B41" s="76" t="str">
+        <x:v>Phase 5</x:v>
+      </x:c>
+      <x:c r="C41" s="76" t="str">
+        <x:v>Capacity Plan Detail</x:v>
+      </x:c>
+      <x:c r="D41" s="76" t="str">
+        <x:v>Alignment, Progress and Revision History tabs</x:v>
+      </x:c>
+      <x:c r="E41" s="76" t="str">
+        <x:v>Future Feature</x:v>
+      </x:c>
+      <x:c r="F41" s="111" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G41" s="76" t="str">
+        <x:v>These tabs are not included in the accepted P5.2 detail surface.</x:v>
+      </x:c>
+      <x:c r="H41" s="76" t="str">
+        <x:v>Each tab requires its own problem statement and data contract.</x:v>
+      </x:c>
+      <x:c r="I41" s="76" t="str">
+        <x:v>Prioritize separately; define purpose, fields, permissions and relation to Reports/Audit.</x:v>
+      </x:c>
+      <x:c r="J41" s="76" t="str">
+        <x:v>Phase 5/02_Capacity_Planning/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="58" customHeight="1">
+      <x:c r="A42" s="112" t="str">
+        <x:v>FB-P6-001</x:v>
+      </x:c>
+      <x:c r="B42" s="76" t="str">
+        <x:v>Phase 6</x:v>
+      </x:c>
+      <x:c r="C42" s="76" t="str">
+        <x:v>Release Tracking</x:v>
+      </x:c>
+      <x:c r="D42" s="76" t="str">
+        <x:v>Release dependency analysis and cross-release risk view</x:v>
+      </x:c>
+      <x:c r="E42" s="76" t="str">
+        <x:v>Future Capability</x:v>
+      </x:c>
+      <x:c r="F42" s="111" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+      <x:c r="G42" s="76" t="str">
+        <x:v>Dependencies is not part of the approved Release Tracking slice.</x:v>
+      </x:c>
+      <x:c r="H42" s="76" t="str">
+        <x:v>Requires a dependency model, direction and cross-release risk semantics.</x:v>
+      </x:c>
+      <x:c r="I42" s="76" t="str">
+        <x:v>Define supported item types, direction, circular validation, severity, roll-up, permissions and navigation.</x:v>
+      </x:c>
+      <x:c r="J42" s="76" t="str">
+        <x:v>Phase 6/01_Release_Tracking/SRS.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="58" customHeight="1">
+      <x:c r="A43" s="112"/>
+      <x:c r="B43" s="76"/>
+      <x:c r="C43" s="76"/>
+      <x:c r="D43" s="76"/>
+      <x:c r="E43" s="76"/>
+      <x:c r="F43" s="111"/>
+      <x:c r="G43" s="76"/>
+      <x:c r="H43" s="76"/>
+      <x:c r="I43" s="76"/>
+      <x:c r="J43" s="76"/>
+    </x:row>
+    <x:row r="44" ht="58" customHeight="1">
+      <x:c r="A44" s="112"/>
+      <x:c r="B44" s="76"/>
+      <x:c r="C44" s="76"/>
+      <x:c r="D44" s="76"/>
+      <x:c r="E44" s="76"/>
+      <x:c r="F44" s="111"/>
+      <x:c r="G44" s="76"/>
+      <x:c r="H44" s="76"/>
+      <x:c r="I44" s="76"/>
+      <x:c r="J44" s="76"/>
+    </x:row>
+    <x:row r="46" ht="25" customHeight="1">
+      <x:c r="A46" s="116" t="str">
+        <x:v>Source precedence: RECONCILED_SOURCE_OF_TRUTH.md and current phase handoffs/SRS override historical stubs. Items marked Conditional are not planned work unless their stated trigger occurs.</x:v>
+      </x:c>
+      <x:c r="B46" s="116"/>
+      <x:c r="C46" s="116"/>
+      <x:c r="D46" s="116"/>
+      <x:c r="E46" s="116"/>
+      <x:c r="F46" s="116"/>
+      <x:c r="G46" s="116"/>
+      <x:c r="H46" s="116"/>
+      <x:c r="I46" s="116"/>
+      <x:c r="J46" s="116"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+    <x:mergeCell ref="A6:J6"/>
+    <x:mergeCell ref="A46:J46"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="F9:F44">
+    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Future Backlog"/>
+    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Decision Pending"/>
+    <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Deferred"/>
+    <x:cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Conditional"/>
+    <x:cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="Promoted to Phase 6"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="E9:E44">
+      <x:formula1>"Future Feature,Future Capability,Open Decision,Deferred Enhancement,Deferred Configuration,Conditional Option"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F9:F44">
+      <x:formula1>"Future Backlog,Decision Pending,Deferred,Conditional,Promoted to Phase 6"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb12394d898734640"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="146" t="str">
+        <x:v>MINI RALLY — PHASE 6 REPORTS</x:v>
+      </x:c>
+      <x:c r="B1" s="146"/>
+      <x:c r="C1" s="146"/>
+      <x:c r="D1" s="146"/>
+      <x:c r="E1" s="146"/>
+      <x:c r="F1" s="146"/>
+      <x:c r="G1" s="146"/>
+      <x:c r="H1" s="146"/>
+      <x:c r="I1" s="146"/>
+      <x:c r="J1" s="146"/>
+    </x:row>
+    <x:row r="2" ht="25" customHeight="1">
+      <x:c r="A2" s="149" t="str">
+        <x:v>BA/mockup approved 2026-07-31 | Exactly 3 report types | Release Tracking is a separate Portfolio surface | Production implementation is DEV-owned</x:v>
+      </x:c>
+      <x:c r="B2" s="149"/>
+      <x:c r="C2" s="149"/>
+      <x:c r="D2" s="149"/>
+      <x:c r="E2" s="149"/>
+      <x:c r="F2" s="149"/>
+      <x:c r="G2" s="149"/>
+      <x:c r="H2" s="149"/>
+      <x:c r="I2" s="149"/>
+      <x:c r="J2" s="149"/>
+    </x:row>
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="152" t="str">
+        <x:v>Phase Status</x:v>
+      </x:c>
+      <x:c r="B4" s="157" t="str">
+        <x:v>BA/Mockup Approved</x:v>
+      </x:c>
+      <x:c r="C4" s="152" t="str">
+        <x:v>Report Types</x:v>
+      </x:c>
+      <x:c r="D4" s="157" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E4" s="152" t="str">
+        <x:v>Product Surface</x:v>
+      </x:c>
+      <x:c r="F4" s="157" t="str">
+        <x:v>Reports</x:v>
+      </x:c>
+      <x:c r="G4" s="152" t="str">
+        <x:v>Open Decisions</x:v>
+      </x:c>
+      <x:c r="H4" s="157" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I4" s="152" t="str">
+        <x:v>Next Gate</x:v>
+      </x:c>
+      <x:c r="J4" s="157" t="str">
+        <x:v>DEV Handoff</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="32" customHeight="1">
+      <x:c r="A5" s="152" t="str">
+        <x:v>Scope</x:v>
+      </x:c>
+      <x:c r="B5" s="157" t="str">
+        <x:v>BA + Mockup</x:v>
+      </x:c>
+      <x:c r="C5" s="152" t="str">
+        <x:v>Historical Rule</x:v>
+      </x:c>
+      <x:c r="D5" s="157" t="str">
+        <x:v>Per-report contract</x:v>
+      </x:c>
+      <x:c r="E5" s="152" t="str">
+        <x:v>Units</x:v>
+      </x:c>
+      <x:c r="F5" s="157" t="str">
+        <x:v>Points + Hours</x:v>
+      </x:c>
+      <x:c r="G5" s="152" t="str">
+        <x:v>Playwright</x:v>
+      </x:c>
+      <x:c r="H5" s="157" t="str">
+        <x:v>Not required by BA</x:v>
+      </x:c>
+      <x:c r="I5" s="152" t="str">
+        <x:v>Production</x:v>
+      </x:c>
+      <x:c r="J5" s="157" t="str">
+        <x:v>DEV-owned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="25" customHeight="1">
+      <x:c r="A7" s="159" t="str">
+        <x:v>RECOMMENDED REPORT INFORMATION ARCHITECTURE</x:v>
+      </x:c>
+      <x:c r="B7" s="159"/>
+      <x:c r="C7" s="159"/>
+      <x:c r="D7" s="159"/>
+      <x:c r="E7" s="159"/>
+      <x:c r="F7" s="159"/>
+      <x:c r="G7" s="159"/>
+      <x:c r="H7" s="159"/>
+      <x:c r="I7" s="159"/>
+      <x:c r="J7" s="159"/>
+    </x:row>
+    <x:row r="8" ht="34" customHeight="1">
+      <x:c r="A8" s="162" t="str">
+        <x:v>Area</x:v>
+      </x:c>
+      <x:c r="B8" s="162" t="str">
+        <x:v>Report</x:v>
+      </x:c>
+      <x:c r="C8" s="162" t="str">
+        <x:v>Primary Context</x:v>
+      </x:c>
+      <x:c r="D8" s="162" t="str">
+        <x:v>Required Filters</x:v>
+      </x:c>
+      <x:c r="E8" s="162" t="str">
+        <x:v>Business Question</x:v>
+      </x:c>
+      <x:c r="F8" s="162" t="str">
+        <x:v>Recommended Visual</x:v>
+      </x:c>
+      <x:c r="G8" s="162" t="str">
+        <x:v>Key KPI</x:v>
+      </x:c>
+      <x:c r="H8" s="162" t="str">
+        <x:v>Default Drill-down</x:v>
+      </x:c>
+      <x:c r="I8" s="162" t="str">
+        <x:v>Data Readiness</x:v>
+      </x:c>
+      <x:c r="J8" s="162" t="str">
+        <x:v>BA Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="64" customHeight="1">
+      <x:c r="A9" s="76" t="str">
+        <x:v>Iteration Analytics</x:v>
+      </x:c>
+      <x:c r="B9" s="76" t="str">
+        <x:v>Iteration Burndown</x:v>
+      </x:c>
+      <x:c r="C9" s="76" t="str">
+        <x:v>One selected Iteration</x:v>
+      </x:c>
+      <x:c r="D9" s="76" t="str">
+        <x:v>Global Project/Team + Iteration picker</x:v>
+      </x:c>
+      <x:c r="E9" s="76" t="str">
+        <x:v>Is remaining Task ToDo reducing against the planning baseline?</x:v>
+      </x:c>
+      <x:c r="F9" s="76" t="str">
+        <x:v>ToDo hours bars + Accepted points bars + Ideal Task-hours line</x:v>
+      </x:c>
+      <x:c r="G9" s="76" t="str">
+        <x:v>Remaining ToDo / Accepted Points</x:v>
+      </x:c>
+      <x:c r="H9" s="76" t="str">
+        <x:v>Date snapshot</x:v>
+      </x:c>
+      <x:c r="I9" s="76" t="str">
+        <x:v>Daily snapshots + start baseline required</x:v>
+      </x:c>
+      <x:c r="J9" s="221" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="64" customHeight="1">
+      <x:c r="A10" s="76" t="str">
+        <x:v>Iteration Analytics</x:v>
+      </x:c>
+      <x:c r="B10" s="76" t="str">
+        <x:v>Velocity</x:v>
+      </x:c>
+      <x:c r="C10" s="76" t="str">
+        <x:v>Last 5 or 10 completed Iterations</x:v>
+      </x:c>
+      <x:c r="D10" s="76" t="str">
+        <x:v>Global Project/Team + window</x:v>
+      </x:c>
+      <x:c r="E10" s="76" t="str">
+        <x:v>How much work is accepted on time versus late?</x:v>
+      </x:c>
+      <x:c r="F10" s="76" t="str">
+        <x:v>Stacked During/After/Not Accepted + Trend</x:v>
+      </x:c>
+      <x:c r="G10" s="76" t="str">
+        <x:v>Accepted During and averages</x:v>
+      </x:c>
+      <x:c r="H10" s="76" t="str">
+        <x:v>Iteration work items</x:v>
+      </x:c>
+      <x:c r="I10" s="76" t="str">
+        <x:v>acceptedDate required</x:v>
+      </x:c>
+      <x:c r="J10" s="221" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="64" customHeight="1">
+      <x:c r="A11" s="76" t="str">
+        <x:v>Team Execution</x:v>
+      </x:c>
+      <x:c r="B11" s="76" t="str">
+        <x:v>Team Capacity</x:v>
+      </x:c>
+      <x:c r="C11" s="76" t="str">
+        <x:v>One selected Iteration</x:v>
+      </x:c>
+      <x:c r="D11" s="76" t="str">
+        <x:v>Global Project/Team + Iteration picker</x:v>
+      </x:c>
+      <x:c r="E11" s="76" t="str">
+        <x:v>What are Capacity, Estimate, ToDo and Actual hours?</x:v>
+      </x:c>
+      <x:c r="F11" s="76" t="str">
+        <x:v>Team Status-style expandable table</x:v>
+      </x:c>
+      <x:c r="G11" s="76" t="str">
+        <x:v>Capacity / Estimate / ToDo / Actual</x:v>
+      </x:c>
+      <x:c r="H11" s="76" t="str">
+        <x:v>Team -&gt; Member</x:v>
+      </x:c>
+      <x:c r="I11" s="76" t="str">
+        <x:v>Reuse Team Status source</x:v>
+      </x:c>
+      <x:c r="J11" s="221" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="64" customHeight="1">
+      <x:c r="A12" s="76" t="str">
+        <x:v>Separate Surface</x:v>
+      </x:c>
+      <x:c r="B12" s="76" t="str">
+        <x:v>Portfolio &gt; Release Tracking</x:v>
+      </x:c>
+      <x:c r="C12" s="76" t="str">
+        <x:v>One selected Release</x:v>
+      </x:c>
+      <x:c r="D12" s="76" t="str">
+        <x:v>Global Project/Team + Release</x:v>
+      </x:c>
+      <x:c r="E12" s="76" t="str">
+        <x:v>Track Direct, Derived and Unparented Release delivery</x:v>
+      </x:c>
+      <x:c r="F12" s="76" t="str">
+        <x:v>Feature list + Release Burnup</x:v>
+      </x:c>
+      <x:c r="G12" s="76" t="str">
+        <x:v>Points or Count</x:v>
+      </x:c>
+      <x:c r="H12" s="76" t="str">
+        <x:v>Feature / Work Item</x:v>
+      </x:c>
+      <x:c r="I12" s="76" t="str">
+        <x:v>Governed by Release Tracking SRS</x:v>
+      </x:c>
+      <x:c r="J12" s="221" t="str">
+        <x:v>Approved separately</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="33" customHeight="1">
+      <x:c r="A14" s="171" t="str">
+        <x:v>Confirmed navigation: Reports renders one selected Type from Iteration Burndown, Velocity or Team Capacity. Release Tracking is not a Reports type and stays under Portfolio.</x:v>
+      </x:c>
+      <x:c r="B14" s="172"/>
+      <x:c r="C14" s="172"/>
+      <x:c r="D14" s="172"/>
+      <x:c r="E14" s="172"/>
+      <x:c r="F14" s="172"/>
+      <x:c r="G14" s="172"/>
+      <x:c r="H14" s="172"/>
+      <x:c r="I14" s="172"/>
+      <x:c r="J14" s="173"/>
+    </x:row>
+    <x:row r="16" ht="25" customHeight="1">
+      <x:c r="A16" s="159" t="str">
+        <x:v>METRIC CONTRACTS AND RECOMMENDATIONS</x:v>
+      </x:c>
+      <x:c r="B16" s="159"/>
+      <x:c r="C16" s="159"/>
+      <x:c r="D16" s="159"/>
+      <x:c r="E16" s="159"/>
+      <x:c r="F16" s="159"/>
+      <x:c r="G16" s="159"/>
+      <x:c r="H16" s="159"/>
+      <x:c r="I16" s="159"/>
+      <x:c r="J16" s="159"/>
+    </x:row>
+    <x:row r="17" ht="34" customHeight="1">
+      <x:c r="A17" s="162" t="str">
+        <x:v>Report</x:v>
+      </x:c>
+      <x:c r="B17" s="162" t="str">
+        <x:v>Scope Rule</x:v>
+      </x:c>
+      <x:c r="C17" s="162" t="str">
+        <x:v>Numerator / Actual</x:v>
+      </x:c>
+      <x:c r="D17" s="162" t="str">
+        <x:v>Denominator / Baseline</x:v>
+      </x:c>
+      <x:c r="E17" s="162" t="str">
+        <x:v>Completion Rule</x:v>
+      </x:c>
+      <x:c r="F17" s="162" t="str">
+        <x:v>Special Handling</x:v>
+      </x:c>
+      <x:c r="G17" s="162" t="str">
+        <x:v>Recommended Display</x:v>
+      </x:c>
+      <x:c r="H17" s="162" t="str">
+        <x:v>Drill-down</x:v>
+      </x:c>
+      <x:c r="I17" s="162" t="str">
+        <x:v>Data Source</x:v>
+      </x:c>
+      <x:c r="J17" s="162" t="str">
+        <x:v>Assessment</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="76" customHeight="1">
+      <x:c r="A18" s="76" t="str">
+        <x:v>Iteration Burndown</x:v>
+      </x:c>
+      <x:c r="B18" s="76" t="str">
+        <x:v>Tasks under selected Iteration Story/Defect</x:v>
+      </x:c>
+      <x:c r="C18" s="76" t="str">
+        <x:v>Remaining ToDo = end-of-day SUM(Task.todo); Accepted Points = cumulative Accepted/Release Plan Estimate</x:v>
+      </x:c>
+      <x:c r="D18" s="76" t="str">
+        <x:v>Ideal = totalTaskEstimateAtStart</x:v>
+      </x:c>
+      <x:c r="E18" s="76" t="str">
+        <x:v>Snapshots are immutable</x:v>
+      </x:c>
+      <x:c r="F18" s="76" t="str">
+        <x:v>Workspace-local dates; no reconstructed past</x:v>
+      </x:c>
+      <x:c r="G18" s="76" t="str">
+        <x:v>Dual-axis daily chart</x:v>
+      </x:c>
+      <x:c r="H18" s="76" t="str">
+        <x:v>Daily snapshot</x:v>
+      </x:c>
+      <x:c r="I18" s="76" t="str">
+        <x:v>IterationDailySnapshot + Iteration baseline</x:v>
+      </x:c>
+      <x:c r="J18" s="76" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="76" customHeight="1">
+      <x:c r="A19" s="76" t="str">
+        <x:v>Velocity</x:v>
+      </x:c>
+      <x:c r="B19" s="76" t="str">
+        <x:v>Completed Iterations with scheduled work</x:v>
+      </x:c>
+      <x:c r="C19" s="76" t="str">
+        <x:v>Accepted During / Accepted After / Not Accepted</x:v>
+      </x:c>
+      <x:c r="D19" s="76" t="str">
+        <x:v>Trend = AVG Accepted During for up to last 10</x:v>
+      </x:c>
+      <x:c r="E19" s="76" t="str">
+        <x:v>Last3/Best3/Worst3 use During only</x:v>
+      </x:c>
+      <x:c r="F19" s="76" t="str">
+        <x:v>Current assignments recalculate chart; acceptedDate separates segments</x:v>
+      </x:c>
+      <x:c r="G19" s="76" t="str">
+        <x:v>Stacked bars + trend</x:v>
+      </x:c>
+      <x:c r="H19" s="76" t="str">
+        <x:v>Iteration items</x:v>
+      </x:c>
+      <x:c r="I19" s="76" t="str">
+        <x:v>Story/Defect planEstimate + acceptedDate</x:v>
+      </x:c>
+      <x:c r="J19" s="76" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="76" customHeight="1">
+      <x:c r="A20" s="76" t="str">
+        <x:v>Team Capacity</x:v>
+      </x:c>
+      <x:c r="B20" s="76" t="str">
+        <x:v>Selected Iteration and global Project/Team</x:v>
+      </x:c>
+      <x:c r="C20" s="76" t="str">
+        <x:v>SUM Capacity / Estimate / ToDo / Actual hours</x:v>
+      </x:c>
+      <x:c r="D20" s="76" t="str">
+        <x:v>Capacity from Team Status</x:v>
+      </x:c>
+      <x:c r="E20" s="76" t="str">
+        <x:v>No separate capacity store</x:v>
+      </x:c>
+      <x:c r="F20" s="76" t="str">
+        <x:v>All Teams expands Team to Member</x:v>
+      </x:c>
+      <x:c r="G20" s="76" t="str">
+        <x:v>Four columns + summary</x:v>
+      </x:c>
+      <x:c r="H20" s="76" t="str">
+        <x:v>Team/member rows</x:v>
+      </x:c>
+      <x:c r="I20" s="76" t="str">
+        <x:v>Team Status capacity + Tasks</x:v>
+      </x:c>
+      <x:c r="J20" s="76" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="76" customHeight="1">
+      <x:c r="A21" s="76" t="str">
+        <x:v>Release Tracking</x:v>
+      </x:c>
+      <x:c r="B21" s="76" t="str">
+        <x:v>Separate Portfolio SRS</x:v>
+      </x:c>
+      <x:c r="C21" s="76" t="str">
+        <x:v>See Direct/Derived/Unparented and Burnup formulas</x:v>
+      </x:c>
+      <x:c r="D21" s="76" t="str">
+        <x:v>Persisted historical baseline/events</x:v>
+      </x:c>
+      <x:c r="E21" s="76" t="str">
+        <x:v>Chart Unit Points/Count</x:v>
+      </x:c>
+      <x:c r="F21" s="76" t="str">
+        <x:v>Dependencies remains FB-P6-001</x:v>
+      </x:c>
+      <x:c r="G21" s="76" t="str">
+        <x:v>Feature list + Burnup</x:v>
+      </x:c>
+      <x:c r="H21" s="76" t="str">
+        <x:v>Feature/Work Item</x:v>
+      </x:c>
+      <x:c r="I21" s="76" t="str">
+        <x:v>Phase 6/01_Release_Tracking/SRS.md</x:v>
+      </x:c>
+      <x:c r="J21" s="76" t="str">
+        <x:v>Approved separately</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="25" customHeight="1">
+      <x:c r="A23" s="159" t="str">
+        <x:v>PHASE 6 BA / MOCKUP PLAN</x:v>
+      </x:c>
+      <x:c r="B23" s="159"/>
+      <x:c r="C23" s="159"/>
+      <x:c r="D23" s="159"/>
+      <x:c r="E23" s="159"/>
+      <x:c r="F23" s="159"/>
+      <x:c r="G23" s="159"/>
+      <x:c r="H23" s="159"/>
+      <x:c r="I23" s="159"/>
+      <x:c r="J23" s="159"/>
+    </x:row>
+    <x:row r="24" ht="34" customHeight="1">
+      <x:c r="A24" s="162" t="str">
+        <x:v>PHASE 6 BA / MOCKUP STATUS</x:v>
+      </x:c>
+      <x:c r="B24" s="162" t="str">
+        <x:v>Work Package</x:v>
+      </x:c>
+      <x:c r="C24" s="162" t="str">
+        <x:v>Primary Outcome</x:v>
+      </x:c>
+      <x:c r="D24" s="162" t="str">
+        <x:v>Owner</x:v>
+      </x:c>
+      <x:c r="E24" s="162" t="str">
+        <x:v>Dependency</x:v>
+      </x:c>
+      <x:c r="F24" s="162" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="G24" s="162" t="str">
+        <x:v>Exit Criteria</x:v>
+      </x:c>
+      <x:c r="H24" s="162" t="str">
+        <x:v>Mockup Output</x:v>
+      </x:c>
+      <x:c r="I24" s="162" t="str">
+        <x:v>UAT Focus</x:v>
+      </x:c>
+      <x:c r="J24" s="162" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="58" customHeight="1">
+      <x:c r="A25" s="76" t="str">
+        <x:v>P6.0</x:v>
+      </x:c>
+      <x:c r="B25" s="76" t="str">
+        <x:v>Scope &amp; Data Contract</x:v>
+      </x:c>
+      <x:c r="C25" s="76" t="str">
+        <x:v>Confirm report and Release Tracking vocabulary</x:v>
+      </x:c>
+      <x:c r="D25" s="76" t="str">
+        <x:v>BA/PO</x:v>
+      </x:c>
+      <x:c r="E25" s="76" t="str">
+        <x:v>Closed Phase 5</x:v>
+      </x:c>
+      <x:c r="F25" s="221" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="G25" s="76" t="str">
+        <x:v>No open BA decision</x:v>
+      </x:c>
+      <x:c r="H25" s="76" t="str">
+        <x:v>Contracts</x:v>
+      </x:c>
+      <x:c r="I25" s="76" t="str">
+        <x:v>Cross-screen consistency</x:v>
+      </x:c>
+      <x:c r="J25" s="76" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="58" customHeight="1">
+      <x:c r="A26" s="76" t="str">
+        <x:v>P6.1</x:v>
+      </x:c>
+      <x:c r="B26" s="76" t="str">
+        <x:v>Iteration Burndown</x:v>
+      </x:c>
+      <x:c r="C26" s="76" t="str">
+        <x:v>Daily ToDo, Accepted Points and fixed Ideal</x:v>
+      </x:c>
+      <x:c r="D26" s="76" t="str">
+        <x:v>BA/UX</x:v>
+      </x:c>
+      <x:c r="E26" s="76" t="str">
+        <x:v>P6.0</x:v>
+      </x:c>
+      <x:c r="F26" s="221" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="G26" s="76" t="str">
+        <x:v>Formula and snapshot behavior explicit</x:v>
+      </x:c>
+      <x:c r="H26" s="76" t="str">
+        <x:v>Mockup</x:v>
+      </x:c>
+      <x:c r="I26" s="76" t="str">
+        <x:v>Missing history</x:v>
+      </x:c>
+      <x:c r="J26" s="76" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="58" customHeight="1">
+      <x:c r="A27" s="76" t="str">
+        <x:v>P6.2</x:v>
+      </x:c>
+      <x:c r="B27" s="76" t="str">
+        <x:v>Velocity</x:v>
+      </x:c>
+      <x:c r="C27" s="76" t="str">
+        <x:v>During/After/Not Accepted with trend/averages</x:v>
+      </x:c>
+      <x:c r="D27" s="76" t="str">
+        <x:v>BA/UX</x:v>
+      </x:c>
+      <x:c r="E27" s="76" t="str">
+        <x:v>P6.0</x:v>
+      </x:c>
+      <x:c r="F27" s="221" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="G27" s="76" t="str">
+        <x:v>5/10 window and eligibility explicit</x:v>
+      </x:c>
+      <x:c r="H27" s="76" t="str">
+        <x:v>Mockup</x:v>
+      </x:c>
+      <x:c r="I27" s="76" t="str">
+        <x:v>Late acceptance</x:v>
+      </x:c>
+      <x:c r="J27" s="76" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="58" customHeight="1">
+      <x:c r="A28" s="76" t="str">
+        <x:v>P6.3</x:v>
+      </x:c>
+      <x:c r="B28" s="76" t="str">
+        <x:v>Team Capacity</x:v>
+      </x:c>
+      <x:c r="C28" s="76" t="str">
+        <x:v>Team Status capacity-hour projection</x:v>
+      </x:c>
+      <x:c r="D28" s="76" t="str">
+        <x:v>BA/UX</x:v>
+      </x:c>
+      <x:c r="E28" s="76" t="str">
+        <x:v>P6.0</x:v>
+      </x:c>
+      <x:c r="F28" s="221" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="G28" s="76" t="str">
+        <x:v>All Teams and selected Team explicit</x:v>
+      </x:c>
+      <x:c r="H28" s="76" t="str">
+        <x:v>Mockup</x:v>
+      </x:c>
+      <x:c r="I28" s="76" t="str">
+        <x:v>Team/member expansion</x:v>
+      </x:c>
+      <x:c r="J28" s="76" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="58" customHeight="1">
+      <x:c r="A29" s="76" t="str">
+        <x:v>P6.4</x:v>
+      </x:c>
+      <x:c r="B29" s="76" t="str">
+        <x:v>Release Tracking</x:v>
+      </x:c>
+      <x:c r="C29" s="76" t="str">
+        <x:v>Dedicated Portfolio Release Tracking</x:v>
+      </x:c>
+      <x:c r="D29" s="76" t="str">
+        <x:v>BA/UX</x:v>
+      </x:c>
+      <x:c r="E29" s="76" t="str">
+        <x:v>P6.0</x:v>
+      </x:c>
+      <x:c r="F29" s="221" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="G29" s="76" t="str">
+        <x:v>Classification, status, issues and Burnup explicit</x:v>
+      </x:c>
+      <x:c r="H29" s="76" t="str">
+        <x:v>Mockup</x:v>
+      </x:c>
+      <x:c r="I29" s="76" t="str">
+        <x:v>Mismatch and scope</x:v>
+      </x:c>
+      <x:c r="J29" s="76" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="58" customHeight="1">
+      <x:c r="A30" s="76" t="str">
+        <x:v>P6.5</x:v>
+      </x:c>
+      <x:c r="B30" s="76" t="str">
+        <x:v>Navigation &amp; Shell</x:v>
+      </x:c>
+      <x:c r="C30" s="76" t="str">
+        <x:v>Three Reports types; Release Tracking final Portfolio item</x:v>
+      </x:c>
+      <x:c r="D30" s="76" t="str">
+        <x:v>BA/UX</x:v>
+      </x:c>
+      <x:c r="E30" s="76" t="str">
+        <x:v>P6.1..P6.4</x:v>
+      </x:c>
+      <x:c r="F30" s="221" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="G30" s="76" t="str">
+        <x:v>Navigation and filters aligned</x:v>
+      </x:c>
+      <x:c r="H30" s="76" t="str">
+        <x:v>Mockup</x:v>
+      </x:c>
+      <x:c r="I30" s="76" t="str">
+        <x:v>Context switching</x:v>
+      </x:c>
+      <x:c r="J30" s="76" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="58" customHeight="1">
+      <x:c r="A31" s="76" t="str">
+        <x:v>P6.6</x:v>
+      </x:c>
+      <x:c r="B31" s="76" t="str">
+        <x:v>Documentation</x:v>
+      </x:c>
+      <x:c r="C31" s="76" t="str">
+        <x:v>Reconcile SRS, source of truth and Product Plan</x:v>
+      </x:c>
+      <x:c r="D31" s="76" t="str">
+        <x:v>Lead BA</x:v>
+      </x:c>
+      <x:c r="E31" s="76" t="str">
+        <x:v>P6.5</x:v>
+      </x:c>
+      <x:c r="F31" s="221" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="G31" s="76" t="str">
+        <x:v>No contradictory active rule</x:v>
+      </x:c>
+      <x:c r="H31" s="76" t="str">
+        <x:v>Handoff pack</x:v>
+      </x:c>
+      <x:c r="I31" s="76" t="str">
+        <x:v>Formula traceability</x:v>
+      </x:c>
+      <x:c r="J31" s="76" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="58" customHeight="1">
+      <x:c r="A32" s="76" t="str">
+        <x:v>P6.7</x:v>
+      </x:c>
+      <x:c r="B32" s="76" t="str">
+        <x:v>DEV Handoff</x:v>
+      </x:c>
+      <x:c r="C32" s="76" t="str">
+        <x:v>Transfer production implementation and QA</x:v>
+      </x:c>
+      <x:c r="D32" s="76" t="str">
+        <x:v>DEV/QA</x:v>
+      </x:c>
+      <x:c r="E32" s="76" t="str">
+        <x:v>P6.6</x:v>
+      </x:c>
+      <x:c r="F32" s="231" t="str">
+        <x:v>Ready</x:v>
+      </x:c>
+      <x:c r="G32" s="76" t="str">
+        <x:v>BA/mockup package accepted</x:v>
+      </x:c>
+      <x:c r="H32" s="76" t="str">
+        <x:v>Production build</x:v>
+      </x:c>
+      <x:c r="I32" s="76" t="str">
+        <x:v>Automated and deployment tests</x:v>
+      </x:c>
+      <x:c r="J32" s="76" t="str">
+        <x:v>DEV-owned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="25" customHeight="1">
+      <x:c r="A34" s="176" t="str">
+        <x:v>PHASE 6 DECISIONS — ALL BA DECISIONS CONFIRMED</x:v>
+      </x:c>
+      <x:c r="B34" s="176"/>
+      <x:c r="C34" s="176"/>
+      <x:c r="D34" s="176"/>
+      <x:c r="E34" s="176"/>
+      <x:c r="F34" s="176"/>
+      <x:c r="G34" s="176"/>
+      <x:c r="H34" s="176"/>
+      <x:c r="I34" s="176"/>
+      <x:c r="J34" s="176"/>
+    </x:row>
+    <x:row r="35" ht="35" customHeight="1">
+      <x:c r="A35" s="179" t="str">
+        <x:v>Question ID</x:v>
+      </x:c>
+      <x:c r="B35" s="179" t="str">
+        <x:v>Report</x:v>
+      </x:c>
+      <x:c r="C35" s="179" t="str">
+        <x:v>Decision Needed</x:v>
+      </x:c>
+      <x:c r="D35" s="179" t="str">
+        <x:v>Recommended Default</x:v>
+      </x:c>
+      <x:c r="E35" s="179" t="str">
+        <x:v>Reason</x:v>
+      </x:c>
+      <x:c r="F35" s="179" t="str">
+        <x:v>Alternative</x:v>
+      </x:c>
+      <x:c r="G35" s="179" t="str">
+        <x:v>Impact if Unresolved</x:v>
+      </x:c>
+      <x:c r="H35" s="179" t="str">
+        <x:v>User Answer</x:v>
+      </x:c>
+      <x:c r="I35" s="179" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="J35" s="179" t="str">
+        <x:v>Decision Source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="72" customHeight="1">
+      <x:c r="A36" s="76" t="str">
+        <x:v>Q6-01</x:v>
+      </x:c>
+      <x:c r="B36" s="76" t="str">
+        <x:v>Iteration Burndown</x:v>
+      </x:c>
+      <x:c r="C36" s="76" t="str">
+        <x:v>Remaining series</x:v>
+      </x:c>
+      <x:c r="D36" s="76" t="str">
+        <x:v>SUM Task.todo at end of day</x:v>
+      </x:c>
+      <x:c r="E36" s="76" t="str">
+        <x:v>Represents current remaining hours</x:v>
+      </x:c>
+      <x:c r="F36" s="76" t="str">
+        <x:v>Derive from accepted points</x:v>
+      </x:c>
+      <x:c r="G36" s="76" t="str">
+        <x:v>Historical chart would be wrong</x:v>
+      </x:c>
+      <x:c r="H36" s="190" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="I36" s="221" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="J36" s="76" t="str">
+        <x:v>Burndown SRS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="72" customHeight="1">
+      <x:c r="A37" s="76" t="str">
+        <x:v>Q6-02</x:v>
+      </x:c>
+      <x:c r="B37" s="76" t="str">
+        <x:v>Iteration Burndown</x:v>
+      </x:c>
+      <x:c r="C37" s="76" t="str">
+        <x:v>Ideal baseline</x:v>
+      </x:c>
+      <x:c r="D37" s="76" t="str">
+        <x:v>Task Estimate captured once at Iteration start</x:v>
+      </x:c>
+      <x:c r="E37" s="76" t="str">
+        <x:v>Stable planning target</x:v>
+      </x:c>
+      <x:c r="F37" s="76" t="str">
+        <x:v>Current ToDo</x:v>
+      </x:c>
+      <x:c r="G37" s="76" t="str">
+        <x:v>Ideal would move</x:v>
+      </x:c>
+      <x:c r="H37" s="190" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="I37" s="221" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="J37" s="76" t="str">
+        <x:v>Burndown SRS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="72" customHeight="1">
+      <x:c r="A38" s="76" t="str">
+        <x:v>Q6-03</x:v>
+      </x:c>
+      <x:c r="B38" s="76" t="str">
+        <x:v>Velocity</x:v>
+      </x:c>
+      <x:c r="C38" s="76" t="str">
+        <x:v>Segments</x:v>
+      </x:c>
+      <x:c r="D38" s="76" t="str">
+        <x:v>During / After / Not Accepted</x:v>
+      </x:c>
+      <x:c r="E38" s="76" t="str">
+        <x:v>Distinguishes on-time and late</x:v>
+      </x:c>
+      <x:c r="F38" s="76" t="str">
+        <x:v>One accepted total</x:v>
+      </x:c>
+      <x:c r="G38" s="76" t="str">
+        <x:v>Lateness is hidden</x:v>
+      </x:c>
+      <x:c r="H38" s="190" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="I38" s="221" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="J38" s="76" t="str">
+        <x:v>Velocity SRS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="72" customHeight="1">
+      <x:c r="A39" s="76" t="str">
+        <x:v>Q6-04</x:v>
+      </x:c>
+      <x:c r="B39" s="76" t="str">
+        <x:v>Velocity</x:v>
+      </x:c>
+      <x:c r="C39" s="76" t="str">
+        <x:v>Window and averages</x:v>
+      </x:c>
+      <x:c r="D39" s="76" t="str">
+        <x:v>Last 5 or 10; During only</x:v>
+      </x:c>
+      <x:c r="E39" s="76" t="str">
+        <x:v>Comparable team pace</x:v>
+      </x:c>
+      <x:c r="F39" s="76" t="str">
+        <x:v>Include late/unaccepted</x:v>
+      </x:c>
+      <x:c r="G39" s="76" t="str">
+        <x:v>Trend is distorted</x:v>
+      </x:c>
+      <x:c r="H39" s="190" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="I39" s="221" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="J39" s="76" t="str">
+        <x:v>Velocity SRS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="86" customHeight="1">
+      <x:c r="A40" s="76" t="str">
+        <x:v>Q6-05</x:v>
+      </x:c>
+      <x:c r="B40" s="76" t="str">
+        <x:v>Team Capacity</x:v>
+      </x:c>
+      <x:c r="C40" s="76" t="str">
+        <x:v>Source and fields</x:v>
+      </x:c>
+      <x:c r="D40" s="76" t="str">
+        <x:v>Team Status; Capacity, Estimate, ToDo, Actual</x:v>
+      </x:c>
+      <x:c r="E40" s="76" t="str">
+        <x:v>Matches operational capacity</x:v>
+      </x:c>
+      <x:c r="F40" s="76" t="str">
+        <x:v>Capacity Plan points</x:v>
+      </x:c>
+      <x:c r="G40" s="76" t="str">
+        <x:v>Units/timebox mismatch</x:v>
+      </x:c>
+      <x:c r="H40" s="190" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="I40" s="221" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="J40" s="76" t="str">
+        <x:v>Team Capacity SRS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="72" customHeight="1">
+      <x:c r="A41" s="76" t="str">
+        <x:v>Q6-06</x:v>
+      </x:c>
+      <x:c r="B41" s="76" t="str">
+        <x:v>Release Tracking</x:v>
+      </x:c>
+      <x:c r="C41" s="76" t="str">
+        <x:v>Classification</x:v>
+      </x:c>
+      <x:c r="D41" s="76" t="str">
+        <x:v>Owning Release fields and direct child relationships</x:v>
+      </x:c>
+      <x:c r="E41" s="76" t="str">
+        <x:v>Mutually exclusive buckets</x:v>
+      </x:c>
+      <x:c r="F41" s="76" t="str">
+        <x:v>Child match percentage</x:v>
+      </x:c>
+      <x:c r="G41" s="76" t="str">
+        <x:v>Counts become ambiguous</x:v>
+      </x:c>
+      <x:c r="H41" s="190" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="I41" s="221" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="J41" s="76" t="str">
+        <x:v>Release Tracking SRS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="72" customHeight="1">
+      <x:c r="A42" s="76" t="str">
+        <x:v>Q6-07</x:v>
+      </x:c>
+      <x:c r="B42" s="76" t="str">
+        <x:v>Release Tracking</x:v>
+      </x:c>
+      <x:c r="C42" s="76" t="str">
+        <x:v>Unparented filter</x:v>
+      </x:c>
+      <x:c r="D42" s="76" t="str">
+        <x:v>Only its own selected Release and current scope</x:v>
+      </x:c>
+      <x:c r="E42" s="76" t="str">
+        <x:v>Preserves filter meaning</x:v>
+      </x:c>
+      <x:c r="F42" s="76" t="str">
+        <x:v>Every Release</x:v>
+      </x:c>
+      <x:c r="G42" s="76" t="str">
+        <x:v>Duplicates totals</x:v>
+      </x:c>
+      <x:c r="H42" s="190" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="I42" s="221" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="J42" s="76" t="str">
+        <x:v>RT-Q-01 resolved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="52" customHeight="1">
+      <x:c r="A43" t="str">
+        <x:v>Q6-08</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Release Tracking</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Dependencies</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>Future Backlog FB-P6-001</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>Needs separate dependency contract</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>Expose placeholder as active</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>Implies unsupported behavior</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="I43" s="227" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>Release Tracking SRS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="28" customHeight="1">
+      <x:c r="A44" s="130" t="str">
+        <x:v>Source precedence: Phase 6 report SRS files and Phase 6/01_Release_Tracking/SRS.md override historical workbook drafts and static mock fixtures.</x:v>
+      </x:c>
+      <x:c r="B44" s="130"/>
+      <x:c r="C44" s="130"/>
+      <x:c r="D44" s="130"/>
+      <x:c r="E44" s="130"/>
+      <x:c r="F44" s="130"/>
+      <x:c r="G44" s="130"/>
+      <x:c r="H44" s="130"/>
+      <x:c r="I44" s="130"/>
+      <x:c r="J44" s="130"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+    <x:mergeCell ref="A7:J7"/>
+    <x:mergeCell ref="A14:J14"/>
+    <x:mergeCell ref="A16:J16"/>
+    <x:mergeCell ref="A23:J23"/>
+    <x:mergeCell ref="A34:J34"/>
+    <x:mergeCell ref="A44:J44"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="J9:J12">
+    <x:cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="Decision Pending"/>
+    <x:cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="Draft Proposal"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F25:F32">
+    <x:cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="Decision Pending"/>
+    <x:cfRule type="containsText" dxfId="14" priority="4" operator="containsText" text="Planned"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="I36:I42">
+      <x:formula1>"Decision Pending,Confirmed,Rejected,Needs Revision"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="39" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="29" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="195" t="str">
+        <x:v>PORTFOLIO &gt; RELEASE TRACKING — BUSINESS CONTRACT</x:v>
+      </x:c>
+      <x:c r="B1" s="195"/>
+      <x:c r="C1" s="195"/>
+      <x:c r="D1" s="195"/>
+      <x:c r="E1" s="195"/>
+      <x:c r="F1" s="195"/>
+      <x:c r="G1" s="195"/>
+      <x:c r="H1" s="195"/>
+      <x:c r="I1" s="195"/>
+      <x:c r="J1" s="195"/>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="197" t="str">
+        <x:v>BA/mockup approved | Updated 2026-07-31 | All business decisions closed | DEV implementation and production history excluded</x:v>
+      </x:c>
+      <x:c r="B2" s="197"/>
+      <x:c r="C2" s="197"/>
+      <x:c r="D2" s="197"/>
+      <x:c r="E2" s="197"/>
+      <x:c r="F2" s="197"/>
+      <x:c r="G2" s="197"/>
+      <x:c r="H2" s="197"/>
+      <x:c r="I2" s="197"/>
+      <x:c r="J2" s="197"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="193"/>
+      <x:c r="B3" s="193"/>
+      <x:c r="C3" s="193"/>
+      <x:c r="D3" s="193"/>
+      <x:c r="E3" s="193"/>
+      <x:c r="F3" s="193"/>
+      <x:c r="G3" s="193"/>
+      <x:c r="H3" s="193"/>
+      <x:c r="I3" s="193"/>
+      <x:c r="J3" s="193"/>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="205" t="str">
+        <x:v>Phase</x:v>
+      </x:c>
+      <x:c r="B4" s="204" t="str">
+        <x:v>Phase 6</x:v>
+      </x:c>
+      <x:c r="C4" s="205" t="str">
+        <x:v>Navigation</x:v>
+      </x:c>
+      <x:c r="D4" s="204" t="str">
+        <x:v>Portfolio &gt; Release Tracking (final Portfolio item)</x:v>
+      </x:c>
+      <x:c r="E4" s="205" t="str">
+        <x:v>Primary Filter</x:v>
+      </x:c>
+      <x:c r="F4" s="204" t="str">
+        <x:v>Selected Release</x:v>
+      </x:c>
+      <x:c r="G4" s="205" t="str">
+        <x:v>Shared Unit</x:v>
+      </x:c>
+      <x:c r="H4" s="204" t="str">
+        <x:v>Chart Unit: Points / Count</x:v>
+      </x:c>
+      <x:c r="I4" s="205" t="str">
+        <x:v>Open Decisions</x:v>
+      </x:c>
+      <x:c r="J4" s="206" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="205" t="str">
+        <x:v>BA Status</x:v>
+      </x:c>
+      <x:c r="B5" s="234" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="C5" s="205" t="str">
+        <x:v>Classification Rules</x:v>
+      </x:c>
+      <x:c r="D5" s="204" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E5" s="205" t="str">
+        <x:v>Mockup</x:v>
+      </x:c>
+      <x:c r="F5" s="204" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="G5" s="205" t="str">
+        <x:v>Production History</x:v>
+      </x:c>
+      <x:c r="H5" s="204" t="str">
+        <x:v>DEV-owned</x:v>
+      </x:c>
+      <x:c r="I5" s="205" t="str">
+        <x:v>Next Gate</x:v>
+      </x:c>
+      <x:c r="J5" s="204" t="str">
+        <x:v>DEV Handoff</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="193"/>
+      <x:c r="B6" s="193"/>
+      <x:c r="C6" s="193"/>
+      <x:c r="D6" s="193"/>
+      <x:c r="E6" s="193"/>
+      <x:c r="F6" s="193"/>
+      <x:c r="G6" s="193"/>
+      <x:c r="H6" s="193"/>
+      <x:c r="I6" s="193"/>
+      <x:c r="J6" s="193"/>
+    </x:row>
+    <x:row r="7" ht="23" customHeight="1">
+      <x:c r="A7" s="199" t="str">
+        <x:v>CLASSIFICATION RULES</x:v>
+      </x:c>
+      <x:c r="B7" s="199"/>
+      <x:c r="C7" s="199"/>
+      <x:c r="D7" s="199"/>
+      <x:c r="E7" s="199"/>
+      <x:c r="F7" s="199"/>
+      <x:c r="G7" s="199"/>
+      <x:c r="H7" s="199"/>
+      <x:c r="I7" s="199"/>
+      <x:c r="J7" s="199"/>
+    </x:row>
+    <x:row r="8" ht="34" customHeight="1">
+      <x:c r="A8" s="202" t="str">
+        <x:v>Rule ID</x:v>
+      </x:c>
+      <x:c r="B8" s="202" t="str">
+        <x:v>Bucket / Topic</x:v>
+      </x:c>
+      <x:c r="C8" s="202" t="str">
+        <x:v>Selected Release R condition</x:v>
+      </x:c>
+      <x:c r="D8" s="202" t="str">
+        <x:v>Appears in list?</x:v>
+      </x:c>
+      <x:c r="E8" s="202" t="str">
+        <x:v>Counts in Feature progress?</x:v>
+      </x:c>
+      <x:c r="F8" s="202" t="str">
+        <x:v>Counts in Release Planned?</x:v>
+      </x:c>
+      <x:c r="G8" s="202" t="str">
+        <x:v>Counts in Release Accepted?</x:v>
+      </x:c>
+      <x:c r="H8" s="202" t="str">
+        <x:v>Deduplication</x:v>
+      </x:c>
+      <x:c r="I8" s="202" t="str">
+        <x:v>Example</x:v>
+      </x:c>
+      <x:c r="J8" s="202" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="203" t="str">
+        <x:v>RT-BR-01</x:v>
+      </x:c>
+      <x:c r="B9" s="203" t="str">
+        <x:v>Features in Release</x:v>
+      </x:c>
+      <x:c r="C9" s="203" t="str">
+        <x:v>Feature.Release = R</x:v>
+      </x:c>
+      <x:c r="D9" s="203" t="str">
+        <x:v>Yes, as Feature</x:v>
+      </x:c>
+      <x:c r="E9" s="203" t="str">
+        <x:v>All direct Story/Defect children</x:v>
+      </x:c>
+      <x:c r="F9" s="203" t="str">
+        <x:v>N/A at Feature level</x:v>
+      </x:c>
+      <x:c r="G9" s="203" t="str">
+        <x:v>N/A at Feature level</x:v>
+      </x:c>
+      <x:c r="H9" s="203" t="str">
+        <x:v>Feature ID once</x:v>
+      </x:c>
+      <x:c r="I9" s="203" t="str">
+        <x:v>F1.Release=A; filter A -&gt; direct</x:v>
+      </x:c>
+      <x:c r="J9" s="208" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="203" t="str">
+        <x:v>RT-BR-02</x:v>
+      </x:c>
+      <x:c r="B10" s="203" t="str">
+        <x:v>Derived Features</x:v>
+      </x:c>
+      <x:c r="C10" s="203" t="str">
+        <x:v>Feature.Release != R AND any direct Story/Defect.Release = R</x:v>
+      </x:c>
+      <x:c r="D10" s="203" t="str">
+        <x:v>Yes, as Feature</x:v>
+      </x:c>
+      <x:c r="E10" s="203" t="str">
+        <x:v>All direct Story/Defect children</x:v>
+      </x:c>
+      <x:c r="F10" s="203" t="str">
+        <x:v>N/A at Feature level</x:v>
+      </x:c>
+      <x:c r="G10" s="203" t="str">
+        <x:v>N/A at Feature level</x:v>
+      </x:c>
+      <x:c r="H10" s="203" t="str">
+        <x:v>Cannot also be direct in same filter</x:v>
+      </x:c>
+      <x:c r="I10" s="203" t="str">
+        <x:v>F1.Release=A; child.Release=B; filter B -&gt; Derived</x:v>
+      </x:c>
+      <x:c r="J10" s="208" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="203" t="str">
+        <x:v>RT-BR-03</x:v>
+      </x:c>
+      <x:c r="B11" s="203" t="str">
+        <x:v>Child without Release</x:v>
+      </x:c>
+      <x:c r="C11" s="203" t="str">
+        <x:v>Item.Release is empty / Unscheduled</x:v>
+      </x:c>
+      <x:c r="D11" s="203" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E11" s="203" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F11" s="203" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G11" s="203" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="H11" s="203" t="str">
+        <x:v>Does not derive Feature into any Release</x:v>
+      </x:c>
+      <x:c r="I11" s="203" t="str">
+        <x:v>Child remains in F1 denominator but is not track-ready</x:v>
+      </x:c>
+      <x:c r="J11" s="208" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="203" t="str">
+        <x:v>RT-BR-04</x:v>
+      </x:c>
+      <x:c r="B12" s="203" t="str">
+        <x:v>Unparented Story/Defect</x:v>
+      </x:c>
+      <x:c r="C12" s="203" t="str">
+        <x:v>Item has Release and no Feature parent</x:v>
+      </x:c>
+      <x:c r="D12" s="203" t="str">
+        <x:v>Yes, in Unparented</x:v>
+      </x:c>
+      <x:c r="E12" s="203" t="str">
+        <x:v>No parent Feature</x:v>
+      </x:c>
+      <x:c r="F12" s="203" t="str">
+        <x:v>Yes, when Item.Release = R</x:v>
+      </x:c>
+      <x:c r="G12" s="203" t="str">
+        <x:v>Yes, when State is Accepted/Release</x:v>
+      </x:c>
+      <x:c r="H12" s="203" t="str">
+        <x:v>Work Item ID once</x:v>
+      </x:c>
+      <x:c r="I12" s="203" t="str">
+        <x:v>D1.Release=B, no Feature</x:v>
+      </x:c>
+      <x:c r="J12" s="236" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="203" t="str">
+        <x:v>RT-BR-05</x:v>
+      </x:c>
+      <x:c r="B13" s="203" t="str">
+        <x:v>Completion</x:v>
+      </x:c>
+      <x:c r="C13" s="203" t="str">
+        <x:v>State in {Accepted, Release}</x:v>
+      </x:c>
+      <x:c r="D13" s="203" t="str">
+        <x:v>State visible</x:v>
+      </x:c>
+      <x:c r="E13" s="203" t="str">
+        <x:v>Accepted numerator</x:v>
+      </x:c>
+      <x:c r="F13" s="203" t="str">
+        <x:v>Planned denominator</x:v>
+      </x:c>
+      <x:c r="G13" s="203" t="str">
+        <x:v>Accepted numerator</x:v>
+      </x:c>
+      <x:c r="H13" s="203" t="str">
+        <x:v>Completed stays separate</x:v>
+      </x:c>
+      <x:c r="I13" s="203" t="str">
+        <x:v>Completed does not count as accepted</x:v>
+      </x:c>
+      <x:c r="J13" s="208" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="193"/>
+      <x:c r="B14" s="193"/>
+      <x:c r="C14" s="193"/>
+      <x:c r="D14" s="193"/>
+      <x:c r="E14" s="193"/>
+      <x:c r="F14" s="193"/>
+      <x:c r="G14" s="193"/>
+      <x:c r="H14" s="193"/>
+      <x:c r="I14" s="193"/>
+      <x:c r="J14" s="193"/>
+    </x:row>
+    <x:row r="15" ht="23" customHeight="1">
+      <x:c r="A15" s="199" t="str">
+        <x:v>METRIC CONTRACTS</x:v>
+      </x:c>
+      <x:c r="B15" s="199"/>
+      <x:c r="C15" s="199"/>
+      <x:c r="D15" s="199"/>
+      <x:c r="E15" s="199"/>
+      <x:c r="F15" s="199"/>
+      <x:c r="G15" s="199"/>
+      <x:c r="H15" s="199"/>
+      <x:c r="I15" s="199"/>
+      <x:c r="J15" s="199"/>
+    </x:row>
+    <x:row r="16" ht="34" customHeight="1">
+      <x:c r="A16" s="202" t="str">
+        <x:v>Metric</x:v>
+      </x:c>
+      <x:c r="B16" s="202" t="str">
+        <x:v>Scope</x:v>
+      </x:c>
+      <x:c r="C16" s="202" t="str">
+        <x:v>Formula / Rule</x:v>
+      </x:c>
+      <x:c r="D16" s="202" t="str">
+        <x:v>Other-Release child</x:v>
+      </x:c>
+      <x:c r="E16" s="202" t="str">
+        <x:v>Unreleased child</x:v>
+      </x:c>
+      <x:c r="F16" s="202" t="str">
+        <x:v>Zero denominator</x:v>
+      </x:c>
+      <x:c r="G16" s="202" t="str">
+        <x:v>Display</x:v>
+      </x:c>
+      <x:c r="H16" s="202" t="str">
+        <x:v>Drill-down</x:v>
+      </x:c>
+      <x:c r="I16" s="202" t="str">
+        <x:v>Data readiness</x:v>
+      </x:c>
+      <x:c r="J16" s="202" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="203" t="str">
+        <x:v>Direct Feature Status</x:v>
+      </x:c>
+      <x:c r="B17" s="203" t="str">
+        <x:v>Feature.releaseId = R in current scope</x:v>
+      </x:c>
+      <x:c r="C17" s="203" t="str">
+        <x:v>Accepted/total from every direct Story/Defect child; percent = floor(accepted/total*100)</x:v>
+      </x:c>
+      <x:c r="D17" s="203" t="str">
+        <x:v>Included</x:v>
+      </x:c>
+      <x:c r="E17" s="203" t="str">
+        <x:v>Included</x:v>
+      </x:c>
+      <x:c r="F17" s="203" t="str">
+        <x:v>0% and 0/0</x:v>
+      </x:c>
+      <x:c r="G17" s="203" t="str">
+        <x:v>% plus accepted/total</x:v>
+      </x:c>
+      <x:c r="H17" s="203" t="str">
+        <x:v>All direct children</x:v>
+      </x:c>
+      <x:c r="I17" s="203" t="str">
+        <x:v>Current state</x:v>
+      </x:c>
+      <x:c r="J17" s="208" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="203" t="str">
+        <x:v>Derived Feature Status</x:v>
+      </x:c>
+      <x:c r="B18" s="203" t="str">
+        <x:v>Feature.releaseId != R with matching child</x:v>
+      </x:c>
+      <x:c r="C18" s="203" t="str">
+        <x:v>Accepted/total from children whose releaseId = R and ownership is in current scope</x:v>
+      </x:c>
+      <x:c r="D18" s="203" t="str">
+        <x:v>Only matching R</x:v>
+      </x:c>
+      <x:c r="E18" s="203" t="str">
+        <x:v>Excluded</x:v>
+      </x:c>
+      <x:c r="F18" s="203" t="str">
+        <x:v>0/0</x:v>
+      </x:c>
+      <x:c r="G18" s="203" t="str">
+        <x:v>Accepted/total only</x:v>
+      </x:c>
+      <x:c r="H18" s="203" t="str">
+        <x:v>Matching children</x:v>
+      </x:c>
+      <x:c r="I18" s="203" t="str">
+        <x:v>Current state</x:v>
+      </x:c>
+      <x:c r="J18" s="208" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="A19" s="203" t="str">
+        <x:v>Release Planned</x:v>
+      </x:c>
+      <x:c r="B19" s="203" t="str">
+        <x:v>TrackedLeaves(R,S)</x:v>
+      </x:c>
+      <x:c r="C19" s="203" t="str">
+        <x:v>Points = SUM planEstimate; Count = Work Item count</x:v>
+      </x:c>
+      <x:c r="D19" s="203" t="str">
+        <x:v>Only child assigned R</x:v>
+      </x:c>
+      <x:c r="E19" s="203" t="str">
+        <x:v>Excluded</x:v>
+      </x:c>
+      <x:c r="F19" s="203" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="203" t="str">
+        <x:v>Planned series/KPI</x:v>
+      </x:c>
+      <x:c r="H19" s="203" t="str">
+        <x:v>Release items</x:v>
+      </x:c>
+      <x:c r="I19" s="203" t="str">
+        <x:v>Current + history</x:v>
+      </x:c>
+      <x:c r="J19" s="208" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="A20" s="203" t="str">
+        <x:v>Release Accepted</x:v>
+      </x:c>
+      <x:c r="B20" s="203" t="str">
+        <x:v>TrackedLeaves(R,S) in Accepted or Release</x:v>
+      </x:c>
+      <x:c r="C20" s="203" t="str">
+        <x:v>Points = SUM planEstimate; Count = Work Item count</x:v>
+      </x:c>
+      <x:c r="D20" s="203" t="str">
+        <x:v>Only child assigned R</x:v>
+      </x:c>
+      <x:c r="E20" s="203" t="str">
+        <x:v>Excluded</x:v>
+      </x:c>
+      <x:c r="F20" s="203" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="203" t="str">
+        <x:v>Accepted series/KPI</x:v>
+      </x:c>
+      <x:c r="H20" s="203" t="str">
+        <x:v>Accepted items</x:v>
+      </x:c>
+      <x:c r="I20" s="203" t="str">
+        <x:v>Current + history</x:v>
+      </x:c>
+      <x:c r="J20" s="208" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="203" t="str">
+        <x:v>Preliminary / Ideal / History</x:v>
+      </x:c>
+      <x:c r="B21" s="203" t="str">
+        <x:v>Direct + Derived Features and Release date range</x:v>
+      </x:c>
+      <x:c r="C21" s="203" t="str">
+        <x:v>Preliminary uses top-down estimate; historical series requires snapshots/events; Ideal uses persisted Release baseline</x:v>
+      </x:c>
+      <x:c r="D21" s="203" t="str">
+        <x:v>Feature deduped</x:v>
+      </x:c>
+      <x:c r="E21" s="203" t="str">
+        <x:v>Not tracked</x:v>
+      </x:c>
+      <x:c r="F21" s="203" t="str">
+        <x:v>Unavailable state</x:v>
+      </x:c>
+      <x:c r="G21" s="203" t="str">
+        <x:v>Burnup</x:v>
+      </x:c>
+      <x:c r="H21" s="203" t="str">
+        <x:v>Date / iteration</x:v>
+      </x:c>
+      <x:c r="I21" s="203" t="str">
+        <x:v>DEV data dependency</x:v>
+      </x:c>
+      <x:c r="J21" s="208" t="str">
+        <x:v>Confirmed contract</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="193"/>
+      <x:c r="B22" s="193"/>
+      <x:c r="C22" s="193"/>
+      <x:c r="D22" s="193"/>
+      <x:c r="E22" s="193"/>
+      <x:c r="F22" s="193"/>
+      <x:c r="G22" s="193"/>
+      <x:c r="H22" s="193"/>
+      <x:c r="I22" s="193"/>
+      <x:c r="J22" s="193"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="193"/>
+      <x:c r="B23" s="193"/>
+      <x:c r="C23" s="193"/>
+      <x:c r="D23" s="193"/>
+      <x:c r="E23" s="193"/>
+      <x:c r="F23" s="193"/>
+      <x:c r="G23" s="193"/>
+      <x:c r="H23" s="193"/>
+      <x:c r="I23" s="193"/>
+      <x:c r="J23" s="193"/>
+    </x:row>
+    <x:row r="24" ht="23" customHeight="1">
+      <x:c r="A24" s="199" t="str">
+        <x:v>MOCKUP / PAGE CONTRACT</x:v>
+      </x:c>
+      <x:c r="B24" s="199"/>
+      <x:c r="C24" s="199"/>
+      <x:c r="D24" s="199"/>
+      <x:c r="E24" s="199"/>
+      <x:c r="F24" s="199"/>
+      <x:c r="G24" s="199"/>
+      <x:c r="H24" s="199"/>
+      <x:c r="I24" s="199"/>
+      <x:c r="J24" s="199"/>
+    </x:row>
+    <x:row r="25" ht="34" customHeight="1">
+      <x:c r="A25" s="202" t="str">
+        <x:v>Area</x:v>
+      </x:c>
+      <x:c r="B25" s="202" t="str">
+        <x:v>Control / Component</x:v>
+      </x:c>
+      <x:c r="C25" s="202" t="str">
+        <x:v>Default</x:v>
+      </x:c>
+      <x:c r="D25" s="202" t="str">
+        <x:v>Business behavior</x:v>
+      </x:c>
+      <x:c r="E25" s="202" t="str">
+        <x:v>Data shown</x:v>
+      </x:c>
+      <x:c r="F25" s="202" t="str">
+        <x:v>Empty state</x:v>
+      </x:c>
+      <x:c r="G25" s="202" t="str">
+        <x:v>Interaction</x:v>
+      </x:c>
+      <x:c r="H25" s="202" t="str">
+        <x:v>Permission posture</x:v>
+      </x:c>
+      <x:c r="I25" s="202" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="J25" s="202" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="42" customHeight="1">
+      <x:c r="A26" s="203" t="str">
+        <x:v>Header</x:v>
+      </x:c>
+      <x:c r="B26" s="203" t="str">
+        <x:v>Release selector + dates + previous/next</x:v>
+      </x:c>
+      <x:c r="C26" s="203" t="str">
+        <x:v>First Project Release</x:v>
+      </x:c>
+      <x:c r="D26" s="203" t="str">
+        <x:v>Global Project/Team scope; no duplicate filter</x:v>
+      </x:c>
+      <x:c r="E26" s="203" t="str">
+        <x:v>Release and date window</x:v>
+      </x:c>
+      <x:c r="F26" s="203" t="str">
+        <x:v>No Release for Project</x:v>
+      </x:c>
+      <x:c r="G26" s="203" t="str">
+        <x:v>Select/step Release</x:v>
+      </x:c>
+      <x:c r="H26" s="203" t="str">
+        <x:v>Authorized read</x:v>
+      </x:c>
+      <x:c r="I26" s="203" t="str">
+        <x:v>Release registry</x:v>
+      </x:c>
+      <x:c r="J26" s="208" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="42" customHeight="1">
+      <x:c r="A27" s="203" t="str">
+        <x:v>Summary</x:v>
+      </x:c>
+      <x:c r="B27" s="203" t="str">
+        <x:v>Direct / Derived / Unparented counters + terminology tooltip</x:v>
+      </x:c>
+      <x:c r="C27" s="203" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="D27" s="203" t="str">
+        <x:v>Counts use owning fields and current scope</x:v>
+      </x:c>
+      <x:c r="E27" s="203" t="str">
+        <x:v>Three non-overlapping counts</x:v>
+      </x:c>
+      <x:c r="F27" s="203" t="str">
+        <x:v>0 allowed</x:v>
+      </x:c>
+      <x:c r="G27" s="203" t="str">
+        <x:v>Select active bucket</x:v>
+      </x:c>
+      <x:c r="H27" s="203" t="str">
+        <x:v>Read-only</x:v>
+      </x:c>
+      <x:c r="I27" s="203" t="str">
+        <x:v>Classification rules</x:v>
+      </x:c>
+      <x:c r="J27" s="208" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="A28" s="203" t="str">
+        <x:v>List</x:v>
+      </x:c>
+      <x:c r="B28" s="203" t="str">
+        <x:v>Bucket selector, search, resizable/sortable columns</x:v>
+      </x:c>
+      <x:c r="C28" s="203" t="str">
+        <x:v>Direct</x:v>
+      </x:c>
+      <x:c r="D28" s="203" t="str">
+        <x:v>Numeric rank per bucket; Chart Unit controls Status</x:v>
+      </x:c>
+      <x:c r="E28" s="203" t="str">
+        <x:v>Rank, ID, Team, Issue, Name, Status</x:v>
+      </x:c>
+      <x:c r="F28" s="203" t="str">
+        <x:v>Empty bucket</x:v>
+      </x:c>
+      <x:c r="G28" s="203" t="str">
+        <x:v>Sort/resize/open item</x:v>
+      </x:c>
+      <x:c r="H28" s="203" t="str">
+        <x:v>Read-only</x:v>
+      </x:c>
+      <x:c r="I28" s="203" t="str">
+        <x:v>Feature/Work Item</x:v>
+      </x:c>
+      <x:c r="J28" s="208" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="42" customHeight="1">
+      <x:c r="A29" s="203" t="str">
+        <x:v>Chart</x:v>
+      </x:c>
+      <x:c r="B29" s="203" t="str">
+        <x:v>Release Burnup</x:v>
+      </x:c>
+      <x:c r="C29" s="203" t="str">
+        <x:v>Points</x:v>
+      </x:c>
+      <x:c r="D29" s="203" t="str">
+        <x:v>Points/Count, correct title/dates/Y label and iteration row</x:v>
+      </x:c>
+      <x:c r="E29" s="203" t="str">
+        <x:v>Accepted, Planned, Preliminary, Ideal</x:v>
+      </x:c>
+      <x:c r="F29" s="203" t="str">
+        <x:v>Unavailable history</x:v>
+      </x:c>
+      <x:c r="G29" s="203" t="str">
+        <x:v>Hover</x:v>
+      </x:c>
+      <x:c r="H29" s="203" t="str">
+        <x:v>Read-only</x:v>
+      </x:c>
+      <x:c r="I29" s="203" t="str">
+        <x:v>Snapshots/events + baseline</x:v>
+      </x:c>
+      <x:c r="J29" s="208" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="42" customHeight="1">
+      <x:c r="A30" s="203" t="str">
+        <x:v>Issues</x:v>
+      </x:c>
+      <x:c r="B30" s="203" t="str">
+        <x:v>Red mismatch icon + overlay</x:v>
+      </x:c>
+      <x:c r="C30" s="203" t="str">
+        <x:v>Closed</x:v>
+      </x:c>
+      <x:c r="D30" s="203" t="str">
+        <x:v>Group by issue; selected Release comparison; full-mismatch warning; outside-click closes</x:v>
+      </x:c>
+      <x:c r="E30" s="203" t="str">
+        <x:v>Feature progress + mismatched items</x:v>
+      </x:c>
+      <x:c r="F30" s="203" t="str">
+        <x:v>No icon if no mismatch</x:v>
+      </x:c>
+      <x:c r="G30" s="203" t="str">
+        <x:v>Open/close item</x:v>
+      </x:c>
+      <x:c r="H30" s="203" t="str">
+        <x:v>Read-only</x:v>
+      </x:c>
+      <x:c r="I30" s="203" t="str">
+        <x:v>Direct children</x:v>
+      </x:c>
+      <x:c r="J30" s="208" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="42" customHeight="1">
+      <x:c r="A31" s="203" t="str">
+        <x:v>Dependencies</x:v>
+      </x:c>
+      <x:c r="B31" s="203" t="str">
+        <x:v>Disabled Future control</x:v>
+      </x:c>
+      <x:c r="C31" s="203" t="str">
+        <x:v>Unavailable</x:v>
+      </x:c>
+      <x:c r="D31" s="203" t="str">
+        <x:v>No active behavior</x:v>
+      </x:c>
+      <x:c r="E31" s="203" t="str">
+        <x:v>Future label</x:v>
+      </x:c>
+      <x:c r="F31" s="203" t="str">
+        <x:v>Not available</x:v>
+      </x:c>
+      <x:c r="G31" s="203" t="str">
+        <x:v>No action</x:v>
+      </x:c>
+      <x:c r="H31" s="203" t="str">
+        <x:v>Read-only</x:v>
+      </x:c>
+      <x:c r="I31" s="203" t="str">
+        <x:v>FB-P6-001</x:v>
+      </x:c>
+      <x:c r="J31" s="208" t="str">
+        <x:v>Future Backlog</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="193"/>
+      <x:c r="B32" s="193"/>
+      <x:c r="C32" s="193"/>
+      <x:c r="D32" s="193"/>
+      <x:c r="E32" s="193"/>
+      <x:c r="F32" s="193"/>
+      <x:c r="G32" s="193"/>
+      <x:c r="H32" s="193"/>
+      <x:c r="I32" s="193"/>
+      <x:c r="J32" s="193"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="193"/>
+      <x:c r="B33" s="193"/>
+      <x:c r="C33" s="193"/>
+      <x:c r="D33" s="193"/>
+      <x:c r="E33" s="193"/>
+      <x:c r="F33" s="193"/>
+      <x:c r="G33" s="193"/>
+      <x:c r="H33" s="193"/>
+      <x:c r="I33" s="193"/>
+      <x:c r="J33" s="193"/>
+    </x:row>
+    <x:row r="34" ht="23" customHeight="1">
+      <x:c r="A34" s="199" t="str">
+        <x:v>CONFIRMED DECISIONS</x:v>
+      </x:c>
+      <x:c r="B34" s="199"/>
+      <x:c r="C34" s="199"/>
+      <x:c r="D34" s="199"/>
+      <x:c r="E34" s="199"/>
+      <x:c r="F34" s="199"/>
+      <x:c r="G34" s="199"/>
+      <x:c r="H34" s="199"/>
+      <x:c r="I34" s="199"/>
+      <x:c r="J34" s="199"/>
+    </x:row>
+    <x:row r="35" ht="34" customHeight="1">
+      <x:c r="A35" s="202" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="B35" s="202" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="C35" s="202" t="str">
+        <x:v>Approved Rule</x:v>
+      </x:c>
+      <x:c r="D35" s="202" t="str">
+        <x:v>Reason</x:v>
+      </x:c>
+      <x:c r="E35" s="202" t="str">
+        <x:v>Alternative</x:v>
+      </x:c>
+      <x:c r="F35" s="202" t="str">
+        <x:v>Impact</x:v>
+      </x:c>
+      <x:c r="G35" s="202" t="str">
+        <x:v>Mockup</x:v>
+      </x:c>
+      <x:c r="H35" s="202" t="str">
+        <x:v>Owner</x:v>
+      </x:c>
+      <x:c r="I35" s="202" t="str">
+        <x:v>Next Action</x:v>
+      </x:c>
+      <x:c r="J35" s="202" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="42" customHeight="1">
+      <x:c r="A36" s="203" t="str">
+        <x:v>RT-Q-01</x:v>
+      </x:c>
+      <x:c r="B36" s="203" t="str">
+        <x:v>Unparented Release filter</x:v>
+      </x:c>
+      <x:c r="C36" s="203" t="str">
+        <x:v>Only under its own selected Release and current Project/Team scope</x:v>
+      </x:c>
+      <x:c r="D36" s="203" t="str">
+        <x:v>Preserves filter meaning</x:v>
+      </x:c>
+      <x:c r="E36" s="203" t="str">
+        <x:v>Every Release</x:v>
+      </x:c>
+      <x:c r="F36" s="203" t="str">
+        <x:v>Would duplicate counts/totals</x:v>
+      </x:c>
+      <x:c r="G36" s="203" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H36" s="203" t="str">
+        <x:v>BA/PO</x:v>
+      </x:c>
+      <x:c r="I36" s="203" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="J36" s="236" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="42" customHeight="1">
+      <x:c r="A37" s="203" t="str">
+        <x:v>RT-Q-02</x:v>
+      </x:c>
+      <x:c r="B37" s="203" t="str">
+        <x:v>Derived rank</x:v>
+      </x:c>
+      <x:c r="C37" s="203" t="str">
+        <x:v>Numeric sequential rank inside active Derived bucket</x:v>
+      </x:c>
+      <x:c r="D37" s="203" t="str">
+        <x:v>Consistent list behavior</x:v>
+      </x:c>
+      <x:c r="E37" s="203" t="str">
+        <x:v>D marker</x:v>
+      </x:c>
+      <x:c r="F37" s="203" t="str">
+        <x:v>Mixed rank semantics</x:v>
+      </x:c>
+      <x:c r="G37" s="203" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H37" s="203" t="str">
+        <x:v>BA/PO</x:v>
+      </x:c>
+      <x:c r="I37" s="203" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="J37" s="236" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="193" t="str">
+        <x:v>RT-Q-03</x:v>
+      </x:c>
+      <x:c r="B38" s="193" t="str">
+        <x:v>Points / Count selector</x:v>
+      </x:c>
+      <x:c r="C38" s="193" t="str">
+        <x:v>Chart Unit is the only selector and changes list plus chart</x:v>
+      </x:c>
+      <x:c r="D38" s="193" t="str">
+        <x:v>Single source of display unit</x:v>
+      </x:c>
+      <x:c r="E38" s="193" t="str">
+        <x:v>Separate Grid Unit</x:v>
+      </x:c>
+      <x:c r="F38" s="193" t="str">
+        <x:v>Controls can disagree</x:v>
+      </x:c>
+      <x:c r="G38" s="193" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H38" s="193" t="str">
+        <x:v>BA/PO</x:v>
+      </x:c>
+      <x:c r="I38" s="193" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="J38" s="239" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="193" t="str">
+        <x:v>RT-Q-04</x:v>
+      </x:c>
+      <x:c r="B39" s="193" t="str">
+        <x:v>Views</x:v>
+      </x:c>
+      <x:c r="C39" s="193" t="str">
+        <x:v>Chart only; Breakdown removed; Dependencies stays Future</x:v>
+      </x:c>
+      <x:c r="D39" s="193" t="str">
+        <x:v>Matches approved slice</x:v>
+      </x:c>
+      <x:c r="E39" s="193" t="str">
+        <x:v>Expose unfinished views</x:v>
+      </x:c>
+      <x:c r="F39" s="193" t="str">
+        <x:v>Implies unsupported behavior</x:v>
+      </x:c>
+      <x:c r="G39" s="193" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="H39" s="193" t="str">
+        <x:v>BA/PO</x:v>
+      </x:c>
+      <x:c r="I39" s="193" t="str">
+        <x:v>FB-P6-001</x:v>
+      </x:c>
+      <x:c r="J39" s="239" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="32" customHeight="1">
+      <x:c r="A40" s="211" t="str">
+        <x:v>Source: 04_Developement_tracking/Phase 6/01_Release_Tracking/SRS.md. BA/mockup approved 2026-07-31; DEV owns production persistence, history, APIs, authorization, tests and deployment.</x:v>
+      </x:c>
+      <x:c r="B40" s="211"/>
+      <x:c r="C40" s="211"/>
+      <x:c r="D40" s="211"/>
+      <x:c r="E40" s="211"/>
+      <x:c r="F40" s="211"/>
+      <x:c r="G40" s="211"/>
+      <x:c r="H40" s="211"/>
+      <x:c r="I40" s="211"/>
+      <x:c r="J40" s="211"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+    <x:mergeCell ref="A7:J7"/>
+    <x:mergeCell ref="A15:J15"/>
+    <x:mergeCell ref="A24:J24"/>
+    <x:mergeCell ref="A34:J34"/>
+    <x:mergeCell ref="A40:J40"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>